--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -15,11 +15,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$I$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Смета'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Заказ Гросснер'!$A$4:$F$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Заказ Гросснер'!$A$4:$F$64</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Заказ Гросснер'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ведомость рукавов'!$A$4:$G$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Ведомость рукавов'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ведомость соединений'!$A$4:$E$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ведомость соединений'!$A$4:$E$89</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Ведомость соединений'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,29 +761,29 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="8" t="n"/>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
+    <row r="6" ht="43.5" customHeight="1">
       <c r="A6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Переход 50,5→½″ (для P3)</t>
+          <t>Переход кламп концентрический К50,5 → К25 (1″ × ½″), 3A, AISI 316</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>штуцер P3 → кран V-P3 (дозирование)</t>
+          <t>штуцер P3 → кран V-P3 (1); отводы тройников под BV-1: SP-1, V-S1 (2); отвод тройника на входе нутча (1)</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Гросснер: переход кламп</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -805,7 +805,7 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Тройник кламп ½″ (порт регулятора G-1 → PSV-3, аргон A2)</t>
+          <t>Тройник кламп прямой К25 (½″), 3A, AISI 316 (порт регулятора G-1 → PSV-3, аргон A2)</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
       <c r="I7" s="19" t="inlineStr">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
+    <row r="19" ht="70.5" customHeight="1">
       <c r="A19" s="9" t="n">
         <v>13</v>
       </c>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Заглушка-переход 3″→½″ (концентрический)</t>
+          <t>Переход кламп 3″ → ½″ (К91 → К25), концентрический</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>низ и верх колонн C-1, C-2</t>
+          <t>низ и верх колонн C-1, C-2; в каталоге Гросснера одной деталью нет (переходы 3″ — от 91 × 50,5, 4″ — от 119 × 64): заказать изготовление у Гросснера или собрать из двух-трёх переходов</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -1281,35 +1281,31 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Гросснер: заглушка кламп</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>grossner.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+          <t>Гросснер: переход кламп</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="43.5" customHeight="1">
       <c r="A20" s="15" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="16" t="n"/>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый 3″ (сетка ≤ 1 мм, 316)</t>
+          <t>Фильтр межкламповый 3″ (К91), AISI 316: перфорированный диск 3 мм + сетка 0,5 мм</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>опора и верх засыпки C-1, C-2</t>
+          <t>опора засыпки: низ C-1, C-2 — на нём лежат сита / NaOH; верх — прижим засыпки. В кламп-стык между двумя прокладками EPDM K91</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
@@ -1329,7 +1325,7 @@
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый</t>
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
       <c r="I20" s="17" t="n"/>
@@ -2142,29 +2138,29 @@
       </c>
       <c r="I42" s="11" t="n"/>
     </row>
-    <row r="43" ht="57" customHeight="1">
+    <row r="43" ht="70.5" customHeight="1">
       <c r="A43" s="15" t="n">
         <v>34</v>
       </c>
       <c r="B43" s="16" t="n"/>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Тройник кламп переходной 50,5 × ½″ под BV-1: 45° + прямой</t>
+          <t>Тройники кламп прямые равнопроходные К50,5 (1″), 3A, AISI 316 под BV-1 (переходы К50,5 → К25 на отводы — строка «Переход 50,5→½″»)</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>1-й (45°): отвод вниз — проба SP-1; 2-й (прямой): вбок V-S1 на бочку; прямо — выгрузка 50,5 на P-2. Размер выхода BV-1 замерить</t>
+          <t>1-й: вниз — проба SP-1; 2-й: вбок V-S1 на бочку; прямо — выгрузка 50,5 на P-2. Переходных тройников 50,5 × 25 у Гросснера нет — тройник + переход. Размер выхода BV-1 замерить</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>1 + 1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F43" s="18" t="inlineStr">
         <is>
-          <t>2 + 2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
@@ -2174,14 +2170,10 @@
       </c>
       <c r="H43" s="19" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45°</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr">
-        <is>
-          <t>grossner.ru</t>
-        </is>
-      </c>
+          <t>Гросснер: тройник кламп 1″ 316</t>
+        </is>
+      </c>
+      <c r="I43" s="17" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="9" t="n">
@@ -2479,7 +2471,7 @@
       </c>
       <c r="I51" s="17" t="n"/>
     </row>
-    <row r="52" ht="111" customHeight="1">
+    <row r="52" ht="151.5" customHeight="1">
       <c r="A52" s="9" t="n">
         <v>43</v>
       </c>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Нутч — сборка K119 на клампах: тройник 45° переходной 50,5×½″ (вход), 3 тройника ½″ гребёнки, 1 переходник ½″→¼″ (аргон A4, V-F1); PI-5 и PSV-4 — на кламп прямо на тройники, переход 50,5→K119, диоптр K119, 2 царги K119 × 500, межкламповый фильтр K119, переход K119→½″, хомуты усиленные и прокладки PTFE K119 × 5</t>
+          <t>Нутч — сборка K119 на клампах: тройник прямой К50,5 + переход 50,5 → 25 на отвод (вход, вбок — гребёнка), 3 тройника прямых К25 гребёнки, 1 переходник ½″ → ¼″ (аргон A4, V-F1); PI-5 и PSV-4 — на кламп прямо на тройники; переход 50,5 → K119*, диоптр K119, 2 царги K119 × 500, межкламповый фильтр K119, переход K119 → ½″*; хомуты усиленные и прокладки PTFE K119 × 5. * в каталоге Гросснера одной деталью нет — под заказ</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -2617,7 +2609,7 @@
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Тройник кламп ½″ T-тип + переходник K25 → вход VP-1 (KF16 или ёлочка — по насосу)</t>
+          <t>Тройник кламп прямой К25 (½″), 3A, AISI 316 + переходник K25 → вход VP-1 (KF16 или ёлочка — по насосу)</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -2642,7 +2634,7 @@
       </c>
       <c r="H55" s="19" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
       <c r="I55" s="19" t="inlineStr">
@@ -3253,17 +3245,17 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>ведомость, лист 8: K25 59 (вкл. 2 воздушных у насосов), K50,5 13, K91 6 (+ 4 на межкламповые), K119 4 (+1); + 2 шт.</t>
+          <t>ведомость, лист 8: K25 59 (вкл. 2 воздушных у насосов), K50,5 16 (вкл. 3 стыка тройник → переход 50,5/25), K91 6 (+ 4 на межкламповые), K119 4 (+ 1); + 2 шт.</t>
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
-          <t>59 / 13 / 10 / 5</t>
+          <t>59 / 16 / 10 / 5</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
         <is>
-          <t>61 / 15 / 12 / 7</t>
+          <t>61 / 18 / 12 / 7</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
@@ -3294,17 +3286,17 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>ведомость: 43 / 13 / 4 (+1), + 2 шт.</t>
+          <t>ведомость: 43 / 16 / 4 (+1), + 2 шт.</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>43 / 13 / 5</t>
+          <t>43 / 16 / 5</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>45 / 15 / 7</t>
+          <t>45 / 18 / 7</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
@@ -3400,70 +3392,68 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3486,7 +3476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3597,7 +3587,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="43.5" customHeight="1">
+    <row r="8" ht="57" customHeight="1">
       <c r="A8" s="15" t="n">
         <v>2</v>
       </c>
@@ -3613,17 +3603,17 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>P1–P4, слив BV-1, отвод 90° под BV-1, линия выгрузки слив → P-2 → тройник 45° 50,5×½″ и переход 50,5/K119 на входе нутча (6)</t>
+          <t>P1–P4, слив BV-1, отвод под BV-1, 2 тройника 50,5 под BV-1 и переходы 50,5→25 на их отводы, выгрузка → P-2 → тройник 50,5 на входе нутча (+ переход 50,5→25 на отвод) и переход 50,5/K119 (ведомость: 16)</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -3703,17 +3693,17 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>P1–P4, слив BV-1, отвод 90° под BV-1, линия выгрузки слив → P-2 → вход нутча (тройник 45° 50,5×½″, переход 50,5/K119)</t>
+          <t>всё на 50,5 (ведомость: 16): P1–P4, слив, тройники под BV-1 и на входе нутча со стыками на переходы 50,5→25, линия выгрузки, переход 50,5/K119</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -3747,923 +3737,923 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="43.5" customHeight="1">
       <c r="A13" s="9" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый (сетка ≤ 1 мм, AISI 316)</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>3″ (91)</t>
+          <t>½″ (25)</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>опора и верх засыпки C-1, C-2</t>
+          <t>генератор G-1: порты (вкл. вход р-ра), PSV-3, V-G1 (щёлочь, водный метиламин) — 7; P-1 → G-1 (3); колонны C-1/C-2, входы и выходы ½″ — 4; воздух насосов P-2, P-4 — 2</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Краны и клапаны</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Кран кламп шаровой, сёдла PTFE</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>½″</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>V-P3 (дозирование), V-G1 (генератор), SP-1 (проба), V-S1 (бочка растворителя), V-F3 (выход фильтра F-2), V-P1 (после P-1), VV-2 (вакуум нутча)</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Клапан обратный кламп пружинный</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>½″</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>NRV-6 — нагнетание P-1 → G-1, после крана V-P1</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="43.5" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Тройник кламп (прямой, равнопроходной), 3A, AISI 316, ≈2 610 ₽</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>всас VP-1: сводит рукава PTFE от VV-1 (гребёнка) и VV-2 (нутч); третий отвод — переходник К25 на вход насоса (KF16 / ёлочка — по VP-1)</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1">
+      <c r="A18" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Кран кламп шаровой, сёдла PTFE</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>½″</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>V-F2 — выход нутча (фильтрат, К25)</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="43.5" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный угловой кламп, 0,3–0,5 бар</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>½″</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>PSV-3 на генераторе (0,3–0,5 бар) и PSV-4 на гребёнке нутча (0,3 бар); выходы → переходник на резьбу (коллектор сбросов — у смежников)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Фасонные детали</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Тройник кламп (прямой, равнопроходной), 3A, AISI 316, ≈2 610 ₽</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>порт регулятора G-1 (PSV-3, аргон A2); манометр PI-3 — на крышке бака</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="43.5" customHeight="1">
+      <c r="A22" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Отвод кламп 90°</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>сразу под краном слива BV-1: выход в горизонталь (от дна реактора до пола мало высоты), дальше тройники SP-1 и V-S1</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="57" customHeight="1">
+      <c r="A23" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Тройник кламп (прямой, равнопроходной), 3A, AISI 316, ≈2 370 ₽</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>под BV-1: 1-й — вниз проба SP-1, 2-й — вбок V-S1 на бочку (на оба отвода — переход 50,5→25), прямо — выгрузка 50,5 на P-2. Переходных тройников 50,5 × 25 у Гросснера нет — равнопроходной + переход</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316, ≈2 300 ₽</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>К50,5 → К25</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>штуцер P3 → V-P3 (1); отводы тройников под BV-1: SP-1 и V-S1 (2); отвод тройника на входе нутча → гребёнка (1)</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="43.5" customHeight="1">
-      <c r="A14" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>½″ (25)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>генератор G-1: порты (вкл. вход р-ра), PSV-3, V-G1 (щёлочь, водный метиламин) — 7; P-1 → G-1 (3); колонны C-1/C-2, входы и выходы ½″ — 4; воздух насосов P-2, P-4 — 2</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
+    <row r="25" ht="16.5" customHeight="1">
+      <c r="A25" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Отвод кламп 90°</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>½″</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>носик пробоотбора после SP-1</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 мм (¼″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>К25 × 6,35</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>выход P-1: силикон PF ¼″ (ID 6,4) из головки насоса → кламп К25 → кран V-P1 (Р11)</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 мм (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>суспензия: силикон TSO 1″ (Р1, Р2) — тройник V-S1, вход и выход P-2, тройник 45° нутча</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 мм (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>все рукава K25: силикон TSO ¾″ — 18 концов</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Краны и клапаны</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="8" t="n"/>
-    </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Кран кламп шаровой, сёдла PTFE</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>DN 1″ (ID 25,4)</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>суспензия: слив → P-2 → нутч (Р1, Р2), на ёлочках К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>5 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="43.5" customHeight="1">
+      <c r="A30" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>DN ¾″ (ID 19)</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>все линии K25 на ёлочках К25 × 19,05: верх E-1, гребёнка нутча, фильтрат, бочка, налив, вакуум, vent, подача метиламина NRV-6 → G-1 (Р3–Р11)</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>≈16,5 м</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>18 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический PF (неармированный)</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>DN ¼″ (ID 6,4)</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>головка перистальтического P-1: V-1 → насос → штуцер К25 × 6,35 (армированный в головке не работает)</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>1 м</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>2 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Хомут червячный нерж.</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>8–12 / 25–40 / 32–50</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>по 2 на конец рукава: силикон PF ¼″ на P-1 (по 1) / силикон TSO ¾″ / силикон TSO 1″</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>2 / 36 / 8</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>4 / 38 / 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба наружная ¼″</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>½″</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>V-P3 (дозирование), V-G1 (генератор), SP-1 (проба), V-S1 (бочка растворителя), V-F3 (выход фильтра F-2), V-P1 (после P-1), VV-2 (вакуум нутча)</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>ввод трубки P-3 на P3 (заглушка с обжимом ¼″, после NRV-4); аргон A2 в тройник G-1</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="43.5" customHeight="1">
+      <c r="A34" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба наружная ½″</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>½″</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>трубка PTFE 10×12 через обжим: после V-G1, вход и выход C-1 и C-2, выходы PSV-3 и PSV-4 (на коллектор сбросов смежников)</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>Клапан обратный кламп пружинный</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>NRV-6 — нагнетание P-1 → G-1, после крана V-P1</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="43.5" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO, DN8, резьба ¼″, ферула 25 мм, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>K25 × G¼″ вн.</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>бак Altmaler G-1: вход р-ра метиламина (сифон) и выход газа — штуцеры наружная G¼″ (замер: Ø≈13,2, шаг 1,337)</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="43.5" customHeight="1">
+      <c r="A36" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба, резьба по баку</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>½″ × G?</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>бак Altmaler G-1: порт регулятора (Ar A2, PSV-3, PI-3) — резьбу замерить; если тоже наружная G¼″ — третий переходник как выше</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F36" s="18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="43.5" customHeight="1">
-      <c r="A18" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Тройник кламп T-тип</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>всас VP-1: сводит рукава PTFE от VV-1 (гребёнка) и VV-2 (нутч); третий отвод — переходник К25 на вход насоса (KF16 / ёлочка — по VP-1)</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
+    <row r="37" ht="70.5" customHeight="1">
+      <c r="A37" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба наружная, ¼″ NPT, кламп К50,5, AISI 316 — под заказ (в каталоге только BSP); не нужен, если берём ниппель + кламп с внутр. резьбой (строки ниже)</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>50,5 × ¼″ NPT нар.</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>запасной вариант для насосов P-2 и P-4</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>0 (4)</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>0 (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="57" customHeight="1">
+      <c r="A38" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, резьба ¼″ (BSP), кламп К50,5, AISI 316 (≈1 455 ₽). Ссылка открывает карточку с уже выбранным вариантом</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>50,5 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>основной: насос P-2 (суспензия), вход и выход — на ниппель ¼″ NPT × ¼″ BSP (строка ниже)</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>Кран кламп шаровой, сёдла PTFE</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>V-F2 — выход нутча (фильтрат, К25)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="57" customHeight="1">
+      <c r="A39" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. — не у Гросснера (у Гросснера ниппели только BSP), RizurLok-NP или аналог; оцинкованные не брать</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>¼″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>основной: насос (¼″ NPT вн.) → ниппель → кламп с внутр. резьбой ¼″ BSP × К50,5</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Сжатый воздух к насосам P-2, P-4 (вход ⅛″ NPT) — та же схема</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41" ht="43.5" customHeight="1">
+      <c r="A41" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, резьба ¼″ (BSP), кламп К25, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>воздух P-2, P-4: по 2 на насос (на ниппель и ответный на цангу) — 4; насос P-4 (фильтрат), вход и выход на ниппель ¼″ NPT × ¼″ BSP — 2</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь — не у Гросснера</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>вход воздуха насоса → кламп ¼″ × К25</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="43.5" customHeight="1">
-      <c r="A20" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Клапан предохранительный угловой кламп, 0,3–0,5 бар</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>PSV-3 на генераторе (0,3–0,5 бар) и PSV-4 на гребёнке нутча (0,3 бар); выходы → переходник на резьбу (коллектор сбросов — у смежников)</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Колонны осушки C-1, C-2</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="8" t="n"/>
+    </row>
+    <row r="44" ht="57" customHeight="1">
+      <c r="A44" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10, ≈3 925 ₽</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>К91 (3″)</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>опора засыпки: низ C-1 и C-2 — на нём лежат сита 3A / NaOH; верх — прижимает засыпку. Ставится в кламп-стык между двумя прокладками EPDM K91 (хомут и прокладка на фильтр — в строках K91 выше)</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1">
+      <c r="A45" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>Царга кламп (труба 76,2×1,6)</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>3″ (DN65) × 400</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>корпуса C-1 (сита 3A) и C-2 (NaOH/KOH), низ</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Фасонные детали</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>Тройник кламп T-тип</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>порт регулятора G-1 (PSV-3, аргон A2); манометр PI-3 — на крышке бака</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F45" s="18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="43.5" customHeight="1">
-      <c r="A23" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>Отвод кламп 90°</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>50,5</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>сразу под краном слива BV-1: выход в горизонталь (от дна реактора до пола мало высоты), дальше тройники SP-1 и V-S1</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Тройник кламп 45° переходной</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>50,5 × ½″</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>1-й после отвода под BV-1: отвод 45° вниз — проба SP-1 (суспензия не застаивается)</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="A25" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>Тройник кламп переходной</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>50,5 × ½″</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>2-й: вбок V-S1 на бочку, прямо — выгрузка 50,5 на P-2</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Переход кламп–кламп концентрический</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>50,5 → ½″</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>штуцер P3 → кран V-P3</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="A27" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Отвод кламп 90°</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>носик пробоотбора после SP-1</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 6,35 мм (¼″), AISI 316</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>К25 × 6,35</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>выход P-1: силикон PF ¼″ (ID 6,4) из головки насоса → кламп К25 → кран V-P1 (Р11)</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 мм (1″), AISI 316</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>К50,5 × 25,4</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>суспензия: силикон TSO 1″ (Р1, Р2) — тройник V-S1, вход и выход P-2, тройник 45° нутча</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 мм (¾″), AISI 316</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>К25 × 19,05</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>все рукава K25: силикон TSO ¾″ — 18 концов</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>DN 1″ (ID 25,4)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>суспензия: слив → P-2 → нутч (Р1, Р2), на ёлочках К50,5 × 25,4</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>4 м</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="43.5" customHeight="1">
-      <c r="A32" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>DN ¾″ (ID 19)</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>все линии K25 на ёлочках К25 × 19,05: верх E-1, гребёнка нутча, фильтрат, бочка, налив, вакуум, vent, подача метиламина NRV-6 → G-1 (Р3–Р11)</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>≈16,5 м</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>18 м</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>DN ¼″ (ID 6,4)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>головка перистальтического P-1: V-1 → насос → штуцер К25 × 6,35 (армированный в головке не работает)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>1 м</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>2 м</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Хомут червячный нерж.</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>8–12 / 25–40 / 32–50</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>по 2 на конец рукава: силикон PF ¼″ на P-1 (по 1) / силикон TSO ¾″ / силикон TSO 1″</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>2 / 36 / 8</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>4 / 38 / 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба наружная ¼″</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>ввод трубки P-3 на P3 (заглушка с обжимом ¼″, после NRV-4); аргон A2 в тройник G-1</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="43.5" customHeight="1">
-      <c r="A36" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба наружная ½″</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>трубка PTFE 10×12 через обжим: после V-G1, вход и выход C-1 и C-2, выходы PSV-3 и PSV-4 (на коллектор сбросов смежников)</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="43.5" customHeight="1">
-      <c r="A37" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO, DN8, резьба ¼″, ферула 25 мм, AISI 316 (≈1 455 ₽)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>K25 × G¼″ вн.</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>бак Altmaler G-1: вход р-ра метиламина (сифон) и выход газа — штуцеры наружная G¼″ (замер: Ø≈13,2, шаг 1,337)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="43.5" customHeight="1">
-      <c r="A38" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба, резьба по баку</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>½″ × G?</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>бак Altmaler G-1: порт регулятора (Ar A2, PSV-3, PI-3) — резьбу замерить; если тоже наружная G¼″ — третий переходник как выше</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="70.5" customHeight="1">
-      <c r="A39" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба наружная, ¼″ NPT, кламп К50,5, AISI 316 — под заказ (в каталоге только BSP); не нужен, если берём ниппель + кламп с внутр. резьбой (строки ниже)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>50,5 × ¼″ NPT нар.</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>запасной вариант для насосов P-2 и P-4</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>0 (4)</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>0 (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="57" customHeight="1">
-      <c r="A40" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, резьба ¼″ (BSP), кламп К50,5, AISI 316 (≈1 455 ₽). Ссылка открывает карточку с уже выбранным вариантом</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>50,5 × ¼″ BSP вн.</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>основной: насос P-2 (суспензия), вход и выход — на ниппель ¼″ NPT × ¼″ BSP (строка ниже)</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="57" customHeight="1">
-      <c r="A41" s="15" t="n">
-        <v>33</v>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. — не у Гросснера (у Гросснера ниппели только BSP), RizurLok-NP или аналог; оцинкованные не брать</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>¼″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>основной: насос (¼″ NPT вн.) → ниппель → кламп с внутр. резьбой ¼″ BSP × К50,5</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F41" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Сжатый воздух к насосам P-2, P-4 (вход ⅛″ NPT) — та же схема</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="43.5" customHeight="1">
-      <c r="A43" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, резьба ¼″ (BSP), кламп К25, AISI 316 (≈1 455 ₽)</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>К25 × ¼″ BSP вн.</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>воздух P-2, P-4: по 2 на насос (на ниппель и ответный на цангу) — 4; насос P-4 (фильтрат), вход и выход на ниппель ¼″ NPT × ¼″ BSP — 2</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь — не у Гросснера</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>вход воздуха насоса → кламп ¼″ × К25</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Колонны осушки C-1, C-2</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="8" t="n"/>
     </row>
     <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="9" t="n">
@@ -4671,17 +4661,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2×1,6)</t>
+          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>3″ (DN65) × 400</t>
+          <t>3″ (91), L ≈ 200</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>корпуса C-1 (сита 3A) и C-2 (NaOH/KOH), низ</t>
+          <t>верх C-1 и C-2 — видно засыпку и фронт влаги</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -4695,550 +4685,520 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1">
+    <row r="47" ht="57" customHeight="1">
       <c r="A47" s="15" t="n">
         <v>37</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
+          <t>Переход кламп концентрический (или заглушка с отводом)</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>К91 → К25 (3″ → ½″)</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>низ и верх каждой колонны; в каталоге Гросснера одной деталью нет (переходы 3″ — от 91 × 50,5, 4″ — от 119 × 64): заказать изготовление у Гросснера или собрать из двух-трёх переходов</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Нутч F-1 — сборка K119 (4″) на клампах, пробный вариант без сверления</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="43.5" customHeight="1">
+      <c r="A49" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Тройник кламп (прямой, равнопроходной), 3A, AISI 316, ≈2 370 ₽</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>вход нутча: прямо — суспензия 50,5 (рукав от P-2), вбок через переход 50,5→25 (в строке «Переход 1″ × ½″» выше) — гребёнка газов</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>Тройник кламп (прямой, равнопроходной), 3A, AISI 316, ≈2 610 ₽</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Мановакуумметр 63 мм с мембранным разделителем кламп</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>½″ (К25), −1…+0,6 бар</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>PI-5 — гребёнка нутча, на отвод тройника</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>Хомут-держатель для труб нерж.</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>по Ø: ½″, 3″, K119</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>крепление колонн C-1/C-2, гребёнки реактора и гребёнки нутча к раме/стойкам — по месту</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба наружная ¼″</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>½″ → ¼″</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>конец гребёнки нутча → V-F1 (аргон A4); PI-5, PSV-4 и VV-2 — на кламп прямо на тройники</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="57" customHeight="1">
+      <c r="A54" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>Переход кламп концентрический</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>К50,5 → K119</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>крышка нутча (позже — заглушка K119 со штуцерами); в каталоге Гросснера одной деталью нет (переходы 3″ — от 91 × 50,5, 4″ — от 119 × 64): заказать изготовление у Гросснера или собрать из двух-трёх переходов</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16.5" customHeight="1">
+      <c r="A55" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
           <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>3″ (91), L ≈ 200</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>верх C-1 и C-2 — видно засыпку и фронт влаги</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>K119 (4″)</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>видно уровень суспензии</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" ht="43.5" customHeight="1">
+      <c r="A56" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>Царга кламп</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>K119 (4″) × 500, AISI 316L (≈6 150 ₽)</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>корпус нутча: 2 царги подряд через кламп K119 — 7,4 л, весь осадок партии</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F47" s="18" t="inlineStr">
+      <c r="F56" s="18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>Переход кламп–кламп концентрический (или заглушка с отводом)</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>3″ → ½″</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>низ и верх каждой колонны</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
+    <row r="57" ht="43.5" customHeight="1">
+      <c r="A57" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10, ≈5 655 ₽</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>K119 (4″)</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>опора слоя (ткань PTFE/PP + Na₂SO₄). Если K119 сняли — прокладка с сеткой K119 + перфорированный диск</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="57" customHeight="1">
+      <c r="A58" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>Переход кламп концентрический</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>K119 → К25</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>низ нутча → V-F2 (фильтрат — К25); в каталоге Гросснера одной деталью нет (переходы 3″ — от 91 × 50,5, 4″ — от 119 × 64): заказать изготовление у Гросснера или собрать из двух-трёх переходов</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="43.5" customHeight="1">
+      <c r="A59" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Хомут кламп усиленный (болтовой), AISI 304, ≈2 770 ₽</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>K119</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>нутч: 4 стыка (вкл. царга → царга) + 1 на межкламповый фильтр; с прокладками PTFE Гросснер рекомендует усиленные болтовые хомуты</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Нутч F-1 — сборка K119 (4″) на клампах, пробный вариант без сверления</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="8" t="n"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>Тройник кламп 45° переходной</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>50,5 × ½″</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>вход нутча: прямо — суспензия 50,5 (рукав от P-2), вбок ½″ — гребёнка газов</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16.5" customHeight="1">
+      <c r="A60" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>K119</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>4 стыка (вкл. царга → царга) + 1 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Под заказ и фильтр F-2</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="8" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>кламп по корпусу</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>F-2, тонкая фильтрация продукта</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16.5" customHeight="1">
-      <c r="A51" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>Тройник кламп T-тип</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>½″</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F51" s="18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>Мановакуумметр 63 мм с мембранным разделителем кламп</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>½″ (К25), −1…+0,6 бар</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>PI-5 — гребёнка нутча, на отвод тройника</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="15" t="n">
-        <v>42</v>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>Хомут-держатель для труб нерж.</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>по Ø: ½″, 3″, K119</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>крепление колонн C-1/C-2, гребёнки реактора и гребёнки нутча к раме/стойкам — по месту</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм, PTFE или PP/PES</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>F-2, по 2 шт. каждого</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Кольца уплотнительные в оболочке FEP (FEP/силикон) — вместо штатных силикон/EPDM</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>под корпус 10″ и посадку патрона</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>F-2: кольцо крышки корпуса + кольца патронов (продукт — углеводород, EPDM не стоек)</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="F53" s="18" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба наружная ¼″</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>½″ → ¼″</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>конец гребёнки нутча → V-F1 (аргон A4); PI-5, PSV-4 и VV-2 — на кламп прямо на тройники</t>
-        </is>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16.5" customHeight="1">
-      <c r="A55" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t>Переход кламп концентрический</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>50,5 → K119</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>крышка нутча (позже — заглушка K119 со штуцерами)</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F55" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16.5" customHeight="1">
-      <c r="A56" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>K119 (4″)</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>видно уровень суспензии</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" ht="43.5" customHeight="1">
-      <c r="A57" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>Царга кламп</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>K119 (4″) × 500, AISI 316L (≈6 150 ₽)</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>корпус нутча: 2 царги подряд через кламп K119 — 7,4 л, весь осадок партии</t>
-        </is>
-      </c>
-      <c r="E57" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F57" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>Фильтр межкламповый</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>K119 (4″)</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>опора слоя (ткань PTFE/PP + Na₂SO₄). Если K119 сняли — прокладка с сеткой K119 + перфорированный диск</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16.5" customHeight="1">
-      <c r="A59" s="15" t="n">
-        <v>48</v>
-      </c>
-      <c r="B59" s="19" t="inlineStr">
-        <is>
-          <t>Переход кламп концентрический</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>K119 → ½″</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>низ нутча → V-F2 (фильтрат — К25)</t>
-        </is>
-      </c>
-      <c r="E59" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F59" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="43.5" customHeight="1">
-      <c r="A60" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>Хомут кламп усиленный (болтовой), AISI 304, ≈2 770 ₽</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>K119</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>нутч: 4 стыка (вкл. царга → царга) + 1 на межкламповый фильтр; с прокладками PTFE Гросснер рекомендует усиленные болтовые хомуты</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16.5" customHeight="1">
-      <c r="A61" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>K119</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>4 стыка (вкл. царга → царга) + 1 на межкламповый фильтр</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F61" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Под заказ и фильтр F-2</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="8" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="9" t="n">
-        <v>51</v>
-      </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>кламп по корпусу</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>F-2, тонкая фильтрация продукта</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="15" t="n">
-        <v>52</v>
-      </c>
-      <c r="B64" s="19" t="inlineStr">
-        <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм, PTFE или PP/PES</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>10″</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>F-2, по 2 шт. каждого</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>Кольца уплотнительные в оболочке FEP (FEP/силикон) — вместо штатных силикон/EPDM</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>под корпус 10″ и посадку патрона</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>F-2: кольцо крышки корпуса + кольца патронов (продукт — углеводород, EPDM не стоек)</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>2 компл.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F65"/>
+  <autoFilter ref="A4:F64"/>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
@@ -5248,12 +5208,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId16"/>
@@ -5272,13 +5232,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId41"/>
@@ -5290,10 +5250,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5884,7 +5843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7146,7 +7105,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>отвод 90° 50,5 → тройник 45° 50,5×½″</t>
+          <t>отвод 90° 50,5 → тройник 50,5 (SP-1)</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -7171,12 +7130,12 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>тройник 45° 50,5×½″ → кран SP-1</t>
+          <t>тройник 50,5 (SP-1) → переход 50,5/25</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>K25</t>
+          <t>K50,5 (1″)</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
@@ -7196,7 +7155,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>SP-1 → носик пробоотборника</t>
+          <t>переход 50,5/25 → кран SP-1</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -7221,12 +7180,12 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>тройник → тройник переходной 50,5×½″ (выгрузка / бочка)</t>
+          <t>SP-1 → носик пробоотборника</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>K50,5 (1″)</t>
+          <t>K25</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
@@ -7246,12 +7205,12 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>тройник → кран V-S1</t>
+          <t>тройник SP-1 → тройник V-S1 (50,5)</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>K25</t>
+          <t>K50,5 (1″)</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -7271,12 +7230,12 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>V-S1 → рукав от бочки растворителя</t>
+          <t>тройник 50,5 (V-S1) → переход 50,5/25</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>K25</t>
+          <t>K50,5 (1″)</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr">
@@ -7296,12 +7255,12 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>тройник → штуцер K50,5×25,4 (рукав на P-2)</t>
+          <t>переход 50,5/25 → кран V-S1</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>K50,5 (1″)</t>
+          <t>K25</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -7321,12 +7280,12 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>рукав → переходник 50,5/¼″NPT на P-2 (вход)</t>
+          <t>V-S1 → рукав от бочки растворителя</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>K50,5 (1″)</t>
+          <t>K25</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
@@ -7346,17 +7305,17 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>P-2 воздух: ниппель ⅛″NPT/¼″ + кламп ¼″×К25 → линия воздуха</t>
+          <t>тройник → штуцер K50,5×25,4 (рукав на P-2)</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>K25</t>
+          <t>K50,5 (1″)</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>EPDM</t>
+          <t>PTFE</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7330,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>P-2 выход (переходник ¼″NPT/50,5) → рукав</t>
+          <t>рукав → переходник 50,5/¼″NPT на P-2 (вход)</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
@@ -7396,17 +7355,17 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>рукав → вход нутча F-1</t>
+          <t>P-2 воздух: ниппель ⅛″NPT/¼″ + кламп ¼″×К25 → линия воздуха</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>K50,5 (1″)</t>
+          <t>K25</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>PTFE</t>
+          <t>EPDM</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7380,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>тройник 45° 50,5×½″ → переход 50,5/K119 (крышка нутча)</t>
+          <t>P-2 выход (переходник ¼″NPT/50,5) → рукав</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
@@ -7446,12 +7405,12 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>переход 50,5/K119 → диоптр</t>
+          <t>рукав → вход нутча F-1</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>K119 (4″)</t>
+          <t>K50,5 (1″)</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -7471,12 +7430,12 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>диоптр → царга K119</t>
+          <t>тройник 50,5 (вход нутча) → переход 50,5/K119 (крышка нутча)</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>K119 (4″)</t>
+          <t>K50,5 (1″)</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr">
@@ -7496,7 +7455,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>царга K119 → царга K119</t>
+          <t>переход 50,5/K119 → диоптр</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -7521,7 +7480,7 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>царга → межкламповый фильтр K119 → переход K119/½″</t>
+          <t>диоптр → царга K119</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -7546,12 +7505,12 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>тройник 45° → рукав на гребёнку нутча</t>
+          <t>царга K119 → царга K119</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>K25</t>
+          <t>K119 (4″)</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
@@ -7571,12 +7530,12 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>рукав → гребёнка нутча (на раме)</t>
+          <t>царга → межкламповый фильтр K119 → переход K119/½″</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>K25</t>
+          <t>K119 (4″)</t>
         </is>
       </c>
       <c r="E70" s="16" t="inlineStr">
@@ -7596,12 +7555,12 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>гребёнка нутча: тройник → PI-5 (мембранный разделитель, кламп)</t>
+          <t>тройник 50,5 (вход нутча) → переход 50,5/25</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>K25</t>
+          <t>K50,5 (1″)</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
@@ -7621,7 +7580,7 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>гребёнка нутча: PI-5 → PSV-4</t>
+          <t>переход 50,5/25 → рукав на гребёнку нутча</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -7646,7 +7605,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>гребёнка нутча: тройник → PSV-4 (угловой, кламп)</t>
+          <t>рукав → гребёнка нутча (на раме)</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -7671,7 +7630,7 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>PSV-4 выход → переходник ½″/G½″ (сброс в коллектор сбросов)</t>
+          <t>гребёнка нутча: тройник → PI-5 (мембранный разделитель, кламп)</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -7696,7 +7655,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>гребёнка нутча: PSV-4 → VV-2</t>
+          <t>гребёнка нутча: PI-5 → PSV-4</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -7721,7 +7680,7 @@
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>тройник → кран VV-2</t>
+          <t>гребёнка нутча: тройник → PSV-4 (угловой, кламп)</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -7746,7 +7705,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>VV-2 → штуцер K25×19,05 (рукав на VP-1)</t>
+          <t>PSV-4 выход → переходник ½″/G½″ (сброс в коллектор сбросов)</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -7771,7 +7730,7 @@
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>гребёнка нутча: VV-2 → кран V-F1 (аргон A4)</t>
+          <t>гребёнка нутча: PSV-4 → VV-2</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -7796,7 +7755,7 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>выход нутча → кран V-F2</t>
+          <t>тройник → кран VV-2</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -7821,7 +7780,7 @@
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>V-F2 → рукав на P-4</t>
+          <t>VV-2 → штуцер K25×19,05 (рукав на VP-1)</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -7846,7 +7805,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>рукав → P-4 (вход)</t>
+          <t>гребёнка нутча: VV-2 → кран V-F1 (аргон A4)</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -7871,7 +7830,7 @@
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>P-4 воздух: ниппель ⅛″NPT/¼″ + кламп ¼″×К25 → линия воздуха</t>
+          <t>выход нутча → кран V-F2</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -7881,7 +7840,7 @@
       </c>
       <c r="E82" s="16" t="inlineStr">
         <is>
-          <t>EPDM</t>
+          <t>PTFE</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7855,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>P-4 выход → рукав на F-2</t>
+          <t>V-F2 → рукав на P-4</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -7921,7 +7880,7 @@
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>рукав → вход F-2</t>
+          <t>рукав → P-4 (вход)</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -7946,7 +7905,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>выход F-2 → кран V-F3</t>
+          <t>P-4 воздух: ниппель ⅛″NPT/¼″ + кламп ¼″×К25 → линия воздуха</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -7956,7 +7915,7 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>PTFE</t>
+          <t>EPDM</t>
         </is>
       </c>
     </row>
@@ -7971,22 +7930,97 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
+          <t>P-4 выход → рукав на F-2</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>K25</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16.5" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>рукав → вход F-2</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>K25</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16.5" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>выход F-2 → кран V-F3</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>K25</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16.5" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
           <t>V-F3 → рукав на налив</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>K25</t>
         </is>
       </c>
-      <c r="E86" s="16" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr">
         <is>
           <t>PTFE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E86"/>
+  <autoFilter ref="A4:E89"/>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Смета" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$J$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$J$114</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Смета'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4695,12 +4695,12 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
@@ -4715,34 +4715,34 @@
       </c>
       <c r="J102" s="9" t="n"/>
     </row>
-    <row r="103" ht="30" customHeight="1">
+    <row r="103" ht="43.5" customHeight="1">
       <c r="A103" s="13" t="n">
         <v>90</v>
       </c>
       <c r="B103" s="14" t="n"/>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E103" s="15" t="inlineStr">
         <is>
-          <t>нутч: стыки переходов</t>
+          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
         </is>
       </c>
       <c r="F103" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G103" s="16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
       <c r="J103" s="15" t="n"/>
@@ -4769,22 +4769,22 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
+          <t>нутч: стыки переходов</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -4806,27 +4806,27 @@
       <c r="B105" s="14" t="n"/>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E105" s="15" t="inlineStr">
         <is>
-          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2)</t>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
         </is>
       </c>
       <c r="F105" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G105" s="16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="I105" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="J105" s="15" t="n"/>
@@ -4853,22 +4853,22 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>колонны: стыки переходов 3″/1″ → 1″/½″</t>
+          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2)</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
@@ -4883,295 +4883,338 @@
       </c>
       <c r="J106" s="9" t="n"/>
     </row>
-    <row r="107" ht="30" customHeight="1">
+    <row r="107" ht="70.5" customHeight="1">
       <c r="A107" s="13" t="n">
         <v>94</v>
       </c>
       <c r="B107" s="14" t="n"/>
       <c r="C107" s="15" t="inlineStr">
         <is>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
+        </is>
+      </c>
+      <c r="F107" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I107" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+        </is>
+      </c>
+      <c r="J107" s="15" t="n"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
           <t>Прокладка кламп EPDM</t>
         </is>
       </c>
-      <c r="D107" s="14" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>К91 (3″)</t>
         </is>
       </c>
-      <c r="E107" s="15" t="inlineStr">
+      <c r="E108" s="9" t="inlineStr">
         <is>
           <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
         </is>
       </c>
-      <c r="F107" s="14" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G107" s="16" t="inlineStr">
+      <c r="G108" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H107" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I107" s="17" t="inlineStr">
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I108" s="12" t="inlineStr">
         <is>
           <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
-      <c r="J107" s="15" t="n"/>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="J108" s="9" t="n"/>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="5" t="n"/>
-      <c r="D108" s="5" t="n"/>
-      <c r="E108" s="5" t="n"/>
-      <c r="F108" s="5" t="n"/>
-      <c r="G108" s="5" t="n"/>
-      <c r="H108" s="5" t="n"/>
-      <c r="I108" s="5" t="n"/>
-      <c r="J108" s="6" t="n"/>
-    </row>
-    <row r="109" ht="57" customHeight="1">
-      <c r="A109" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="B109" s="8" t="n"/>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="5" t="n"/>
+      <c r="I109" s="5" t="n"/>
+      <c r="J109" s="6" t="n"/>
+    </row>
+    <row r="110" ht="57" customHeight="1">
+      <c r="A110" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="9" t="inlineStr">
         <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D110" s="8" t="inlineStr">
         <is>
           <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
-      <c r="E109" s="9" t="inlineStr">
+      <c r="E110" s="9" t="inlineStr">
         <is>
           <t>все линии K25 на ёлочках K25 × 19,05: верх E-1 → гребёнка, гребёнка нутча, V-F2 → P-4, P-4 → F-2, бочка → V-S1, F-2 → канистра, вакуум, vent, NRV-6 → G-1; хомуты 25–40</t>
         </is>
       </c>
-      <c r="F109" s="8" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>≈16,5 м</t>
         </is>
       </c>
-      <c r="G109" s="10" t="inlineStr">
+      <c r="G110" s="10" t="inlineStr">
         <is>
           <t>18 м</t>
         </is>
       </c>
-      <c r="H109" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I109" s="12" t="inlineStr">
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
-      <c r="J109" s="9" t="n"/>
-    </row>
-    <row r="110" ht="30" customHeight="1">
-      <c r="A110" s="13" t="n">
-        <v>96</v>
-      </c>
-      <c r="B110" s="14" t="n"/>
-      <c r="C110" s="15" t="inlineStr">
+      <c r="J110" s="9" t="n"/>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="B111" s="14" t="n"/>
+      <c r="C111" s="15" t="inlineStr">
         <is>
           <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
-      <c r="D110" s="14" t="inlineStr">
+      <c r="D111" s="14" t="inlineStr">
         <is>
           <t>К25 × 19,05</t>
         </is>
       </c>
-      <c r="E110" s="15" t="inlineStr">
+      <c r="E111" s="15" t="inlineStr">
         <is>
           <t>концы рукавов ¾″ (18)</t>
         </is>
       </c>
-      <c r="F110" s="14" t="inlineStr">
+      <c r="F111" s="14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G110" s="16" t="inlineStr">
+      <c r="G111" s="16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H110" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
-      <c r="J110" s="15" t="n"/>
-    </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="B111" s="8" t="n"/>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="J111" s="15" t="n"/>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="9" t="inlineStr">
         <is>
           <t>Хомут червячный нерж.</t>
         </is>
       </c>
-      <c r="D111" s="8" t="inlineStr">
+      <c r="D112" s="8" t="inlineStr">
         <is>
           <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="E112" s="9" t="inlineStr">
         <is>
           <t>по 2 на конец рукава: PF ¼″ на P-1 (по 1) / TSO ¾″ / TSO 1″</t>
         </is>
       </c>
-      <c r="F111" s="8" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>2 / 36 / 8</t>
         </is>
       </c>
-      <c r="G111" s="10" t="inlineStr">
+      <c r="G112" s="10" t="inlineStr">
         <is>
           <t>4 / 38 / 10</t>
         </is>
       </c>
-      <c r="H111" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I111" s="12" t="inlineStr">
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
         <is>
           <t>Гросснер: хомут червячный</t>
         </is>
       </c>
-      <c r="J111" s="9" t="n"/>
-    </row>
-    <row r="112" ht="43.5" customHeight="1">
-      <c r="A112" s="13" t="n">
-        <v>98</v>
-      </c>
-      <c r="B112" s="14" t="n"/>
-      <c r="C112" s="15" t="inlineStr">
+      <c r="J112" s="9" t="n"/>
+    </row>
+    <row r="113" ht="43.5" customHeight="1">
+      <c r="A113" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="B113" s="14" t="n"/>
+      <c r="C113" s="15" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="D112" s="14" t="inlineStr">
+      <c r="D113" s="14" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="E112" s="15" t="inlineStr">
+      <c r="E113" s="15" t="inlineStr">
         <is>
           <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
         </is>
       </c>
-      <c r="F112" s="14" t="inlineStr">
+      <c r="F113" s="14" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="G112" s="16" t="inlineStr">
+      <c r="G113" s="16" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="H112" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
-      <c r="J112" s="17" t="inlineStr">
+      <c r="J113" s="17" t="inlineStr">
         <is>
           <t>fluid-line.ru</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="30" customHeight="1">
-      <c r="A113" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="9" t="inlineStr">
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="9" t="inlineStr">
         <is>
           <t>Шина и кабели заземления с зажимами-крокодилами</t>
         </is>
       </c>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="9" t="inlineStr">
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="9" t="inlineStr">
         <is>
           <t>заземление R-1, P-2, F-1, F-2, канистр (5–6 точек)</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="G113" s="10" t="inlineStr">
+      <c r="G114" s="10" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="H113" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I113" s="12" t="inlineStr">
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I114" s="12" t="inlineStr">
         <is>
           <t>ПромНагрев: заземление бочек</t>
         </is>
       </c>
-      <c r="J113" s="9" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>Позиций: 99</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="28" customHeight="1">
-      <c r="A116" s="21" t="inlineStr">
+      <c r="J114" s="9" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>Позиций: 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="21" t="inlineStr">
         <is>
           <t>Статус: КУПИТЬ — заказывать; УТОЧНИТЬ — сначала замер / уточнение у поставщика; W-2 — использовать весы W-2. Ссылки кликабельны и по возможности открывают карточку сразу с нужным вариантом (размер, AISI 316).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J113"/>
+  <autoFilter ref="A4:J114"/>
   <mergeCells count="12">
-    <mergeCell ref="A116:J116"/>
     <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A117:J117"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A109:J109"/>
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A87:J87"/>
     <mergeCell ref="A48:J48"/>
@@ -5179,7 +5222,6 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A60:J60"/>
     <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A108:J108"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
@@ -5285,12 +5327,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -2575,7 +2575,7 @@
       </c>
       <c r="J49" s="9" t="n"/>
     </row>
-    <row r="50" ht="57" customHeight="1">
+    <row r="50" ht="43.5" customHeight="1">
       <c r="A50" s="13" t="n">
         <v>42</v>
       </c>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>1-й — вниз проба SP-1, 2-й — вбок V-S1 на бочку, прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет); запас на все 3 — здесь</t>
+          <t>1-й — вниз проба SP-1, 2-й — вбок V-S1 на бочку, прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -3019,14 +3019,14 @@
       <c r="I60" s="5" t="n"/>
       <c r="J60" s="6" t="n"/>
     </row>
-    <row r="61" ht="30" customHeight="1">
+    <row r="61" ht="43.5" customHeight="1">
       <c r="A61" s="7" t="n">
         <v>52</v>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>вход нутча: прямо — суспензия, вбок — гребёнка газов</t>
+          <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
       <c r="J61" s="9" t="n"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Смета" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$J$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$J$115</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Смета'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2575,14 +2575,14 @@
       </c>
       <c r="J49" s="9" t="n"/>
     </row>
-    <row r="50" ht="43.5" customHeight="1">
+    <row r="50" ht="57" customHeight="1">
       <c r="A50" s="13" t="n">
         <v>42</v>
       </c>
       <c r="B50" s="14" t="n"/>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
@@ -2592,19 +2592,19 @@
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>1-й — вниз проба SP-1, 2-й — вбок V-S1 на бочку, прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
+          <t>1-й после отвода под BV-1: отвод 45° вниз — проба SP-1 (через переход 50,5 → 25), суспензия не застаивается; запас на оба тройника 45° — здесь</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -2612,41 +2612,41 @@
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
       <c r="J50" s="15" t="n"/>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="43.5" customHeight="1">
       <c r="A51" s="7" t="n">
         <v>43</v>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>отводы тройников → SP-1 и V-S1</t>
+          <t>2-й: вбок V-S1 на бочку (через переход 50,5 → 25), прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
       <c r="J51" s="9" t="n"/>
@@ -2663,24 +2663,20 @@
       <c r="A52" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>SP-1, V-S1</t>
-        </is>
-      </c>
+      <c r="B52" s="14" t="n"/>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>SP-1 — проба, V-S1 — бочка растворителя</t>
+          <t>отводы тройников → SP-1 и V-S1</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -2700,19 +2696,23 @@
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
       <c r="J52" s="15" t="n"/>
     </row>
-    <row r="53" ht="16.5" customHeight="1">
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>SP-1, V-S1</t>
+        </is>
+      </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>носик пробоотбора после SP-1</t>
+          <t>SP-1 — проба, V-S1 — бочка растворителя</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -2742,29 +2742,29 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J53" s="9" t="n"/>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" ht="16.5" customHeight="1">
       <c r="A54" s="13" t="n">
         <v>46</v>
       </c>
       <c r="B54" s="14" t="n"/>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Крышка-переходник на бочку растворителя → кламп K25 (под штуцер K25 × 19,05)</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>по горловине</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>горловину бочки замерить</t>
+          <t>носик пробоотбора после SP-1</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -2774,43 +2774,39 @@
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H54" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>Germeon: крышка DURAN GL45, 2 порта</t>
-        </is>
-      </c>
-      <c r="J54" s="17" t="inlineStr">
-        <is>
-          <t>wiegand.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="43.5" customHeight="1">
+          <t>Гросснер: отвод кламп</t>
+        </is>
+      </c>
+      <c r="J54" s="15" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>P-2</t>
-        </is>
-      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="n"/>
+          <t>Крышка-переходник на бочку растворителя → кламп K25 (под штуцер K25 × 19,05)</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>по горловине</t>
+        </is>
+      </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>выгрузка суспензии на нутч</t>
+          <t>горловину бочки замерить</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -2823,46 +2819,50 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="n"/>
+          <t>Germeon: крышка DURAN GL45, 2 порта</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>wiegand.ru</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="43.5" customHeight="1">
       <c r="A56" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="B56" s="14" t="n"/>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>P-2</t>
+        </is>
+      </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>¼″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="n"/>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
+          <t>выгрузка суспензии на нутч</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -2872,39 +2872,39 @@
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>Rizur: ниппель RizurLok-NP</t>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
       <c r="J56" s="15" t="n"/>
     </row>
-    <row r="57" ht="30" customHeight="1">
+    <row r="57" ht="43.5" customHeight="1">
       <c r="A57" s="7" t="n">
         <v>49</v>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>P-2: вход и выход → рукав 1″</t>
+          <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
       <c r="J57" s="9" t="n"/>
@@ -2926,27 +2926,27 @@
       <c r="B58" s="14" t="n"/>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
+          <t>P-2: вход и выход → рукав 1″</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -2956,2272 +2956,2314 @@
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
       <c r="J58" s="15" t="n"/>
     </row>
-    <row r="59" ht="43.5" customHeight="1">
+    <row r="59" ht="30" customHeight="1">
       <c r="A59" s="7" t="n">
         <v>51</v>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="9" t="inlineStr">
         <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="43.5" customHeight="1">
+      <c r="A60" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="14" t="n"/>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
         <is>
           <t>слив → P-2 (1,5 м), P-2 → нутч (2,5 м); хомуты 32–50; армирование — чтобы не сплющивался на всасе</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="G60" s="16" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I59" s="12" t="inlineStr">
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
-      <c r="J59" s="9" t="n"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="J60" s="15" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="6" t="n"/>
-    </row>
-    <row r="61" ht="43.5" customHeight="1">
-      <c r="A61" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="6" t="n"/>
+    </row>
+    <row r="62" ht="43.5" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="B63" s="14" t="n"/>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 → К25</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H61" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I61" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="13" t="n">
-        <v>53</v>
-      </c>
-      <c r="B62" s="14" t="n"/>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
-        </is>
-      </c>
-      <c r="D62" s="14" t="inlineStr">
-        <is>
-          <t>К50,5 → К25</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
-        </is>
-      </c>
-      <c r="F62" s="14" t="inlineStr">
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
+        </is>
+      </c>
+      <c r="J63" s="15" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>К64 → К50,5</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>крышка нутча и низ нутча</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
-        </is>
-      </c>
-      <c r="J62" s="15" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>К64 → К50,5</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>крышка нутча и низ нутча</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: переход 64 × 50,5 316</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B65" s="14" t="n"/>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>К119 → К64</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="G65" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I63" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="13" t="n">
-        <v>55</v>
-      </c>
-      <c r="B64" s="14" t="n"/>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>К119 → К64</t>
-        </is>
-      </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: переход 119 × 64 316</t>
+        </is>
+      </c>
+      <c r="J65" s="15" t="n"/>
+    </row>
+    <row r="66" ht="16.5" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>видно уровень суспензии</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: диоптр кламп</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>F-1</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>К119 (4″) × 500</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: царга кламп</t>
+        </is>
+      </c>
+      <c r="J67" s="15" t="n"/>
+    </row>
+    <row r="68" ht="43.5" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B69" s="14" t="n"/>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I64" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: переход 119 × 64 316</t>
-        </is>
-      </c>
-      <c r="J64" s="15" t="n"/>
-    </row>
-    <row r="65" ht="16.5" customHeight="1">
-      <c r="A65" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: тройник кламп ½″ 316</t>
+        </is>
+      </c>
+      <c r="J69" s="15" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>PI-5</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>на отвод тройника гребёнки</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>PSV-4</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>на тройник гребёнки; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: предохр. клапан угловой кламп</t>
+        </is>
+      </c>
+      <c r="J71" s="15" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>К25 × ½″</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>выход PSV-4 → граница с коллектором сбросов смежников</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба наружная</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>VV-2</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>вакуум нутча</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кран кламп</t>
+        </is>
+      </c>
+      <c r="J73" s="15" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>К25 × ¼″</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба наружная</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>V-F2</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>выход нутча (фильтрат)</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кран кламп</t>
+        </is>
+      </c>
+      <c r="J75" s="15" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Хомут-держатель для труб нерж.</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>по Ø: ½″, 3″, K119</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут-держатель</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Вакуум VP-1</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="6" t="n"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>VP-1</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>всас VP-1: сводит рукава от VV-1 (гребёнка реактора) и VV-2 (нутч)</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: тройник кламп ½″ 316</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>VP-1</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>Переходник K25 → вход VP-1 (KF16 или ёлочка — по насосу)</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>К25 × KF16?</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>вход насоса — уточнить</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G79" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: вакуумный фланец KF</t>
+        </is>
+      </c>
+      <c r="J79" s="15" t="n"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="6" t="n"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>P-4</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>фильтрат нутча → F-2</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B82" s="14" t="n"/>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+      <c r="J82" s="15" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>F-2</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: корпус 10″</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="B84" s="14" t="n"/>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>по 2 шт. каждого рейтинга</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: патроны</t>
+        </is>
+      </c>
+      <c r="J84" s="15" t="n"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>под корпус 10″</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>Hydrohype: кольца в оболочке FEP</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>V-F3</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>выход F-2 → налив</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кран кламп</t>
+        </is>
+      </c>
+      <c r="J86" s="15" t="n"/>
+    </row>
+    <row r="87" ht="16.5" customHeight="1">
+      <c r="A87" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>W-3</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Весы 60 кг, дискр. 10 г</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>фасовка в канистры — можно весами W-2</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="19" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="I87" s="12" t="inlineStr">
+        <is>
+          <t>Аналитпром: ВПС-60</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Сжатый воздух к насосам P-2, P-4</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="6" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>вход воздуха насоса (по 1 на насос)</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="B90" s="14" t="n"/>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H90" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+      <c r="J90" s="15" t="n"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Фильтр-регулятор с манометром Camozzi NXE2-1/4-FR, G¼, 0–10 бар</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>G¼</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>по одному на насос: P-2 1,5–2 бар, P-4 ≤ 2 бар</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I91" s="12" t="inlineStr">
+        <is>
+          <t>BB-Engineering: Camozzi NXE2 G¼</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="B92" s="14" t="n"/>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>G¼ × 8</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>выход регулятора и кламп ¼″ у насоса</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>BB-Engineering: S6510 8-1/4</t>
+        </is>
+      </c>
+      <c r="J92" s="15" t="n"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>G¼</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n"/>
+    </row>
+    <row r="94" ht="16.5" customHeight="1">
+      <c r="A94" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="B94" s="14" t="n"/>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Трубка полиуретановая Camozzi TPU 8/6</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>8/6</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>регулятор → насос, по 3–5 м</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>8 м</t>
+        </is>
+      </c>
+      <c r="G94" s="16" t="inlineStr">
+        <is>
+          <t>10 м</t>
+        </is>
+      </c>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>BB-Engineering: TPU 8/6</t>
+        </is>
+      </c>
+      <c r="J94" s="15" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>по порту</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: ёлочка НР</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости соединений, кроме гребёнки реактора — она есть)</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="6" t="n"/>
+    </row>
+    <row r="97" ht="16.5" customHeight="1">
+      <c r="A97" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>все соединения ½″, кроме гребёнки реактора</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n"/>
+    </row>
+    <row r="98" ht="43.5" customHeight="1">
+      <c r="A98" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="B98" s="14" t="n"/>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>штуцеры P1–P4, слив, тройники под BV-1 и на входе нутча, выгрузка, переходы колонн и нутча</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+      <c r="J98" s="15" t="n"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>К64 (2″)</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="B100" s="14" t="n"/>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>К91 (3″)</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G100" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
+        </is>
+      </c>
+      <c r="J100" s="15" t="n"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>видно уровень суспензии</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="13" t="n">
+        <v>89</v>
+      </c>
+      <c r="B102" s="14" t="n"/>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>где эфир и углеводороды: дозирование, слив, нутч и его гребёнка, вакуум, F-2</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="J102" s="15" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>реактор P1–P4, слив, выгрузка, нутч</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n"/>
+    </row>
+    <row r="104" ht="43.5" customHeight="1">
+      <c r="A104" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B104" s="14" t="n"/>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+        </is>
+      </c>
+      <c r="J104" s="15" t="n"/>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>К64 (2″)</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>нутч: стыки переходов</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I65" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: диоптр кламп</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="n"/>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="13" t="n">
-        <v>57</v>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>F-1</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>К119 (4″) × 500</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G66" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: царга кламп</t>
-        </is>
-      </c>
-      <c r="J66" s="15" t="n"/>
-    </row>
-    <row r="67" ht="43.5" customHeight="1">
-      <c r="A67" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="B106" s="14" t="n"/>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H67" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
-        </is>
-      </c>
-      <c r="J67" s="9" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="13" t="n">
-        <v>59</v>
-      </c>
-      <c r="B68" s="14" t="n"/>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr">
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G106" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="J106" s="15" t="n"/>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G68" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
-        </is>
-      </c>
-      <c r="J68" s="15" t="n"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>PI-5</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>на отвод тройника гребёнки</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="n"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="13" t="n">
-        <v>61</v>
-      </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>PSV-4</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
-        <is>
-          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="inlineStr">
-        <is>
-          <t>на тройник гребёнки; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
-        </is>
-      </c>
-      <c r="F70" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G70" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I70" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: предохр. клапан угловой кламп</t>
-        </is>
-      </c>
-      <c r="J70" s="15" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>К25 × ½″</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>выход PSV-4 → граница с коллектором сбросов смежников</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G71" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I71" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: кламп – резьба наружная</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="n"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="13" t="n">
-        <v>63</v>
-      </c>
-      <c r="B72" s="14" t="inlineStr">
-        <is>
-          <t>VV-2</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr">
-        <is>
-          <t>вакуум нутча</t>
-        </is>
-      </c>
-      <c r="F72" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H72" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I72" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J72" s="15" t="n"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>К25 × ¼″</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: кламп – резьба наружная</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="13" t="n">
-        <v>65</v>
-      </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>V-F2</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E74" s="15" t="inlineStr">
-        <is>
-          <t>выход нутча (фильтрат)</t>
-        </is>
-      </c>
-      <c r="F74" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H74" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J74" s="15" t="n"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>Хомут-держатель для труб нерж.</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>по Ø: ½″, 3″, K119</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2)</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I107" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n"/>
+    </row>
+    <row r="108" ht="70.5" customHeight="1">
+      <c r="A108" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="B108" s="14" t="n"/>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
+        </is>
+      </c>
+      <c r="F108" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G108" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+        </is>
+      </c>
+      <c r="J108" s="15" t="n"/>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>К91 (3″)</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n"/>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="n"/>
+      <c r="I110" s="5" t="n"/>
+      <c r="J110" s="6" t="n"/>
+    </row>
+    <row r="111" ht="57" customHeight="1">
+      <c r="A111" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>DN ¾″ (ID 19)</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>все линии K25 на ёлочках K25 × 19,05: верх E-1 → гребёнка, гребёнка нутча, V-F2 → P-4, P-4 → F-2, бочка → V-S1, F-2 → канистра, вакуум, vent, NRV-6 → G-1; хомуты 25–40</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>≈16,5 м</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>18 м</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: силикон армированный TSO</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n"/>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="B112" s="14" t="n"/>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>концы рукавов ¾″ (18)</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G112" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 19,05</t>
+        </is>
+      </c>
+      <c r="J112" s="15" t="n"/>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="B113" s="8" t="n"/>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Хомут червячный нерж.</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>8–12 / 25–40 / 32–50</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>по 2 на конец рукава: PF ¼″ на P-1 (по 1) / TSO ¾″ / TSO 1″</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>2 / 36 / 8</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t>4 / 38 / 10</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут червячный</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n"/>
+    </row>
+    <row r="114" ht="43.5" customHeight="1">
+      <c r="A114" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B114" s="14" t="n"/>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>12 мм / ¼″</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>≈10</t>
+        </is>
+      </c>
+      <c r="G114" s="16" t="inlineStr">
+        <is>
+          <t>≈12</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>BB-Engineering: обжимные фитинги</t>
+        </is>
+      </c>
+      <c r="J114" s="17" t="inlineStr">
+        <is>
+          <t>fluid-line.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Шина и кабели заземления с зажимами-крокодилами</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>заземление R-1, P-2, F-1, F-2, канистр (5–6 точек)</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G115" s="10" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут-держатель</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="n"/>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>Вакуум VP-1</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="5" t="n"/>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="6" t="n"/>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>VP-1</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>всас VP-1: сводит рукава от VV-1 (гребёнка реактора) и VV-2 (нутч)</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H77" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I77" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="n"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="13" t="n">
-        <v>68</v>
-      </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>VP-1</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>Переходник K25 → вход VP-1 (KF16 или ёлочка — по насосу)</t>
-        </is>
-      </c>
-      <c r="D78" s="14" t="inlineStr">
-        <is>
-          <t>К25 × KF16?</t>
-        </is>
-      </c>
-      <c r="E78" s="15" t="inlineStr">
-        <is>
-          <t>вход насоса — уточнить</t>
-        </is>
-      </c>
-      <c r="F78" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G78" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H78" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: вакуумный фланец KF</t>
-        </is>
-      </c>
-      <c r="J78" s="15" t="n"/>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="6" t="n"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>P-4</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>фильтрат нутча → F-2</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H80" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I80" s="12" t="inlineStr">
-        <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
-        </is>
-      </c>
-      <c r="J80" s="9" t="n"/>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="B81" s="14" t="n"/>
-      <c r="C81" s="15" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>К25 × ¼″ BSP вн.</t>
-        </is>
-      </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
-        </is>
-      </c>
-      <c r="F81" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G81" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H81" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
-        </is>
-      </c>
-      <c r="J81" s="15" t="n"/>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>F-2</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>10″</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H82" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I82" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: корпус 10″</t>
-        </is>
-      </c>
-      <c r="J82" s="9" t="n"/>
-    </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="13" t="n">
-        <v>72</v>
-      </c>
-      <c r="B83" s="14" t="n"/>
-      <c r="C83" s="15" t="inlineStr">
-        <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
-        </is>
-      </c>
-      <c r="D83" s="14" t="inlineStr">
-        <is>
-          <t>10″</t>
-        </is>
-      </c>
-      <c r="E83" s="15" t="inlineStr">
-        <is>
-          <t>по 2 шт. каждого рейтинга</t>
-        </is>
-      </c>
-      <c r="F83" s="14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G83" s="16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H83" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I83" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: патроны</t>
-        </is>
-      </c>
-      <c r="J83" s="15" t="n"/>
-    </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>под корпус 10″</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H84" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I84" s="12" t="inlineStr">
-        <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="n"/>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="13" t="n">
-        <v>74</v>
-      </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>V-F3</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E85" s="15" t="inlineStr">
-        <is>
-          <t>выход F-2 → налив</t>
-        </is>
-      </c>
-      <c r="F85" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G85" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H85" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J85" s="15" t="n"/>
-    </row>
-    <row r="86" ht="16.5" customHeight="1">
-      <c r="A86" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>W-3</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>Весы 60 кг, дискр. 10 г</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>фасовка в канистры — можно весами W-2</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H86" s="19" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="I86" s="12" t="inlineStr">
-        <is>
-          <t>Аналитпром: ВПС-60</t>
-        </is>
-      </c>
-      <c r="J86" s="9" t="n"/>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>Сжатый воздух к насосам P-2, P-4</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="5" t="n"/>
-      <c r="E87" s="5" t="n"/>
-      <c r="F87" s="5" t="n"/>
-      <c r="G87" s="5" t="n"/>
-      <c r="H87" s="5" t="n"/>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="6" t="n"/>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="7" t="n">
-        <v>76</v>
-      </c>
-      <c r="B88" s="8" t="n"/>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>вход воздуха насоса (по 1 на насос)</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H88" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I88" s="12" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель переходной</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="n"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="13" t="n">
-        <v>77</v>
-      </c>
-      <c r="B89" s="14" t="n"/>
-      <c r="C89" s="15" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
-        </is>
-      </c>
-      <c r="D89" s="14" t="inlineStr">
-        <is>
-          <t>К25 × ¼″ BSP вн.</t>
-        </is>
-      </c>
-      <c r="E89" s="15" t="inlineStr">
-        <is>
-          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
-        </is>
-      </c>
-      <c r="F89" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G89" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H89" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
-        </is>
-      </c>
-      <c r="J89" s="15" t="n"/>
-    </row>
-    <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>Фильтр-регулятор с манометром Camozzi NXE2-1/4-FR, G¼, 0–10 бар</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>G¼</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>по одному на насос: P-2 1,5–2 бар, P-4 ≤ 2 бар</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H90" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I90" s="12" t="inlineStr">
-        <is>
-          <t>BB-Engineering: Camozzi NXE2 G¼</t>
-        </is>
-      </c>
-      <c r="J90" s="9" t="n"/>
-    </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="13" t="n">
-        <v>79</v>
-      </c>
-      <c r="B91" s="14" t="n"/>
-      <c r="C91" s="15" t="inlineStr">
-        <is>
-          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
-        </is>
-      </c>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>G¼ × 8</t>
-        </is>
-      </c>
-      <c r="E91" s="15" t="inlineStr">
-        <is>
-          <t>выход регулятора и кламп ¼″ у насоса</t>
-        </is>
-      </c>
-      <c r="F91" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G91" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
-        <is>
-          <t>BB-Engineering: S6510 8-1/4</t>
-        </is>
-      </c>
-      <c r="J91" s="15" t="n"/>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="B92" s="8" t="n"/>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>G¼</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H92" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I92" s="12" t="inlineStr">
-        <is>
-          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
-        </is>
-      </c>
-      <c r="J92" s="9" t="n"/>
-    </row>
-    <row r="93" ht="16.5" customHeight="1">
-      <c r="A93" s="13" t="n">
-        <v>81</v>
-      </c>
-      <c r="B93" s="14" t="n"/>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>Трубка полиуретановая Camozzi TPU 8/6</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>8/6</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>регулятор → насос, по 3–5 м</t>
-        </is>
-      </c>
-      <c r="F93" s="14" t="inlineStr">
-        <is>
-          <t>8 м</t>
-        </is>
-      </c>
-      <c r="G93" s="16" t="inlineStr">
-        <is>
-          <t>10 м</t>
-        </is>
-      </c>
-      <c r="H93" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>BB-Engineering: TPU 8/6</t>
-        </is>
-      </c>
-      <c r="J93" s="15" t="n"/>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
-        </is>
-      </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>по порту</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H94" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="I94" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: ёлочка НР</t>
-        </is>
-      </c>
-      <c r="J94" s="9" t="n"/>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости соединений, кроме гребёнки реактора — она есть)</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="5" t="n"/>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="6" t="n"/>
-    </row>
-    <row r="96" ht="16.5" customHeight="1">
-      <c r="A96" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B96" s="8" t="n"/>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>все соединения ½″, кроме гребёнки реактора</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G96" s="10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H96" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I96" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="n"/>
-    </row>
-    <row r="97" ht="43.5" customHeight="1">
-      <c r="A97" s="13" t="n">
-        <v>84</v>
-      </c>
-      <c r="B97" s="14" t="n"/>
-      <c r="C97" s="15" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E97" s="15" t="inlineStr">
-        <is>
-          <t>штуцеры P1–P4, слив, тройники под BV-1 и на входе нутча, выгрузка, переходы колонн и нутча</t>
-        </is>
-      </c>
-      <c r="F97" s="14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G97" s="16" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H97" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I97" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-      <c r="J97" s="15" t="n"/>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B98" s="8" t="n"/>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>К64 (2″)</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G98" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I98" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-      <c r="J98" s="9" t="n"/>
-    </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="13" t="n">
-        <v>86</v>
-      </c>
-      <c r="B99" s="14" t="n"/>
-      <c r="C99" s="15" t="inlineStr">
-        <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>К91 (3″)</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
-        </is>
-      </c>
-      <c r="F99" s="14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G99" s="16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H99" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
-        </is>
-      </c>
-      <c r="J99" s="15" t="n"/>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G100" s="10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H100" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I100" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-      <c r="J100" s="9" t="n"/>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="13" t="n">
-        <v>88</v>
-      </c>
-      <c r="B101" s="14" t="n"/>
-      <c r="C101" s="15" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D101" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E101" s="15" t="inlineStr">
-        <is>
-          <t>где эфир и углеводороды: дозирование, слив, нутч и его гребёнка, вакуум, F-2</t>
-        </is>
-      </c>
-      <c r="F101" s="14" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="G101" s="16" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H101" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="J101" s="15" t="n"/>
-    </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>реактор P1–P4, слив, выгрузка, нутч</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G102" s="10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H102" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I102" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="J102" s="9" t="n"/>
-    </row>
-    <row r="103" ht="43.5" customHeight="1">
-      <c r="A103" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="B103" s="14" t="n"/>
-      <c r="C103" s="15" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
-        </is>
-      </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E103" s="15" t="inlineStr">
-        <is>
-          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
-        </is>
-      </c>
-      <c r="F103" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G103" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H103" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I103" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
-        </is>
-      </c>
-      <c r="J103" s="15" t="n"/>
-    </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B104" s="8" t="n"/>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>К64 (2″)</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>нутч: стыки переходов</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G104" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H104" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I104" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="J104" s="9" t="n"/>
-    </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="13" t="n">
-        <v>92</v>
-      </c>
-      <c r="B105" s="14" t="n"/>
-      <c r="C105" s="15" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D105" s="14" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="E105" s="15" t="inlineStr">
-        <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
-        </is>
-      </c>
-      <c r="F105" s="14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G105" s="16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H105" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="J105" s="15" t="n"/>
-    </row>
-    <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2)</t>
-        </is>
-      </c>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G106" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H106" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I106" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="n"/>
-    </row>
-    <row r="107" ht="70.5" customHeight="1">
-      <c r="A107" s="13" t="n">
-        <v>94</v>
-      </c>
-      <c r="B107" s="14" t="n"/>
-      <c r="C107" s="15" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
-        </is>
-      </c>
-      <c r="D107" s="14" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E107" s="15" t="inlineStr">
-        <is>
-          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
-        </is>
-      </c>
-      <c r="F107" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G107" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H107" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I107" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
-        </is>
-      </c>
-      <c r="J107" s="15" t="n"/>
-    </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="B108" s="8" t="n"/>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t>К91 (3″)</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
-        </is>
-      </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G108" s="10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H108" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I108" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-      <c r="J108" s="9" t="n"/>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="5" t="n"/>
-      <c r="H109" s="5" t="n"/>
-      <c r="I109" s="5" t="n"/>
-      <c r="J109" s="6" t="n"/>
-    </row>
-    <row r="110" ht="57" customHeight="1">
-      <c r="A110" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="B110" s="8" t="n"/>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t>DN ¾″ (ID 19)</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>все линии K25 на ёлочках K25 × 19,05: верх E-1 → гребёнка, гребёнка нутча, V-F2 → P-4, P-4 → F-2, бочка → V-S1, F-2 → канистра, вакуум, vent, NRV-6 → G-1; хомуты 25–40</t>
-        </is>
-      </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>≈16,5 м</t>
-        </is>
-      </c>
-      <c r="G110" s="10" t="inlineStr">
-        <is>
-          <t>18 м</t>
-        </is>
-      </c>
-      <c r="H110" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I110" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: силикон армированный TSO</t>
-        </is>
-      </c>
-      <c r="J110" s="9" t="n"/>
-    </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="13" t="n">
-        <v>97</v>
-      </c>
-      <c r="B111" s="14" t="n"/>
-      <c r="C111" s="15" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
-        </is>
-      </c>
-      <c r="D111" s="14" t="inlineStr">
-        <is>
-          <t>К25 × 19,05</t>
-        </is>
-      </c>
-      <c r="E111" s="15" t="inlineStr">
-        <is>
-          <t>концы рукавов ¾″ (18)</t>
-        </is>
-      </c>
-      <c r="F111" s="14" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G111" s="16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H111" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
-        </is>
-      </c>
-      <c r="J111" s="15" t="n"/>
-    </row>
-    <row r="112" ht="30" customHeight="1">
-      <c r="A112" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>Хомут червячный нерж.</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>8–12 / 25–40 / 32–50</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>по 2 на конец рукава: PF ¼″ на P-1 (по 1) / TSO ¾″ / TSO 1″</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t>2 / 36 / 8</t>
-        </is>
-      </c>
-      <c r="G112" s="10" t="inlineStr">
-        <is>
-          <t>4 / 38 / 10</t>
-        </is>
-      </c>
-      <c r="H112" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I112" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут червячный</t>
-        </is>
-      </c>
-      <c r="J112" s="9" t="n"/>
-    </row>
-    <row r="113" ht="43.5" customHeight="1">
-      <c r="A113" s="13" t="n">
-        <v>99</v>
-      </c>
-      <c r="B113" s="14" t="n"/>
-      <c r="C113" s="15" t="inlineStr">
-        <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
-        </is>
-      </c>
-      <c r="D113" s="14" t="inlineStr">
-        <is>
-          <t>12 мм / ¼″</t>
-        </is>
-      </c>
-      <c r="E113" s="15" t="inlineStr">
-        <is>
-          <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
-        </is>
-      </c>
-      <c r="F113" s="14" t="inlineStr">
-        <is>
-          <t>≈10</t>
-        </is>
-      </c>
-      <c r="G113" s="16" t="inlineStr">
-        <is>
-          <t>≈12</t>
-        </is>
-      </c>
-      <c r="H113" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I113" s="17" t="inlineStr">
-        <is>
-          <t>BB-Engineering: обжимные фитинги</t>
-        </is>
-      </c>
-      <c r="J113" s="17" t="inlineStr">
-        <is>
-          <t>fluid-line.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="30" customHeight="1">
-      <c r="A114" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="B114" s="8" t="n"/>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>Шина и кабели заземления с зажимами-крокодилами</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="n"/>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>заземление R-1, P-2, F-1, F-2, канистр (5–6 точек)</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="G114" s="10" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="H114" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I114" s="12" t="inlineStr">
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
         <is>
           <t>ПромНагрев: заземление бочек</t>
         </is>
       </c>
-      <c r="J114" s="9" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>Позиций: 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="28" customHeight="1">
-      <c r="A117" s="21" t="inlineStr">
+      <c r="J115" s="9" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>Позиций: 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="21" t="inlineStr">
         <is>
           <t>Статус: КУПИТЬ — заказывать; УТОЧНИТЬ — сначала замер / уточнение у поставщика; W-2 — использовать весы W-2. Ссылки кликабельны и по возможности открывают карточку сразу с нужным вариантом (размер, AISI 316).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J114"/>
+  <autoFilter ref="A4:J115"/>
   <mergeCells count="12">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A117:J117"/>
-    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A118:J118"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A88:J88"/>
     <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A110:J110"/>
+    <mergeCell ref="A77:J77"/>
     <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A87:J87"/>
     <mergeCell ref="A48:J48"/>
-    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A96:J96"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A76:J76"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
@@ -5278,13 +5320,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId64"/>
@@ -5299,23 +5341,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId95"/>
@@ -5328,12 +5370,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -2049,7 +2049,7 @@
       </c>
       <c r="J36" s="9" t="n"/>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="43.5" customHeight="1">
       <c r="A37" s="13" t="n">
         <v>30</v>
       </c>
@@ -2066,17 +2066,17 @@
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>входы и выходы C-1, C-2 → обжим 12 мм (трубка 10×12); запас на все 7 — здесь</t>
+          <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 9 — здесь</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="J38" s="9" t="n"/>
     </row>
-    <row r="39" ht="43.5" customHeight="1">
+    <row r="39" ht="84" customHeight="1">
       <c r="A39" s="13" t="n">
         <v>32</v>
       </c>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Обратный клапан под обжим 12 мм, открытие ≤ 1/3 psi (Swagelok CH 12M или аналог), уплотнение не FKM</t>
+          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>12 мм</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>C-2 → V-G2 → NRV-3 → ввод газа T2</t>
+          <t>C-2 → V-G2 → NRV-3 → ввод газа T2: не пускает пары эфира / MeSiCl₃ из реактора назад в колонны и G-1. Ставится в трубку 10×12 через 2 переходника кламп → ½″ нар. + обжим 12 мм. Генератор держать ≈0,15–0,25 бар (ниже уставки PSV-3)</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>Swagelok: обратные клапаны</t>
+          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
         </is>
       </c>
       <c r="J39" s="15" t="n"/>
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="J93" s="15" t="n"/>
     </row>
-    <row r="94" ht="30" customHeight="1">
+    <row r="94" ht="43.5" customHeight="1">
       <c r="A94" s="7" t="n">
         <v>82</v>
       </c>
@@ -4370,17 +4370,17 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2)</t>
+          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2), NRV-3 (2)</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Смета" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$J$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$J$100</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Смета'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -861,24 +861,28 @@
       </c>
       <c r="J8" s="9" t="n"/>
     </row>
-    <row r="9" ht="43.5" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="13" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>P-3</t>
+          <t>FV-1</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Насос дозирующий мембранный, головка PVDF/PTFE, мембрана PTFE, уплотнения FFKM/PTFE, 1–20 мл/мин</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n"/>
+          <t>Игольчатый вентиль ¼″ под обжим, нерж., PTFE-сальник</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>¼″</t>
+        </is>
+      </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>дозирование MeSiCl₃, PDMS-OH</t>
+          <t>регулировка подачи P-3 → реактор</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -898,12 +902,12 @@
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>WT Pump: Grundfos DDA 7.5-16 PVDF</t>
+          <t>Флюид-Лайн: игольчатые вентили</t>
         </is>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>gematech.ru</t>
+          <t>grossner.ru</t>
         </is>
       </c>
     </row>
@@ -911,10 +915,14 @@
       <c r="A10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>NRV-4</t>
+        </is>
+      </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Переходники под P-3: резьба насоса → обжим ¼″</t>
+          <t>Обратный клапан ¼″ нерж., уплотнение PTFE/FFKM (не FKM)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -924,19 +932,19 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>вход и выход P-3 → трубка PTFE ¼″</t>
+          <t>P-3 → реактор</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -944,23 +952,23 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>BB-Engineering: обжимные фитинги</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="n"/>
+          <t>Флюид-Лайн: обратные клапаны Hy-Lok</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>grossner.ru</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>FV-1</t>
-        </is>
-      </c>
+      <c r="B11" s="14" t="n"/>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Игольчатый вентиль ¼″ под обжим, нерж., PTFE-сальник</t>
+          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -970,17 +978,17 @@
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>регулировка подачи P-3 → реактор</t>
+          <t>тара → P-3 (перистальтический, есть) → FV-1 → NRV-4 → P3</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>≈3 м</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -990,212 +998,204 @@
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>Флюид-Лайн: игольчатые вентили</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>grossner.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>Пневмо-Электро: трубки PTFE</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="43.5" customHeight="1">
       <c r="A12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>NRV-4</t>
-        </is>
-      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Обратный клапан ¼″ нерж., уплотнение PTFE/FFKM (не FKM)</t>
+          <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>¼″</t>
+          <t>GL45 или по таре</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>P-3 → реактор</t>
+          <t>тара MeSiCl₃ / PDMS-OH / эфир; резьбу горловины уточнить</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Флюид-Лайн: обратные клапаны Hy-Lok</t>
+          <t>Germeon: крышка DURAN GL45, 2 порта</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>grossner.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="13" t="n">
+          <t>wiegand.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="70.5" customHeight="1">
+      <c r="A14" s="7" t="n">
         <v>8</v>
-      </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>¼″</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>тара → P-3 → FV-1 → NRV-4 → P3</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>≈3 м</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро: трубки PTFE</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="n"/>
-    </row>
-    <row r="14" ht="43.5" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>9</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
+          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>GL45 или по таре</t>
+          <t>500×500×3</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>тара MeSiCl₃ / PDMS-OH / эфир; резьбу горловины уточнить</t>
+          <t>вода, NaOH, водный метиламин. Перед резкой снять размеры и толщину штатной прокладки (чек-лист g7); толще 3 мм — брать 4 мм. Доп. ссылка — штатная прокладка Altmaler (поз. 3, ≈5 800 ₽)</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
+          <t>1 лист</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>2 листа</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>Профрезина: техпластина EPDM 500×500×3</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>altmaler.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>К25 × G¼″ вн.</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>вход р-ра (сифон) и выход газа — штуцеры G¼″ нар. (Ø≈13,2, шаг 1,337)</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>Germeon: крышка DURAN GL45, 2 порта</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>wiegand.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="70.5" customHeight="1">
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
+          <t>Переходник нерж. резьба порта регулятора → кламп</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>500×500×3</t>
+          <t>К25 × G1/2″</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>вода, NaOH, водный метиламин. Перед резкой снять размеры и толщину штатной прокладки (чек-лист g7); толще 3 мм — брать 4 мм. Доп. ссылка — штатная прокладка Altmaler (поз. 3, ≈5 800 ₽)</t>
+          <t>порт регулятора (PSV-3, аргон A2, PI-3) — резьбу замерить</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>1 лист</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>2 листа</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Профрезина: техпластина EPDM 500×500×3</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>altmaler.ru</t>
+          <t>grossner.ru</t>
         </is>
       </c>
     </row>
@@ -1206,29 +1206,29 @@
       <c r="B17" s="14" t="n"/>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 610 ₽)</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>К25 × G¼″ вн.</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>вход р-ра (сифон) и выход газа — штуцеры G¼″ нар. (Ø≈13,2, шаг 1,337)</t>
+          <t>порт регулятора: вверх PSV-3, вбок аргон A2 (запас на все 4 тройника ½″ — здесь)</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -1236,29 +1236,33 @@
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
       <c r="J17" s="15" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="43.5" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="8" t="n"/>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>PSV-3</t>
+        </is>
+      </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Переходник нерж. резьба порта регулятора → кламп</t>
+          <t>Клапан предохранительный угловой кламп, 0,3–0,5 бар</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>К25 × G1/2″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>порт регулятора (PSV-3, аргон A2, PI-3) — резьбу замерить</t>
+          <t>на тройнике порта регулятора; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1268,24 +1272,20 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="inlineStr">
-        <is>
-          <t>grossner.ru</t>
-        </is>
-      </c>
+          <t>Гросснер: предохр. клапан угловой кламп</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="13" t="n">
@@ -1294,17 +1294,17 @@
       <c r="B19" s="14" t="n"/>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 610 ₽)</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>порт регулятора: вверх PSV-3, вбок аргон A2 (запас на все 4 тройника ½″ — здесь)</t>
+          <t>выход PSV-3 → граница с коллектором сбросов смежников</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -1324,33 +1324,29 @@
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
       <c r="J19" s="15" t="n"/>
     </row>
-    <row r="20" ht="43.5" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>PSV-3</t>
-        </is>
-      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Клапан предохранительный угловой кламп, 0,3–0,5 бар</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>на тройнике порта регулятора; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
+          <t>аргон A2 в тройник порта — граница с аргоновой линией смежников</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -1360,7 +1356,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -1370,7 +1366,7 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: предохр. клапан угловой кламп</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
       <c r="J20" s="9" t="n"/>
@@ -1379,20 +1375,24 @@
       <c r="A21" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="14" t="n"/>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>V-G1</t>
+        </is>
+      </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>выход PSV-3 → граница с коллектором сбросов смежников</t>
+          <t>выход газа G-1 → колонны</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J21" s="15" t="n"/>
@@ -1424,17 +1424,17 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>аргон A2 в тройник порта — граница с аргоновой линией смежников</t>
+          <t>V-G1 → обжим 12 мм (трубка 10×12 на C-1)</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -1465,22 +1465,18 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>V-G1</t>
+          <t>P-1</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
+          <t>Насос перистальтический с регулятором оборотов, 10–100 мл/мин</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n"/>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>выход газа G-1 → колонны</t>
+          <t>подача водного метиламина; привод вне зоны паров</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -1500,10 +1496,14 @@
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="n"/>
+          <t>Brixlab: BT100S</t>
+        </is>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>dia-m.ru</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -1512,27 +1512,27 @@
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>V-G1 → обжим 12 мм (трубка 10×12 на C-1)</t>
+          <t>V-1 → головка P-1 → штуцер K25 × 6,35; толщину стенки сверить с головкой</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 м</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 м</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
       <c r="J24" s="9" t="n"/>
@@ -1551,20 +1551,20 @@
       <c r="A25" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>P-1</t>
-        </is>
-      </c>
+      <c r="B25" s="14" t="n"/>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Насос перистальтический с регулятором оборотов, 10–100 мл/мин</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="n"/>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>К25 × 6,35</t>
+        </is>
+      </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>подача водного метиламина; привод вне зоны паров</t>
+          <t>выход P-1 → кран V-P1; хомут червячный 8–12</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -1584,43 +1584,43 @@
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>Brixlab: BT100S</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>dia-m.ru</t>
-        </is>
-      </c>
+          <t>Гросснер: штуцер K25 × 6,35</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>V-P1</t>
+        </is>
+      </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>V-1 → головка P-1 → штуцер K25 × 6,35; толщину стенки сверить с головкой</t>
+          <t>после P-1</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>1 м</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>2 м</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J26" s="9" t="n"/>
@@ -1639,20 +1639,24 @@
       <c r="A27" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="14" t="n"/>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>NRV-6</t>
+        </is>
+      </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
+          <t>Клапан обратный кламп пружинный</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>К25 × 6,35</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>выход P-1 → кран V-P1; хомут червячный 8–12</t>
+          <t>нагнетание P-1 → G-1 (газ из G-1 не уходит назад в канистру)</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
@@ -1662,7 +1666,7 @@
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1672,7 +1676,7 @@
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 6,35</t>
+          <t>Гросснер: клапан обратный кламп</t>
         </is>
       </c>
       <c r="J27" s="15" t="n"/>
@@ -1681,24 +1685,20 @@
       <c r="A28" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>V-P1</t>
-        </is>
-      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Крышка-переходник на канистру V-1: ввод заборной трубки P-1 + вход аргона</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>по горловине</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>после P-1</t>
+          <t>горловину канистры замерить (DIN 61, 2″ BSP и т. п.)</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -1711,158 +1711,158 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>NRV-6</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>Клапан обратный кламп пружинный</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>нагнетание P-1 → G-1 (газ из G-1 не уходит назад в канистру)</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: клапан обратный кламп</t>
-        </is>
-      </c>
-      <c r="J29" s="15" t="n"/>
+          <t>Germeon: крышка DURAN GL45, 2 порта</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>wiegand.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="6" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>C-1, C-2</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>К91 (3″) × 400</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>корпуса колонн, низ</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: царга кламп</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Крышка-переходник на канистру V-1: ввод заборной трубки P-1 + вход аргона</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>по горловине</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>горловину канистры замерить (DIN 61, 2″ BSP и т. п.)</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>Germeon: крышка DURAN GL45, 2 порта</t>
-        </is>
-      </c>
-      <c r="J30" s="12" t="inlineStr">
-        <is>
-          <t>wiegand.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>C-1, C-2</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>К91 (3″), L ≈ 200</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>верх колонн — видно засыпку и фронт влаги</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: диоптр кламп</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="43.5" customHeight="1">
       <c r="A32" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>C-1, C-2</t>
-        </is>
-      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>К91 (3″) × 400</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>корпуса колонн, низ</t>
+          <t>опора засыпки: низ колонн — на нём лежат сита / NaOH; верх — прижим засыпки. В кламп-стык между двумя прокладками EPDM K91</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
       <c r="J32" s="9" t="n"/>
@@ -1881,34 +1881,30 @@
       <c r="A33" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>C-1, C-2</t>
-        </is>
-      </c>
+      <c r="B33" s="14" t="n"/>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>К91 (3″), L ≈ 200</t>
+          <t>К91 → К50,5</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>верх колонн — видно засыпку и фронт влаги</t>
+          <t>низ и верх каждой колонны (3″ → ½″ одной деталью у Гросснера нет)</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -1918,29 +1914,29 @@
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: диоптр кламп</t>
+          <t>Гросснер: переход 91 × 50,5 316</t>
         </is>
       </c>
       <c r="J33" s="15" t="n"/>
     </row>
-    <row r="34" ht="43.5" customHeight="1">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="7" t="n">
         <v>27</v>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>опора засыпки: низ колонн — на нём лежат сита / NaOH; верх — прижим засыпки. В кламп-стык между двумя прокладками EPDM K91</t>
+          <t>низ и верх каждой колонны, после перехода 3″ → 1″</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -1950,7 +1946,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -1960,39 +1956,39 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
       <c r="J34" s="9" t="n"/>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" ht="43.5" customHeight="1">
       <c r="A35" s="13" t="n">
         <v>28</v>
       </c>
       <c r="B35" s="14" t="n"/>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>К91 → К50,5</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>низ и верх каждой колонны (3″ → ½″ одной деталью у Гросснера нет)</t>
+          <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 9 — здесь</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -2002,7 +1998,7 @@
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: переход 91 × 50,5 316</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
       <c r="J35" s="15" t="n"/>
@@ -2011,30 +2007,34 @@
       <c r="A36" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>V-G2</t>
+        </is>
+      </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
+          <t>Кран шаровой под обжим 12 мм, нерж. 316, сёдла PTFE</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>12 мм</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>низ и верх каждой колонны, после перехода 3″ → 1″</t>
+          <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -2044,39 +2044,43 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Флюид-Лайн: краны шаровые инструментальные</t>
         </is>
       </c>
       <c r="J36" s="9" t="n"/>
     </row>
-    <row r="37" ht="43.5" customHeight="1">
+    <row r="37" ht="84" customHeight="1">
       <c r="A37" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="14" t="n"/>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>NRV-3</t>
+        </is>
+      </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 9 — здесь</t>
+          <t>C-2 → V-G2 → NRV-3 → ввод газа T2: не пускает пары эфира / MeSiCl₃ из реактора назад в колонны и G-1. Ставится в трубку 10×12 через 2 переходника кламп → ½″ нар. + обжим 12 мм. Генератор держать ≈0,15–0,25 бар (ниже уставки PSV-3)</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -2086,43 +2090,39 @@
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
         </is>
       </c>
       <c r="J37" s="15" t="n"/>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="16.5" customHeight="1">
       <c r="A38" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>V-G2</t>
-        </is>
-      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Кран шаровой под обжим 12 мм, нерж. 316, сёдла PTFE</t>
+          <t>Трубка PTFE 10×12, бухта</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>12 мм</t>
+          <t>10×12</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1</t>
+          <t>газ CH₃NH₂: V-G1 → C-1 → C-2 → T2</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>≈8 м</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 м</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -2132,165 +2132,161 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Флюид-Лайн: краны шаровые инструментальные</t>
+          <t>Industriation: PTFE 12/10</t>
         </is>
       </c>
       <c r="J38" s="9" t="n"/>
     </row>
-    <row r="39" ht="84" customHeight="1">
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>NRV-3</t>
-        </is>
-      </c>
+      <c r="B39" s="14" t="n"/>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>Ø76</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>C-2 → V-G2 → NRV-3 → ввод газа T2: не пускает пары эфира / MeSiCl₃ из реактора назад в колонны и G-1. Ставится в трубку 10×12 через 2 переходника кламп → ½″ нар. + обжим 12 мм. Генератор держать ≈0,15–0,25 бар (ниже уставки PSV-3)</t>
+          <t>крепление C-1, C-2 к раме или стенду</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут для труб</t>
+        </is>
+      </c>
+      <c r="J39" s="15" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Отвод кламп 90°, AISI 316</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>сразу под краном слива BV-1 — выход в горизонталь</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="n"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Трубка PTFE 10×12, бухта</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>10×12</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>газ CH₃NH₂: V-G1 → C-1 → C-2 → T2</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>≈8 м</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>10 м</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>Industriation: PTFE 12/10</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="13" t="n">
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: отвод кламп 90°</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="57" customHeight="1">
+      <c r="A42" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B41" s="14" t="n"/>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>Ø76</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>крепление C-1, C-2 к раме или стенду</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I41" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут для труб</t>
-        </is>
-      </c>
-      <c r="J41" s="15" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="6" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>1-й после отвода под BV-1: отвод 45° вниз — проба SP-1 (через переход 50,5 → 25), суспензия не застаивается; запас на оба тройника 45° — здесь</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+        </is>
+      </c>
+      <c r="J42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="43.5" customHeight="1">
       <c r="A43" s="7" t="n">
         <v>35</v>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°, AISI 316</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2300,7 +2296,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>сразу под краном слива BV-1 — выход в горизонталь</t>
+          <t>2-й: вбок V-S1 на бочку (через переход 50,5 → 25), прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -2320,34 +2316,34 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
       <c r="J43" s="9" t="n"/>
     </row>
-    <row r="44" ht="57" customHeight="1">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="13" t="n">
         <v>36</v>
       </c>
       <c r="B44" s="14" t="n"/>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>1-й после отвода под BV-1: отвод 45° вниз — проба SP-1 (через переход 50,5 → 25), суспензия не застаивается; запас на оба тройника 45° — здесь</t>
+          <t>отводы тройников → SP-1 и V-S1</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
@@ -2362,34 +2358,38 @@
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
       <c r="J44" s="15" t="n"/>
     </row>
-    <row r="45" ht="43.5" customHeight="1">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B45" s="8" t="n"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>SP-1, V-S1</t>
+        </is>
+      </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>2-й: вбок V-S1 на бочку (через переход 50,5 → 25), прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
+          <t>SP-1 — проба, V-S1 — бочка растворителя</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -2404,41 +2404,41 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J45" s="9" t="n"/>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="13" t="n">
         <v>38</v>
       </c>
       <c r="B46" s="14" t="n"/>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>отводы тройников → SP-1 и V-S1</t>
+          <t>носик пробоотбора после SP-1</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -2446,43 +2446,39 @@
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: отвод кламп</t>
         </is>
       </c>
       <c r="J46" s="15" t="n"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="43.5" customHeight="1">
       <c r="A47" s="7" t="n">
         <v>39</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>SP-1, V-S1</t>
+          <t>P-2</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>SP-1 — проба, V-S1 — бочка растворителя</t>
+          <t>выгрузка суспензии на нутч</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
@@ -2492,39 +2488,39 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
       <c r="J47" s="9" t="n"/>
     </row>
-    <row r="48" ht="16.5" customHeight="1">
+    <row r="48" ht="43.5" customHeight="1">
       <c r="A48" s="13" t="n">
         <v>40</v>
       </c>
       <c r="B48" s="14" t="n"/>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>носик пробоотбора после SP-1</t>
+          <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -2534,39 +2530,39 @@
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
+          <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
       <c r="J48" s="15" t="n"/>
     </row>
-    <row r="49" ht="43.5" customHeight="1">
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>P-2</t>
-        </is>
-      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="n"/>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>К50,5 × ¼″ BSP вн.</t>
+        </is>
+      </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>выгрузка суспензии на нутч</t>
+          <t>P-2: вход и выход → рукав 1″</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -2576,29 +2572,29 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
       <c r="J49" s="9" t="n"/>
     </row>
-    <row r="50" ht="43.5" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="13" t="n">
         <v>42</v>
       </c>
       <c r="B50" s="14" t="n"/>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>¼″ NPT × ¼″ BSP</t>
+          <t>К50,5 × 25,4</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
+          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -2608,7 +2604,7 @@
       </c>
       <c r="G50" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -2618,39 +2614,39 @@
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>Rizur: ниппель RizurLok-NP</t>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
         </is>
       </c>
       <c r="J50" s="15" t="n"/>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="43.5" customHeight="1">
       <c r="A51" s="7" t="n">
         <v>43</v>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>P-2: вход и выход → рукав 1″</t>
+          <t>слив → P-2 (1,5 м), P-2 → нутч (2,5 м); хомуты 32–50; армирование — чтобы не сплющивался на всасе</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -2660,81 +2656,55 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
       <c r="J51" s="9" t="n"/>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="13" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="14" t="n"/>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr">
-        <is>
-          <t>К50,5 × 25,4</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
-        </is>
-      </c>
-      <c r="J52" s="15" t="n"/>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="6" t="n"/>
     </row>
     <row r="53" ht="43.5" customHeight="1">
       <c r="A53" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>слив → P-2 (1,5 м), P-2 → нутч (2,5 м); хомуты 32–50; армирование — чтобы не сплющивался на всасе</t>
+          <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
@@ -2744,55 +2714,81 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
       <c r="J53" s="9" t="n"/>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="6" t="n"/>
-    </row>
-    <row r="55" ht="43.5" customHeight="1">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="14" t="n"/>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 → К25</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
+        </is>
+      </c>
+      <c r="J54" s="15" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="7" t="n">
         <v>46</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
+          <t>крышка нутча и низ нутча</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -2802,7 +2798,7 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
       <c r="J55" s="9" t="n"/>
@@ -2814,17 +2810,17 @@
       <c r="B56" s="14" t="n"/>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
+          <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -2834,7 +2830,7 @@
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -2844,41 +2840,41 @@
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
       <c r="J56" s="15" t="n"/>
     </row>
-    <row r="57" ht="30" customHeight="1">
+    <row r="57" ht="16.5" customHeight="1">
       <c r="A57" s="7" t="n">
         <v>48</v>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>крышка нутча и низ нутча</t>
+          <t>видно уровень суспензии</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -2886,7 +2882,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: диоптр кламп</t>
         </is>
       </c>
       <c r="J57" s="9" t="n"/>
@@ -2895,20 +2891,24 @@
       <c r="A58" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="B58" s="14" t="n"/>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>F-1</t>
+        </is>
+      </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>К119 → К64</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
+          <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -2928,19 +2928,19 @@
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
       <c r="J58" s="15" t="n"/>
     </row>
-    <row r="59" ht="16.5" customHeight="1">
+    <row r="59" ht="43.5" customHeight="1">
       <c r="A59" s="7" t="n">
         <v>50</v>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>видно уровень суспензии</t>
+          <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: диоптр кламп</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
       <c r="J59" s="9" t="n"/>
@@ -2979,34 +2979,30 @@
       <c r="A60" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>F-1</t>
-        </is>
-      </c>
+      <c r="B60" s="14" t="n"/>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
+          <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -3016,29 +3012,33 @@
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
       <c r="J60" s="15" t="n"/>
     </row>
-    <row r="61" ht="43.5" customHeight="1">
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B61" s="8" t="n"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>PI-5</t>
+        </is>
+      </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
+          <t>на отвод тройника гребёнки</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
       <c r="J61" s="9" t="n"/>
@@ -3067,10 +3067,14 @@
       <c r="A62" s="13" t="n">
         <v>53</v>
       </c>
-      <c r="B62" s="14" t="n"/>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>PSV-4</t>
+        </is>
+      </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
@@ -3080,17 +3084,17 @@
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
+          <t>на тройник гребёнки; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -3100,7 +3104,7 @@
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: предохр. клапан угловой кламп</t>
         </is>
       </c>
       <c r="J62" s="15" t="n"/>
@@ -3109,24 +3113,20 @@
       <c r="A63" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>PI-5</t>
-        </is>
-      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>на отвод тройника гребёнки</t>
+          <t>выход PSV-4 → граница с коллектором сбросов смежников</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
       <c r="J63" s="9" t="n"/>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>PSV-4</t>
+          <t>VV-2</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>на тройник гребёнки; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
+          <t>вакуум нутча</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: предохр. клапан угловой кламп</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J64" s="15" t="n"/>
@@ -3204,17 +3204,17 @@
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>выход PSV-4 → граница с коллектором сбросов смежников</t>
+          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>VV-2</t>
+          <t>V-F2</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>вакуум нутча</t>
+          <t>выход нутча (фильтрат)</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -3292,27 +3292,27 @@
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
+          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -3322,114 +3322,110 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
       <c r="J67" s="9" t="n"/>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="13" t="n">
-        <v>59</v>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>V-F2</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>выход нутча (фильтрат)</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G68" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J68" s="15" t="n"/>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="6" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>P-4</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>фильтрат нутча → F-2</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>Хомут-держатель для труб нерж.</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>по Ø: ½″, 3″, K119</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут-держатель</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="n"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="6" t="n"/>
+      <c r="B70" s="14" t="n"/>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+      <c r="J70" s="15" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="7" t="n">
@@ -3437,18 +3433,22 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>P-4</t>
+          <t>F-2</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="n"/>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>фильтрат нутча → F-2</t>
+          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+          <t>Гросснер: корпус 10″</t>
         </is>
       </c>
       <c r="J71" s="9" t="n"/>
@@ -3480,27 +3480,27 @@
       <c r="B72" s="14" t="n"/>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
+          <t>по 2 шт. каждого рейтинга</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Гросснер: патроны</t>
         </is>
       </c>
       <c r="J72" s="15" t="n"/>
@@ -3519,34 +3519,30 @@
       <c r="A73" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>F-2</t>
-        </is>
-      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>под корпус 10″</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
+          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -3556,7 +3552,7 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: корпус 10″</t>
+          <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
       <c r="J73" s="9" t="n"/>
@@ -3565,30 +3561,34 @@
       <c r="A74" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="B74" s="14" t="n"/>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>V-F3</t>
+        </is>
+      </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>по 2 шт. каждого рейтинга</t>
+          <t>выход F-2 → налив</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
@@ -3598,114 +3598,110 @@
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J74" s="15" t="n"/>
     </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="7" t="n">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Сжатый воздух к насосам P-2, P-4</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="6" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>под корпус 10″</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>вход воздуха насоса (по 1 на насос)</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B77" s="14" t="n"/>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="n"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="13" t="n">
-        <v>66</v>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>V-F3</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E76" s="15" t="inlineStr">
-        <is>
-          <t>выход F-2 → налив</t>
-        </is>
-      </c>
-      <c r="F76" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G76" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H76" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I76" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J76" s="15" t="n"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>Сжатый воздух к насосам P-2, P-4</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="6" t="n"/>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+      <c r="J77" s="15" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="7" t="n">
@@ -3714,27 +3710,27 @@
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
+          <t>G¼ × 8</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>вход воздуха насоса (по 1 на насос)</t>
+          <t>выход регулятора и кламп ¼″ у насоса</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -3744,7 +3740,7 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>Rizur: ниппель переходной</t>
+          <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
       <c r="J78" s="9" t="n"/>
@@ -3756,27 +3752,27 @@
       <c r="B79" s="14" t="n"/>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
+          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>G¼</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
+          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
@@ -3786,7 +3782,7 @@
       </c>
       <c r="I79" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
       <c r="J79" s="15" t="n"/>
@@ -3798,142 +3794,142 @@
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>G¼ × 8</t>
+          <t>по порту</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>выход регулятора и кламп ¼″ у насоса</t>
+          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H80" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>BB-Engineering: S6510 8-1/4</t>
+          <t>Гросснер: ёлочка НР</t>
         </is>
       </c>
       <c r="J80" s="9" t="n"/>
     </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="13" t="n">
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости соединений, кроме гребёнки реактора — она есть)</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="6" t="n"/>
+    </row>
+    <row r="82" ht="16.5" customHeight="1">
+      <c r="A82" s="7" t="n">
         <v>70</v>
-      </c>
-      <c r="B81" s="14" t="n"/>
-      <c r="C81" s="15" t="inlineStr">
-        <is>
-          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>G¼</t>
-        </is>
-      </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
-        </is>
-      </c>
-      <c r="F81" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G81" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H81" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
-        </is>
-      </c>
-      <c r="J81" s="15" t="n"/>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="7" t="n">
-        <v>71</v>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>по порту</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
+          <t>все соединения ½″, кроме гребёнки реактора</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H82" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
         </is>
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: ёлочка НР</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
       <c r="J82" s="9" t="n"/>
     </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости соединений, кроме гребёнки реактора — она есть)</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="n"/>
-      <c r="C83" s="5" t="n"/>
-      <c r="D83" s="5" t="n"/>
-      <c r="E83" s="5" t="n"/>
-      <c r="F83" s="5" t="n"/>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="5" t="n"/>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="6" t="n"/>
-    </row>
-    <row r="84" ht="16.5" customHeight="1">
+    <row r="83" ht="43.5" customHeight="1">
+      <c r="A83" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B83" s="14" t="n"/>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>штуцеры P1–P4, слив, тройники под BV-1 и на входе нутча, выгрузка, переходы колонн и нутча</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+      <c r="J83" s="15" t="n"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="7" t="n">
         <v>72</v>
       </c>
@@ -3945,22 +3941,22 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>все соединения ½″, кроме гребёнки реактора</t>
+          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -3975,34 +3971,34 @@
       </c>
       <c r="J84" s="9" t="n"/>
     </row>
-    <row r="85" ht="43.5" customHeight="1">
+    <row r="85" ht="30" customHeight="1">
       <c r="A85" s="13" t="n">
         <v>73</v>
       </c>
       <c r="B85" s="14" t="n"/>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>штуцеры P1–P4, слив, тройники под BV-1 и на входе нутча, выгрузка, переходы колонн и нутча</t>
+          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
         </is>
       </c>
       <c r="F85" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -4012,7 +4008,7 @@
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
         </is>
       </c>
       <c r="J85" s="15" t="n"/>
@@ -4024,27 +4020,27 @@
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -4054,7 +4050,7 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
       <c r="J86" s="9" t="n"/>
@@ -4066,27 +4062,27 @@
       <c r="B87" s="14" t="n"/>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
+          <t>где эфир и углеводороды: дозирование, слив, нутч и его гребёнка, вакуум, F-2</t>
         </is>
       </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G87" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
@@ -4096,7 +4092,7 @@
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="J87" s="15" t="n"/>
@@ -4108,27 +4104,27 @@
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
+          <t>реактор P1–P4, слив, выгрузка, нутч</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
@@ -4138,39 +4134,39 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="J88" s="9" t="n"/>
     </row>
-    <row r="89" ht="30" customHeight="1">
+    <row r="89" ht="43.5" customHeight="1">
       <c r="A89" s="13" t="n">
         <v>77</v>
       </c>
       <c r="B89" s="14" t="n"/>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>где эфир и углеводороды: дозирование, слив, нутч и его гребёнка, вакуум, F-2</t>
+          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
         </is>
       </c>
       <c r="F89" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G89" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
@@ -4180,7 +4176,7 @@
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
       <c r="J89" s="15" t="n"/>
@@ -4197,22 +4193,22 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>реактор P1–P4, слив, выгрузка, нутч</t>
+          <t>нутч: стыки переходов</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -4227,34 +4223,34 @@
       </c>
       <c r="J90" s="9" t="n"/>
     </row>
-    <row r="91" ht="43.5" customHeight="1">
+    <row r="91" ht="30" customHeight="1">
       <c r="A91" s="13" t="n">
         <v>79</v>
       </c>
       <c r="B91" s="14" t="n"/>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
         </is>
       </c>
       <c r="F91" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G91" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -4264,39 +4260,39 @@
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="J91" s="15" t="n"/>
     </row>
-    <row r="92" ht="30" customHeight="1">
+    <row r="92" ht="43.5" customHeight="1">
       <c r="A92" s="7" t="n">
         <v>80</v>
       </c>
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>нутч: стыки переходов</t>
+          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2), NRV-3 (2)</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
@@ -4306,39 +4302,39 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
       <c r="J92" s="9" t="n"/>
     </row>
-    <row r="93" ht="30" customHeight="1">
+    <row r="93" ht="70.5" customHeight="1">
       <c r="A93" s="13" t="n">
         <v>81</v>
       </c>
       <c r="B93" s="14" t="n"/>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
+          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
         </is>
       </c>
       <c r="F93" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G93" s="16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -4348,12 +4344,12 @@
       </c>
       <c r="I93" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
         </is>
       </c>
       <c r="J93" s="15" t="n"/>
     </row>
-    <row r="94" ht="43.5" customHeight="1">
+    <row r="94" ht="30" customHeight="1">
       <c r="A94" s="7" t="n">
         <v>82</v>
       </c>
@@ -4365,22 +4361,22 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2), NRV-3 (2)</t>
+          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -4395,76 +4391,50 @@
       </c>
       <c r="J94" s="9" t="n"/>
     </row>
-    <row r="95" ht="70.5" customHeight="1">
-      <c r="A95" s="13" t="n">
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="6" t="n"/>
+    </row>
+    <row r="96" ht="57" customHeight="1">
+      <c r="A96" s="7" t="n">
         <v>83</v>
-      </c>
-      <c r="B95" s="14" t="n"/>
-      <c r="C95" s="15" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
-        </is>
-      </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E95" s="15" t="inlineStr">
-        <is>
-          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
-        </is>
-      </c>
-      <c r="F95" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G95" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H95" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I95" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
-        </is>
-      </c>
-      <c r="J95" s="15" t="n"/>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="7" t="n">
-        <v>84</v>
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
+          <t>все линии K25 на ёлочках K25 × 19,05: верх E-1 → гребёнка, гребёнка нутча, V-F2 → P-4, P-4 → F-2, бочка → V-S1, F-2 → канистра, вакуум, vent, NRV-6 → G-1; хомуты 25–40</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>≈16,5 м</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
@@ -4474,55 +4444,81 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
       <c r="J96" s="9" t="n"/>
     </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="n"/>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="57" customHeight="1">
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="B97" s="14" t="n"/>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>концы рукавов ¾″ (18)</t>
+        </is>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 19,05</t>
+        </is>
+      </c>
+      <c r="J97" s="15" t="n"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
       <c r="A98" s="7" t="n">
         <v>85</v>
       </c>
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>все линии K25 на ёлочках K25 × 19,05: верх E-1 → гребёнка, гребёнка нутча, V-F2 → P-4, P-4 → F-2, бочка → V-S1, F-2 → канистра, вакуум, vent, NRV-6 → G-1; хомуты 25–40</t>
+          <t>по 2 на конец рукава: PF ¼″ на P-1 (по 1) / TSO ¾″ / TSO 1″</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>≈16,5 м</t>
+          <t>2 / 36 / 8</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>4 / 38 / 10</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
@@ -4532,39 +4528,39 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
       <c r="J98" s="9" t="n"/>
     </row>
-    <row r="99" ht="30" customHeight="1">
+    <row r="99" ht="43.5" customHeight="1">
       <c r="A99" s="13" t="n">
         <v>86</v>
       </c>
       <c r="B99" s="14" t="n"/>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>12 мм / ¼″</t>
         </is>
       </c>
       <c r="E99" s="15" t="inlineStr">
         <is>
-          <t>концы рукавов ¾″ (18)</t>
+          <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
         </is>
       </c>
       <c r="F99" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>≈10</t>
         </is>
       </c>
       <c r="G99" s="16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>≈12</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
@@ -4574,10 +4570,14 @@
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
-        </is>
-      </c>
-      <c r="J99" s="15" t="n"/>
+          <t>BB-Engineering: обжимные фитинги</t>
+        </is>
+      </c>
+      <c r="J99" s="17" t="inlineStr">
+        <is>
+          <t>fluid-line.ru</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="7" t="n">
@@ -4586,27 +4586,23 @@
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>8–12 / 25–40 / 32–50</t>
-        </is>
-      </c>
+          <t>Шина и кабели заземления с зажимами-крокодилами</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n"/>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>по 2 на конец рукава: PF ¼″ на P-1 (по 1) / TSO ¾″ / TSO 1″</t>
+          <t>заземление R-1, P-2, F-1, F-2, канистр (5–6 точек)</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>2 / 36 / 8</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>4 / 38 / 10</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
@@ -4616,123 +4612,39 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>ПромНагрев: заземление бочек</t>
         </is>
       </c>
       <c r="J100" s="9" t="n"/>
     </row>
-    <row r="101" ht="43.5" customHeight="1">
-      <c r="A101" s="13" t="n">
-        <v>88</v>
-      </c>
-      <c r="B101" s="14" t="n"/>
-      <c r="C101" s="15" t="inlineStr">
-        <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
-        </is>
-      </c>
-      <c r="D101" s="14" t="inlineStr">
-        <is>
-          <t>12 мм / ¼″</t>
-        </is>
-      </c>
-      <c r="E101" s="15" t="inlineStr">
-        <is>
-          <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
-        </is>
-      </c>
-      <c r="F101" s="14" t="inlineStr">
-        <is>
-          <t>≈10</t>
-        </is>
-      </c>
-      <c r="G101" s="16" t="inlineStr">
-        <is>
-          <t>≈12</t>
-        </is>
-      </c>
-      <c r="H101" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>BB-Engineering: обжимные фитинги</t>
-        </is>
-      </c>
-      <c r="J101" s="17" t="inlineStr">
-        <is>
-          <t>fluid-line.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>Шина и кабели заземления с зажимами-крокодилами</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>заземление R-1, P-2, F-1, F-2, канистр (5–6 точек)</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="G102" s="10" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="H102" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I102" s="12" t="inlineStr">
-        <is>
-          <t>ПромНагрев: заземление бочек</t>
-        </is>
-      </c>
-      <c r="J102" s="9" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="19" t="inlineStr">
-        <is>
-          <t>Позиций: 89</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="20" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>Позиций: 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="20" t="inlineStr">
         <is>
           <t>Статус: КУПИТЬ — заказывать; УТОЧНИТЬ — сначала замер / уточнение у поставщика; W-2 — использовать весы W-2. Ссылки кликабельны и по возможности открывают карточку сразу с нужным вариантом (размер, AISI 316).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J102"/>
+  <autoFilter ref="A4:J100"/>
   <mergeCells count="11">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A97:J97"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A77:J77"/>
-    <mergeCell ref="A83:J83"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A105:J105"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A103:J103"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A95:J95"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
@@ -4741,98 +4653,95 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Смета" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$J$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Смета'!$A$4:$J$97</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Смета'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1463,30 +1463,30 @@
       <c r="A23" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>P-1</t>
-        </is>
-      </c>
+      <c r="B23" s="14" t="n"/>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Насос перистальтический с регулятором оборотов, 10–100 мл/мин</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="n"/>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>DN ¼″ (ID 6,4)</t>
+        </is>
+      </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>подача водного метиламина; привод вне зоны паров</t>
+          <t>V-1 → головка P-1 → штуцер K25 × 6,35; толщину стенки сверить с головкой</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 м</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 м</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -1496,14 +1496,10 @@
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>Brixlab: BT100S</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>dia-m.ru</t>
-        </is>
-      </c>
+          <t>Гросснер: силикон PF, DN ¼″</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -1512,27 +1508,27 @@
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>К25 × 6,35</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>V-1 → головка P-1 → штуцер K25 × 6,35; толщину стенки сверить с головкой</t>
+          <t>выход P-1 → кран V-P1; хомут червячный 8–12</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>1 м</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>2 м</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -1542,7 +1538,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
       <c r="J24" s="9" t="n"/>
@@ -1551,20 +1547,24 @@
       <c r="A25" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="14" t="n"/>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>V-P1</t>
+        </is>
+      </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>К25 × 6,35</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>выход P-1 → кран V-P1; хомут червячный 8–12</t>
+          <t>после P-1</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 6,35</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J25" s="15" t="n"/>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>V-P1</t>
+          <t>NRV-6</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Клапан обратный кламп пружинный</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>после P-1</t>
+          <t>нагнетание P-1 → G-1 (газ из G-1 не уходит назад в канистру)</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -1630,151 +1630,147 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: клапан обратный кламп</t>
         </is>
       </c>
       <c r="J26" s="9" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>NRV-6</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Клапан обратный кламп пружинный</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>нагнетание P-1 → G-1 (газ из G-1 не уходит назад в канистру)</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: клапан обратный кламп</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="n"/>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="6" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>C-1, C-2</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>К91 (3″) × 400</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>корпуса колонн, низ</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: царга кламп</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Крышка-переходник на канистру V-1: ввод заборной трубки P-1 + вход аргона</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>по горловине</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>горловину канистры замерить (DIN 61, 2″ BSP и т. п.)</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>Germeon: крышка DURAN GL45, 2 порта</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
-        <is>
-          <t>wiegand.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>C-1, C-2</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>К91 (3″), L ≈ 200</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>верх колонн — видно засыпку и фронт влаги</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: диоптр кламп</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="n"/>
+    </row>
+    <row r="30" ht="43.5" customHeight="1">
       <c r="A30" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>C-1, C-2</t>
-        </is>
-      </c>
+      <c r="B30" s="8" t="n"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>К91 (3″) × 400</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>корпуса колонн, низ</t>
+          <t>опора засыпки: низ колонн — на нём лежат сита / NaOH; верх — прижим засыпки. В кламп-стык между двумя прокладками EPDM K91</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -1784,7 +1780,7 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
       <c r="J30" s="9" t="n"/>
@@ -1793,34 +1789,30 @@
       <c r="A31" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>C-1, C-2</t>
-        </is>
-      </c>
+      <c r="B31" s="14" t="n"/>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>К91 (3″), L ≈ 200</t>
+          <t>К91 → К50,5</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>верх колонн — видно засыпку и фронт влаги</t>
+          <t>низ и верх каждой колонны (3″ → ½″ одной деталью у Гросснера нет)</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -1830,29 +1822,29 @@
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: диоптр кламп</t>
+          <t>Гросснер: переход 91 × 50,5 316</t>
         </is>
       </c>
       <c r="J31" s="15" t="n"/>
     </row>
-    <row r="32" ht="43.5" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="7" t="n">
         <v>25</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>опора засыпки: низ колонн — на нём лежат сита / NaOH; верх — прижим засыпки. В кламп-стык между двумя прокладками EPDM K91</t>
+          <t>низ и верх каждой колонны, после перехода 3″ → 1″</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -1862,7 +1854,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -1872,39 +1864,39 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
       <c r="J32" s="9" t="n"/>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="43.5" customHeight="1">
       <c r="A33" s="13" t="n">
         <v>26</v>
       </c>
       <c r="B33" s="14" t="n"/>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>К91 → К50,5</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>низ и верх каждой колонны (3″ → ½″ одной деталью у Гросснера нет)</t>
+          <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 9 — здесь</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -1914,7 +1906,7 @@
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: переход 91 × 50,5 316</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
       <c r="J33" s="15" t="n"/>
@@ -1923,30 +1915,34 @@
       <c r="A34" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>V-G2</t>
+        </is>
+      </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
+          <t>Кран шаровой под обжим 12 мм, нерж. 316, сёдла PTFE</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>12 мм</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>низ и верх каждой колонны, после перехода 3″ → 1″</t>
+          <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -1956,39 +1952,43 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Флюид-Лайн: краны шаровые инструментальные</t>
         </is>
       </c>
       <c r="J34" s="9" t="n"/>
     </row>
-    <row r="35" ht="43.5" customHeight="1">
+    <row r="35" ht="84" customHeight="1">
       <c r="A35" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="14" t="n"/>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>NRV-3</t>
+        </is>
+      </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 9 — здесь</t>
+          <t>C-2 → V-G2 → NRV-3 → ввод газа T2: не пускает пары эфира / MeSiCl₃ из реактора назад в колонны и G-1. Ставится в трубку 10×12 через 2 переходника кламп → ½″ нар. + обжим 12 мм. Генератор держать ≈0,15–0,25 бар (ниже уставки PSV-3)</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -1998,43 +1998,39 @@
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
         </is>
       </c>
       <c r="J35" s="15" t="n"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="16.5" customHeight="1">
       <c r="A36" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>V-G2</t>
-        </is>
-      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Кран шаровой под обжим 12 мм, нерж. 316, сёдла PTFE</t>
+          <t>Трубка PTFE 10×12, бухта</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>12 мм</t>
+          <t>10×12</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1</t>
+          <t>газ CH₃NH₂: V-G1 → C-1 → C-2 → T2</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>≈8 м</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 м</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -2044,165 +2040,161 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Флюид-Лайн: краны шаровые инструментальные</t>
+          <t>Industriation: PTFE 12/10</t>
         </is>
       </c>
       <c r="J36" s="9" t="n"/>
     </row>
-    <row r="37" ht="84" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>NRV-3</t>
-        </is>
-      </c>
+      <c r="B37" s="14" t="n"/>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>Ø76</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>C-2 → V-G2 → NRV-3 → ввод газа T2: не пускает пары эфира / MeSiCl₃ из реактора назад в колонны и G-1. Ставится в трубку 10×12 через 2 переходника кламп → ½″ нар. + обжим 12 мм. Генератор держать ≈0,15–0,25 бар (ниже уставки PSV-3)</t>
+          <t>крепление C-1, C-2 к раме или стенду</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут для труб</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Отвод кламп 90°, AISI 316</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>сразу под краном слива BV-1 — выход в горизонталь</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
-        </is>
-      </c>
-      <c r="J37" s="15" t="n"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Трубка PTFE 10×12, бухта</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>10×12</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>газ CH₃NH₂: V-G1 → C-1 → C-2 → T2</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>≈8 м</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>10 м</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>Industriation: PTFE 12/10</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="13" t="n">
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>Гросснер: отвод кламп 90°</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="57" customHeight="1">
+      <c r="A40" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B39" s="14" t="n"/>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>Ø76</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>крепление C-1, C-2 к раме или стенду</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут для труб</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="6" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>1-й после отвода под BV-1: отвод 45° вниз — проба SP-1 (через переход 50,5 → 25), суспензия не застаивается; запас на оба тройника 45° — здесь</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+        </is>
+      </c>
+      <c r="J40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="43.5" customHeight="1">
       <c r="A41" s="7" t="n">
         <v>33</v>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°, AISI 316</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2212,7 +2204,7 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>сразу под краном слива BV-1 — выход в горизонталь</t>
+          <t>2-й: вбок V-S1 на бочку (через переход 50,5 → 25), прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -2232,34 +2224,34 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
       <c r="J41" s="9" t="n"/>
     </row>
-    <row r="42" ht="57" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="13" t="n">
         <v>34</v>
       </c>
       <c r="B42" s="14" t="n"/>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>1-й после отвода под BV-1: отвод 45° вниз — проба SP-1 (через переход 50,5 → 25), суспензия не застаивается; запас на оба тройника 45° — здесь</t>
+          <t>отводы тройников → SP-1 и V-S1</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G42" s="16" t="inlineStr">
@@ -2274,34 +2266,38 @@
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
       <c r="J42" s="15" t="n"/>
     </row>
-    <row r="43" ht="43.5" customHeight="1">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B43" s="8" t="n"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>SP-1, V-S1</t>
+        </is>
+      </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>2-й: вбок V-S1 на бочку (через переход 50,5 → 25), прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
+          <t>SP-1 — проба, V-S1 — бочка растворителя</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -2316,41 +2312,41 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J43" s="9" t="n"/>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="16.5" customHeight="1">
       <c r="A44" s="13" t="n">
         <v>36</v>
       </c>
       <c r="B44" s="14" t="n"/>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>отводы тройников → SP-1 и V-S1</t>
+          <t>носик пробоотбора после SP-1</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -2358,43 +2354,39 @@
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: отвод кламп</t>
         </is>
       </c>
       <c r="J44" s="15" t="n"/>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" ht="43.5" customHeight="1">
       <c r="A45" s="7" t="n">
         <v>37</v>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>SP-1, V-S1</t>
+          <t>P-2</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>SP-1 — проба, V-S1 — бочка растворителя</t>
+          <t>выгрузка суспензии на нутч</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -2404,39 +2396,39 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
       <c r="J45" s="9" t="n"/>
     </row>
-    <row r="46" ht="16.5" customHeight="1">
+    <row r="46" ht="43.5" customHeight="1">
       <c r="A46" s="13" t="n">
         <v>38</v>
       </c>
       <c r="B46" s="14" t="n"/>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>носик пробоотбора после SP-1</t>
+          <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
@@ -2446,39 +2438,39 @@
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
+          <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
       <c r="J46" s="15" t="n"/>
     </row>
-    <row r="47" ht="43.5" customHeight="1">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>P-2</t>
-        </is>
-      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="n"/>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>К50,5 × ¼″ BSP вн.</t>
+        </is>
+      </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>выгрузка суспензии на нутч</t>
+          <t>P-2: вход и выход → рукав 1″</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
@@ -2488,29 +2480,29 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
       <c r="J47" s="9" t="n"/>
     </row>
-    <row r="48" ht="43.5" customHeight="1">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="13" t="n">
         <v>40</v>
       </c>
       <c r="B48" s="14" t="n"/>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>¼″ NPT × ¼″ BSP</t>
+          <t>К50,5 × 25,4</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
+          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -2520,7 +2512,7 @@
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -2530,39 +2522,39 @@
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>Rizur: ниппель RizurLok-NP</t>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
         </is>
       </c>
       <c r="J48" s="15" t="n"/>
     </row>
-    <row r="49" ht="30" customHeight="1">
+    <row r="49" ht="43.5" customHeight="1">
       <c r="A49" s="7" t="n">
         <v>41</v>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>P-2: вход и выход → рукав 1″</t>
+          <t>слив → P-2 (1,5 м), P-2 → нутч (2,5 м); хомуты 32–50; армирование — чтобы не сплющивался на всасе</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -2572,81 +2564,55 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
       <c r="J49" s="9" t="n"/>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="14" t="n"/>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>К50,5 × 25,4</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
-        </is>
-      </c>
-      <c r="J50" s="15" t="n"/>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="6" t="n"/>
     </row>
     <row r="51" ht="43.5" customHeight="1">
       <c r="A51" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>слив → P-2 (1,5 м), P-2 → нутч (2,5 м); хомуты 32–50; армирование — чтобы не сплющивался на всасе</t>
+          <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -2656,55 +2622,81 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
       <c r="J51" s="9" t="n"/>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="6" t="n"/>
-    </row>
-    <row r="53" ht="43.5" customHeight="1">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="B52" s="14" t="n"/>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 → К25</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
+        </is>
+      </c>
+      <c r="J52" s="15" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="7" t="n">
         <v>44</v>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
+          <t>крышка нутча и низ нутча</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
@@ -2714,7 +2706,7 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
       <c r="J53" s="9" t="n"/>
@@ -2726,17 +2718,17 @@
       <c r="B54" s="14" t="n"/>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
+          <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -2746,7 +2738,7 @@
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -2756,41 +2748,41 @@
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
       <c r="J54" s="15" t="n"/>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" ht="16.5" customHeight="1">
       <c r="A55" s="7" t="n">
         <v>46</v>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>крышка нутча и низ нутча</t>
+          <t>видно уровень суспензии</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -2798,7 +2790,7 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: диоптр кламп</t>
         </is>
       </c>
       <c r="J55" s="9" t="n"/>
@@ -2807,20 +2799,24 @@
       <c r="A56" s="13" t="n">
         <v>47</v>
       </c>
-      <c r="B56" s="14" t="n"/>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>F-1</t>
+        </is>
+      </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>К119 → К64</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
+          <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -2830,7 +2826,7 @@
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -2840,19 +2836,19 @@
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
       <c r="J56" s="15" t="n"/>
     </row>
-    <row r="57" ht="16.5" customHeight="1">
+    <row r="57" ht="43.5" customHeight="1">
       <c r="A57" s="7" t="n">
         <v>48</v>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -2862,7 +2858,7 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>видно уровень суспензии</t>
+          <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -2882,7 +2878,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: диоптр кламп</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
       <c r="J57" s="9" t="n"/>
@@ -2891,34 +2887,30 @@
       <c r="A58" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>F-1</t>
-        </is>
-      </c>
+      <c r="B58" s="14" t="n"/>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
+          <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -2928,29 +2920,33 @@
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
       <c r="J58" s="15" t="n"/>
     </row>
-    <row r="59" ht="43.5" customHeight="1">
+    <row r="59" ht="30" customHeight="1">
       <c r="A59" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B59" s="8" t="n"/>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>PI-5</t>
+        </is>
+      </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
+          <t>на отвод тройника гребёнки</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -2960,7 +2956,7 @@
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -2970,7 +2966,7 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
       <c r="J59" s="9" t="n"/>
@@ -2979,10 +2975,14 @@
       <c r="A60" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="B60" s="14" t="n"/>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>PSV-4</t>
+        </is>
+      </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
+          <t>на тройник гребёнки; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: предохр. клапан угловой кламп</t>
         </is>
       </c>
       <c r="J60" s="15" t="n"/>
@@ -3021,24 +3021,20 @@
       <c r="A61" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>PI-5</t>
-        </is>
-      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>на отвод тройника гребёнки</t>
+          <t>выход PSV-4 → граница с коллектором сбросов смежников</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -3058,7 +3054,7 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
       <c r="J61" s="9" t="n"/>
@@ -3069,12 +3065,12 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>PSV-4</t>
+          <t>VV-2</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
@@ -3084,7 +3080,7 @@
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>на тройник гребёнки; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
+          <t>вакуум нутча</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -3104,7 +3100,7 @@
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: предохр. клапан угловой кламп</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J62" s="15" t="n"/>
@@ -3116,17 +3112,17 @@
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>выход PSV-4 → граница с коллектором сбросов смежников</t>
+          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -3136,7 +3132,7 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
@@ -3157,7 +3153,7 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>VV-2</t>
+          <t>V-F2</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
@@ -3172,7 +3168,7 @@
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>вакуум нутча</t>
+          <t>выход нутча (фильтрат)</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -3204,27 +3200,27 @@
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
+          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -3234,114 +3230,110 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
       <c r="J65" s="9" t="n"/>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="13" t="n">
-        <v>57</v>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>V-F2</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>выход нутча (фильтрат)</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G66" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J66" s="15" t="n"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="6" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>P-4</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>фильтрат нутча → F-2</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="13" t="n">
         <v>58</v>
       </c>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>Хомут-держатель для труб нерж.</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>по Ø: ½″, 3″, K119</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="H67" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут-держатель</t>
-        </is>
-      </c>
-      <c r="J67" s="9" t="n"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="6" t="n"/>
+      <c r="B68" s="14" t="n"/>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+      <c r="J68" s="15" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="7" t="n">
@@ -3349,18 +3341,22 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>P-4</t>
+          <t>F-2</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="n"/>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>фильтрат нутча → F-2</t>
+          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+          <t>Гросснер: корпус 10″</t>
         </is>
       </c>
       <c r="J69" s="9" t="n"/>
@@ -3392,27 +3388,27 @@
       <c r="B70" s="14" t="n"/>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
+          <t>по 2 шт. каждого рейтинга</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
@@ -3422,7 +3418,7 @@
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Гросснер: патроны</t>
         </is>
       </c>
       <c r="J70" s="15" t="n"/>
@@ -3431,34 +3427,30 @@
       <c r="A71" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>F-2</t>
-        </is>
-      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>под корпус 10″</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
+          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -3468,7 +3460,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: корпус 10″</t>
+          <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
       <c r="J71" s="9" t="n"/>
@@ -3477,30 +3469,34 @@
       <c r="A72" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="B72" s="14" t="n"/>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>V-F3</t>
+        </is>
+      </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>по 2 шт. каждого рейтинга</t>
+          <t>выход F-2 → налив</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
@@ -3510,114 +3506,110 @@
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
       <c r="J72" s="15" t="n"/>
     </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="7" t="n">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Сжатый воздух к насосам P-2, P-4</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="6" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>под корпус 10″</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>вход воздуха насоса (по 1 на насос)</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B75" s="14" t="n"/>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="13" t="n">
-        <v>64</v>
-      </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>V-F3</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E74" s="15" t="inlineStr">
-        <is>
-          <t>выход F-2 → налив</t>
-        </is>
-      </c>
-      <c r="F74" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H74" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-      <c r="J74" s="15" t="n"/>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>Сжатый воздух к насосам P-2, P-4</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="6" t="n"/>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+      <c r="J75" s="15" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -3626,27 +3618,27 @@
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
+          <t>G¼ × 8</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>вход воздуха насоса (по 1 на насос)</t>
+          <t>выход регулятора и кламп ¼″ у насоса</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
@@ -3656,7 +3648,7 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>Rizur: ниппель переходной</t>
+          <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
       <c r="J76" s="9" t="n"/>
@@ -3668,27 +3660,27 @@
       <c r="B77" s="14" t="n"/>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
+          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>G¼</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
+          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -3698,7 +3690,7 @@
       </c>
       <c r="I77" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
       <c r="J77" s="15" t="n"/>
@@ -3710,142 +3702,142 @@
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>G¼ × 8</t>
+          <t>по порту</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>выход регулятора и кламп ¼″ у насоса</t>
+          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>BB-Engineering: S6510 8-1/4</t>
+          <t>Гросснер: ёлочка НР</t>
         </is>
       </c>
       <c r="J78" s="9" t="n"/>
     </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="13" t="n">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости соединений, кроме гребёнки реактора — она есть)</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="6" t="n"/>
+    </row>
+    <row r="80" ht="16.5" customHeight="1">
+      <c r="A80" s="7" t="n">
         <v>68</v>
-      </c>
-      <c r="B79" s="14" t="n"/>
-      <c r="C79" s="15" t="inlineStr">
-        <is>
-          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>G¼</t>
-        </is>
-      </c>
-      <c r="E79" s="15" t="inlineStr">
-        <is>
-          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
-        </is>
-      </c>
-      <c r="F79" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G79" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H79" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I79" s="17" t="inlineStr">
-        <is>
-          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
-        </is>
-      </c>
-      <c r="J79" s="15" t="n"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="7" t="n">
-        <v>69</v>
       </c>
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>по порту</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
+          <t>все соединения ½″, кроме гребёнки реактора</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H80" s="18" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H80" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: ёлочка НР</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
       <c r="J80" s="9" t="n"/>
     </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости соединений, кроме гребёнки реактора — она есть)</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="6" t="n"/>
-    </row>
-    <row r="82" ht="16.5" customHeight="1">
+    <row r="81" ht="43.5" customHeight="1">
+      <c r="A81" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="B81" s="14" t="n"/>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>штуцеры P1–P4, слив, тройники под BV-1 и на входе нутча, выгрузка, переходы колонн и нутча</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+      <c r="J81" s="15" t="n"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
       <c r="A82" s="7" t="n">
         <v>70</v>
       </c>
@@ -3857,22 +3849,22 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>все соединения ½″, кроме гребёнки реактора</t>
+          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
@@ -3887,34 +3879,34 @@
       </c>
       <c r="J82" s="9" t="n"/>
     </row>
-    <row r="83" ht="43.5" customHeight="1">
+    <row r="83" ht="30" customHeight="1">
       <c r="A83" s="13" t="n">
         <v>71</v>
       </c>
       <c r="B83" s="14" t="n"/>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>штуцеры P1–P4, слив, тройники под BV-1 и на входе нутча, выгрузка, переходы колонн и нутча</t>
+          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
         </is>
       </c>
       <c r="F83" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G83" s="16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -3924,7 +3916,7 @@
       </c>
       <c r="I83" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
         </is>
       </c>
       <c r="J83" s="15" t="n"/>
@@ -3936,27 +3928,27 @@
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -3966,7 +3958,7 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
       <c r="J84" s="9" t="n"/>
@@ -3978,27 +3970,27 @@
       <c r="B85" s="14" t="n"/>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
+          <t>где эфир и углеводороды: дозирование, слив, нутч и его гребёнка, вакуум, F-2</t>
         </is>
       </c>
       <c r="F85" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -4008,7 +4000,7 @@
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="J85" s="15" t="n"/>
@@ -4020,27 +4012,27 @@
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
+          <t>реактор P1–P4, слив, выгрузка, нутч</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -4050,39 +4042,39 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="J86" s="9" t="n"/>
     </row>
-    <row r="87" ht="30" customHeight="1">
+    <row r="87" ht="43.5" customHeight="1">
       <c r="A87" s="13" t="n">
         <v>75</v>
       </c>
       <c r="B87" s="14" t="n"/>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>где эфир и углеводороды: дозирование, слив, нутч и его гребёнка, вакуум, F-2</t>
+          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
         </is>
       </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G87" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
@@ -4092,7 +4084,7 @@
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
       <c r="J87" s="15" t="n"/>
@@ -4109,22 +4101,22 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>реактор P1–P4, слив, выгрузка, нутч</t>
+          <t>нутч: стыки переходов</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
@@ -4139,34 +4131,34 @@
       </c>
       <c r="J88" s="9" t="n"/>
     </row>
-    <row r="89" ht="43.5" customHeight="1">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" s="13" t="n">
         <v>77</v>
       </c>
       <c r="B89" s="14" t="n"/>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
         </is>
       </c>
       <c r="F89" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G89" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
@@ -4176,39 +4168,39 @@
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="J89" s="15" t="n"/>
     </row>
-    <row r="90" ht="30" customHeight="1">
+    <row r="90" ht="43.5" customHeight="1">
       <c r="A90" s="7" t="n">
         <v>78</v>
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>нутч: стыки переходов</t>
+          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2), NRV-3 (2)</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -4218,39 +4210,39 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
       <c r="J90" s="9" t="n"/>
     </row>
-    <row r="91" ht="30" customHeight="1">
+    <row r="91" ht="70.5" customHeight="1">
       <c r="A91" s="13" t="n">
         <v>79</v>
       </c>
       <c r="B91" s="14" t="n"/>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
+          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
         </is>
       </c>
       <c r="F91" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G91" s="16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -4260,12 +4252,12 @@
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
         </is>
       </c>
       <c r="J91" s="15" t="n"/>
     </row>
-    <row r="92" ht="43.5" customHeight="1">
+    <row r="92" ht="30" customHeight="1">
       <c r="A92" s="7" t="n">
         <v>80</v>
       </c>
@@ -4277,22 +4269,22 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2), NRV-3 (2)</t>
+          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
@@ -4307,76 +4299,50 @@
       </c>
       <c r="J92" s="9" t="n"/>
     </row>
-    <row r="93" ht="70.5" customHeight="1">
-      <c r="A93" s="13" t="n">
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="6" t="n"/>
+    </row>
+    <row r="94" ht="57" customHeight="1">
+      <c r="A94" s="7" t="n">
         <v>81</v>
-      </c>
-      <c r="B93" s="14" t="n"/>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
-        </is>
-      </c>
-      <c r="F93" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G93" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H93" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
-        </is>
-      </c>
-      <c r="J93" s="15" t="n"/>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="7" t="n">
-        <v>82</v>
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
+          <t>все линии K25 на ёлочках K25 × 19,05: верх E-1 → гребёнка, гребёнка нутча, V-F2 → P-4, P-4 → F-2, бочка → V-S1, F-2 → канистра, вакуум, vent, NRV-6 → G-1; хомуты 25–40</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>≈16,5 м</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -4386,55 +4352,81 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
       <c r="J94" s="9" t="n"/>
     </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="5" t="n"/>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="6" t="n"/>
-    </row>
-    <row r="96" ht="57" customHeight="1">
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="B95" s="14" t="n"/>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>концы рукавов ¾″ (18)</t>
+        </is>
+      </c>
+      <c r="F95" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G95" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 19,05</t>
+        </is>
+      </c>
+      <c r="J95" s="15" t="n"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
       <c r="A96" s="7" t="n">
         <v>83</v>
       </c>
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>все линии K25 на ёлочках K25 × 19,05: верх E-1 → гребёнка, гребёнка нутча, V-F2 → P-4, P-4 → F-2, бочка → V-S1, F-2 → канистра, вакуум, vent, NRV-6 → G-1; хомуты 25–40</t>
+          <t>по 2 на конец рукава: PF ¼″ на P-1 (по 1) / TSO ¾″ / TSO 1″</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>≈16,5 м</t>
+          <t>2 / 36 / 8</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>4 / 38 / 10</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
@@ -4444,39 +4436,39 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
       <c r="J96" s="9" t="n"/>
     </row>
-    <row r="97" ht="30" customHeight="1">
+    <row r="97" ht="43.5" customHeight="1">
       <c r="A97" s="13" t="n">
         <v>84</v>
       </c>
       <c r="B97" s="14" t="n"/>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>12 мм / ¼″</t>
         </is>
       </c>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>концы рукавов ¾″ (18)</t>
+          <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
         </is>
       </c>
       <c r="F97" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>≈10</t>
         </is>
       </c>
       <c r="G97" s="16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>≈12</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -4486,165 +4478,43 @@
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
-        </is>
-      </c>
-      <c r="J97" s="15" t="n"/>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B98" s="8" t="n"/>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Хомут червячный нерж.</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>8–12 / 25–40 / 32–50</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>по 2 на конец рукава: PF ¼″ на P-1 (по 1) / TSO ¾″ / TSO 1″</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>2 / 36 / 8</t>
-        </is>
-      </c>
-      <c r="G98" s="10" t="inlineStr">
-        <is>
-          <t>4 / 38 / 10</t>
-        </is>
-      </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I98" s="12" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут червячный</t>
-        </is>
-      </c>
-      <c r="J98" s="9" t="n"/>
-    </row>
-    <row r="99" ht="43.5" customHeight="1">
-      <c r="A99" s="13" t="n">
-        <v>86</v>
-      </c>
-      <c r="B99" s="14" t="n"/>
-      <c r="C99" s="15" t="inlineStr">
-        <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>12 мм / ¼″</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
-        </is>
-      </c>
-      <c r="F99" s="14" t="inlineStr">
-        <is>
-          <t>≈10</t>
-        </is>
-      </c>
-      <c r="G99" s="16" t="inlineStr">
-        <is>
-          <t>≈12</t>
-        </is>
-      </c>
-      <c r="H99" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
-      <c r="J99" s="17" t="inlineStr">
+      <c r="J97" s="17" t="inlineStr">
         <is>
           <t>fluid-line.ru</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Шина и кабели заземления с зажимами-крокодилами</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>заземление R-1, P-2, F-1, F-2, канистр (5–6 точек)</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="G100" s="10" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="H100" s="11" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I100" s="12" t="inlineStr">
-        <is>
-          <t>ПромНагрев: заземление бочек</t>
-        </is>
-      </c>
-      <c r="J100" s="9" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="19" t="inlineStr">
-        <is>
-          <t>Позиций: 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="A103" s="20" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>Позиций: 84</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="20" t="inlineStr">
         <is>
           <t>Статус: КУПИТЬ — заказывать; УТОЧНИТЬ — сначала замер / уточнение у поставщика; W-2 — использовать весы W-2. Ссылки кликабельны и по возможности открывают карточку сразу с нужным вариантом (размер, AISI 316).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J100"/>
+  <autoFilter ref="A4:J97"/>
   <mergeCells count="11">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A103:J103"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="A81:J81"/>
-    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A93:J93"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A73:J73"/>
     <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A66:J66"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
@@ -4669,79 +4539,74 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Сводная к заказу" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$96</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$81</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="57" customHeight="1">
       <c r="A20" s="11" t="n">
         <v>17</v>
       </c>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>V-1 → головка P-1 → штуцер K25 × 6,35; толщину стенки сверить с головкой</t>
+          <t>одним шлангом ID 6,4 на всей линии: канистра V-1 → головка P-1 (1 м) → K25 × 6,35 … V-P1 → NRV-6 → K25 × 6,35 → вход G-1 (1,5 м); толщину стенки сверить с головкой насоса</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>1 м</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>2 м</t>
+          <t>3,5 м</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>выход P-1 → кран V-P1; хомут червячный 8–12</t>
+          <t>выход P-1 → V-P1; NRV-6 → шланг; шланг → вход G-1 (переходник G¼″); хомуты червячные 8–12</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -1489,38 +1489,34 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="43.5" customHeight="1">
       <c r="A22" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>V-P1</t>
-        </is>
-      </c>
+      <c r="B22" s="12" t="n"/>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>ID 6 мм</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>после P-1</t>
+          <t>водный метиламин, щёлочь — EPDM стойкий; на ёлочки K25 × 6,35. Через головку перистальтики не идёт — там только силикон</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -1530,7 +1526,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
@@ -1540,1706 +1536,1710 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
+          <t>V-P1</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>после P-1</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: кран кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
           <t>NRV-6</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Клапан обратный кламп пружинный</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>нагнетание P-1 → G-1 (газ из G-1 не уходит назад в канистру)</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>Гросснер: клапан обратный кламп</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="4" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>C-1, C-2</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>К91 (3″) × 400</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>корпуса колонн, низ</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>C-1, C-2</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>К91 (3″), L ≈ 200</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>верх колонн — видно засыпку и фронт влаги</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
         <is>
           <t>Гросснер: диоптр кламп</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="43.5" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="7" t="inlineStr">
+    <row r="28" ht="43.5" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>К91 (3″)</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>опора засыпки: низ колонн — на нём лежат сита / NaOH; верх — прижим засыпки. В кламп-стык между двумя прокладками EPDM K91</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="13" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>К91 → К50,5</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>низ и верх каждой колонны (3″ → ½″ одной деталью у Гросснера нет)</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 91 × 50,5 316</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="7" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>К50,5 → К25</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>низ и верх каждой колонны, после перехода 3″ → 1″</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="43.5" customHeight="1">
-      <c r="A30" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="13" t="inlineStr">
+    <row r="31" ht="43.5" customHeight="1">
+      <c r="A31" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>К25 × ½″</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 9 — здесь</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>V-G2</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Кран шаровой под обжим 12 мм, нерж. 316, сёдла PTFE</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>12 мм</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Флюид-Лайн: краны шаровые инструментальные</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="84" customHeight="1">
-      <c r="A32" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
+    <row r="33" ht="84" customHeight="1">
+      <c r="A33" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>NRV-3</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>C-2 → V-G2 → NRV-3 → ввод газа T2: не пускает пары эфира / MeSiCl₃ из реактора назад в колонны и G-1. Ставится в трубку 10×12 через 2 переходника кламп → ½″ нар. + обжим 12 мм. Генератор держать ≈0,15–0,25 бар (ниже уставки PSV-3)</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
         <is>
           <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="7" t="inlineStr">
+    <row r="34" ht="16.5" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE 10×12, бухта</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>10×12</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>газ CH₃NH₂: V-G1 → C-1 → C-2 → T2</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>≈8 м</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>10 м</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Industriation: PTFE 12/10</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="13" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>Ø76</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>крепление C-1, C-2 к раме или стенду</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут для труб</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>сразу под краном слива BV-1 — выход в горизонталь</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Гросснер: отвод кламп 90°</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="57" customHeight="1">
-      <c r="A37" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="13" t="inlineStr">
+    <row r="38" ht="57" customHeight="1">
+      <c r="A38" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>1-й после отвода под BV-1: отвод 45° вниз — проба SP-1 (через переход 50,5 → 25), суспензия не застаивается; запас на оба тройника 45° — здесь</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="43.5" customHeight="1">
-      <c r="A38" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="7" t="inlineStr">
+    <row r="39" ht="43.5" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>2-й: вбок V-S1 на бочку (через переход 50,5 → 25), прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="13" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>К50,5 → К25</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>отводы тройников → SP-1 и V-S1</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>SP-1, V-S1</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>SP-1 — проба, V-S1 — бочка растворителя</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1">
-      <c r="A41" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="13" t="inlineStr">
+    <row r="42" ht="16.5" customHeight="1">
+      <c r="A42" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Отвод кламп 90°</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>носик пробоотбора после SP-1</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>Гросснер: отвод кламп</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="43.5" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="43.5" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>выгрузка суспензии на нутч</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="43.5" customHeight="1">
-      <c r="A43" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="13" t="inlineStr">
+    <row r="44" ht="43.5" customHeight="1">
+      <c r="A44" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="7" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>P-2: вход и выход → рукав 1″</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="13" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>К50,5 × 25,4</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K50,5 × 25,4</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="43.5" customHeight="1">
-      <c r="A46" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="7" t="inlineStr">
+    <row r="47" ht="43.5" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>слив → P-2 (1,5 м), P-2 → нутч (2,5 м); хомуты 32–50; армирование — чтобы не сплющивался на всасе</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="4" t="n"/>
-    </row>
-    <row r="48" ht="43.5" customHeight="1">
-      <c r="A48" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="4" t="n"/>
+    </row>
+    <row r="49" ht="43.5" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="13" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>К50,5 → К25</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="7" t="inlineStr">
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>К64 → К50,5</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>крышка нутча и низ нутча</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="13" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>К119 → К64</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1">
-      <c r="A52" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="7" t="inlineStr">
+    <row r="53" ht="16.5" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>видно уровень суспензии</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Гросснер: диоптр кламп</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>F-1</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>К119 (4″) × 500</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="43.5" customHeight="1">
-      <c r="A54" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="7" t="inlineStr">
+    <row r="55" ht="43.5" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="13" t="inlineStr">
+    <row r="56" ht="43.5" customHeight="1">
+      <c r="A56" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Ø ≈ 110 мм</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>фильтрующий слой нутча под Na₂SO₄ (сетка фильтра 0,5 мм сама осадок не держит); расходник — по 1 кругу на партию</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>отрез 0,5 м²</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>КемИнС: фильтровальные ткани PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>гребёнка нутча: PI-5, PSV-4, VV-2</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>PI-5</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>на отвод тройника гребёнки</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
         <is>
           <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>PSV-4</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>на тройник гребёнки; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>Гросснер: предохр. клапан угловой кламп</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="7" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>К25 × ½″</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>выход PSV-4 → граница с коллектором сбросов смежников</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>VV-2</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>вакуум нутча</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I59" s="15" t="inlineStr">
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="7" t="inlineStr">
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>К25 × ¼″</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="G62" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>V-F2</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>выход нутча (фильтрат)</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G61" s="14" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I61" s="15" t="inlineStr">
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="7" t="inlineStr">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>крепление гребёнки нутча и нутча к раме — по месту</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
-      <c r="J63" s="4" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>P-4</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>фильтрат нутча → F-2</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="13" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
-        </is>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>К25 × ¼″ BSP вн.</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
-        </is>
-      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="4" t="n"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="n">
@@ -3247,22 +3247,18 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>F-2</t>
+          <t>P-4</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>10″</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="n"/>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
+          <t>фильтрат нутча → F-2</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -3282,7 +3278,7 @@
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: корпус 10″</t>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
@@ -3293,27 +3289,27 @@
       <c r="B67" s="12" t="n"/>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>по 2 шт. каждого рейтинга</t>
+          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
@@ -3323,7 +3319,7 @@
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
@@ -3331,30 +3327,34 @@
       <c r="A68" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B68" s="6" t="n"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>F-2</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>под корпус 10″</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
+          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
+          <t>Гросснер: корпус 10″</t>
         </is>
       </c>
     </row>
@@ -3372,144 +3372,144 @@
       <c r="A69" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B69" s="12" t="n"/>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>по 2 шт. каждого рейтинга</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: патроны</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>под корпус 10″</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Hydrohype: кольца в оболочке FEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>V-F3</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>выход F-2 → налив</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G69" s="14" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I69" s="15" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Сжатый воздух к насосам P-2, P-4</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="3" t="n"/>
-      <c r="I70" s="3" t="n"/>
-      <c r="J70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>вход воздуха насоса (по 1 на насос)</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель переходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
-        </is>
-      </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>К25 × ¼″ BSP вн.</t>
-        </is>
-      </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
-        </is>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G72" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
-        </is>
-      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
+      <c r="J72" s="4" t="n"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="n">
@@ -3518,27 +3518,27 @@
       <c r="B73" s="6" t="n"/>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>G¼ × 8</t>
+          <t>⅛″ NPT × ¼″ BSP</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>выход регулятора и кламп ¼″ у насоса</t>
+          <t>вход воздуха насоса (по 1 на насос)</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>BB-Engineering: S6510 8-1/4</t>
+          <t>Rizur: ниппель переходной</t>
         </is>
       </c>
     </row>
@@ -3559,27 +3559,27 @@
       <c r="B74" s="12" t="n"/>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>G¼</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
+          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
@@ -3600,139 +3600,139 @@
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
+          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>по порту</t>
+          <t>G¼ × 8</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
+          <t>выход регулятора и кламп ¼″ у насоса</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>BB-Engineering: S6510 8-1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>G¼</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="G76" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H75" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: ёлочка НР</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости соединений, кроме гребёнки реактора — она есть)</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
-      <c r="J76" s="4" t="n"/>
-    </row>
-    <row r="77" ht="16.5" customHeight="1">
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
       <c r="A77" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B77" s="6" t="n"/>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>по порту</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>все соединения ½″, кроме гребёнки реактора</t>
+          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="43.5" customHeight="1">
-      <c r="A78" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>штуцеры P1–P4, слив, тройники под BV-1 и на входе нутча, выгрузка, переходы колонн и нутча</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G78" s="14" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I78" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
+          <t>Гросснер: ёлочка НР</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости; без реактора — на штуцерах P1–P4 родные клампы, без E-1, гребёнки реактора и VP-1)</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
+      <c r="J78" s="4" t="n"/>
+    </row>
+    <row r="79" ht="16.5" customHeight="1">
       <c r="A79" s="5" t="n">
         <v>70</v>
       </c>
@@ -3744,22 +3744,22 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
+          <t>все соединения ½″ нашей обвязки</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -3780,27 +3780,27 @@
       <c r="B80" s="12" t="n"/>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
+          <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, выгрузка P-2, переходы колонн и нутча</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -3821,27 +3821,27 @@
       <c r="B81" s="6" t="n"/>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
+          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -3862,27 +3862,27 @@
       <c r="B82" s="12" t="n"/>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>где эфир и углеводороды: дозирование, слив, нутч и его гребёнка, вакуум, F-2</t>
+          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
         </is>
       </c>
     </row>
@@ -3903,27 +3903,27 @@
       <c r="B83" s="6" t="n"/>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>реактор P1–P4, слив, выгрузка, нутч</t>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
     </row>
@@ -3944,27 +3944,27 @@
       <c r="B84" s="12" t="n"/>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
+          <t>где эфир и углеводороды: дозирование, слив и проба, выгрузка, нутч и его гребёнка, вакуум нутча, P-4, F-2</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -3990,22 +3990,22 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>нутч: стыки переходов</t>
+          <t>BV-1 → отвод, тройники 45° и прямой, переходы 50,5/25, выгрузка P-2, нутч</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
@@ -4019,34 +4019,34 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="30" customHeight="1">
+    <row r="86" ht="43.5" customHeight="1">
       <c r="A86" s="11" t="n">
         <v>77</v>
       </c>
       <c r="B86" s="12" t="n"/>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
+          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
@@ -4056,38 +4056,38 @@
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="43.5" customHeight="1">
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
       <c r="A87" s="5" t="n">
         <v>78</v>
       </c>
       <c r="B87" s="6" t="n"/>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2), NRV-3 (2)</t>
+          <t>нутч: стыки переходов</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
@@ -4097,38 +4097,38 @@
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="70.5" customHeight="1">
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
       <c r="A88" s="11" t="n">
         <v>79</v>
       </c>
       <c r="B88" s="12" t="n"/>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
@@ -4138,11 +4138,11 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="30" customHeight="1">
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="43.5" customHeight="1">
       <c r="A89" s="5" t="n">
         <v>80</v>
       </c>
@@ -4154,22 +4154,22 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
+          <t>без углеводородов: G-1 и PSV-3 (7), P-1 → G-1 (3), колонны (4), воздух насосов (2), NRV-3 (2)</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
@@ -4183,50 +4183,75 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="4" t="n"/>
-    </row>
-    <row r="91" ht="57" customHeight="1">
+    <row r="90" ht="70.5" customHeight="1">
+      <c r="A90" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="B90" s="12" t="n"/>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
       <c r="A91" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>все линии K25 на ёлочках K25 × 19,05: верх E-1 → гребёнка, гребёнка нутча, V-F2 → P-4, P-4 → F-2, бочка → V-S1, F-2 → канистра, вакуум, vent, NRV-6 → G-1; хомуты 25–40</t>
+          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>≈16,5 м</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
@@ -4236,79 +4261,54 @@
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="11" t="n">
-        <v>82</v>
-      </c>
-      <c r="B92" s="12" t="n"/>
-      <c r="C92" s="13" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
-        </is>
-      </c>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>К25 × 19,05</t>
-        </is>
-      </c>
-      <c r="E92" s="13" t="inlineStr">
-        <is>
-          <t>концы рукавов ¾″ (18)</t>
-        </is>
-      </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G92" s="14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I92" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="30" customHeight="1">
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
+      <c r="D92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="4" t="n"/>
+    </row>
+    <row r="93" ht="70.5" customHeight="1">
       <c r="A93" s="5" t="n">
         <v>83</v>
       </c>
       <c r="B93" s="6" t="n"/>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>по 2 на конец рукава: PF ¼″ на P-1 (по 1) / TSO ¾″ / TSO 1″</t>
+          <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м; хомуты 25–40</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>2 / 36 / 8</t>
+          <t>≈10 м</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>4 / 38 / 10</t>
+          <t>13 м</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -4329,57 +4329,139 @@
       <c r="B94" s="12" t="n"/>
       <c r="C94" s="13" t="inlineStr">
         <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 19,05</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Хомут червячный нерж.</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>8–12 / 25–40 / 32–50</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (11) / рукава 1″ (4)</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>6 / 22 / 8</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>8 / 24 / 10</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут червячный</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="43.5" customHeight="1">
+      <c r="A96" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="B96" s="12" t="n"/>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="D94" s="12" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="E94" s="13" t="inlineStr">
+      <c r="E96" s="13" t="inlineStr">
         <is>
           <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
         </is>
       </c>
-      <c r="F94" s="12" t="inlineStr">
+      <c r="F96" s="12" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="G94" s="14" t="inlineStr">
+      <c r="G96" s="14" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="H94" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
-      <c r="J94" s="16" t="inlineStr">
+      <c r="J96" s="16" t="inlineStr">
         <is>
           <t>fluid-line.ru</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J96"/>
   <mergeCells count="9">
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A92:J92"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A65:J65"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A72:J72"/>
     <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A90:J90"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A25:J25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
@@ -4407,7 +4489,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId29"/>
@@ -4417,7 +4499,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId39"/>
@@ -4428,7 +4510,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
@@ -4443,19 +4525,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId77"/>
@@ -4467,11 +4549,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4492,7 +4576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5622,12 +5706,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -5662,12 +5746,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -6142,12 +6226,12 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -6182,12 +6266,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6262,12 +6346,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2 / 36 / 8</t>
+          <t>6 / 22 / 8</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>4 / 38 / 10</t>
+          <t>8 / 24 / 10</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6422,12 +6506,12 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>1 м</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>2 м</t>
+          <t>3,5 м</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -6502,12 +6586,12 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>≈16,5 м</t>
+          <t>≈10 м</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>13 м</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6542,12 +6626,12 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6622,12 +6706,12 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -7034,7 +7118,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Ампика</t>
+          <t>Titan Lock</t>
         </is>
       </c>
       <c r="B68" s="3" t="n"/>
@@ -7051,23 +7135,27 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="n"/>
+          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>ID 6 мм</t>
+        </is>
+      </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -7077,14 +7165,14 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+          <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Пневмо-Электро</t>
+          <t>Ампика</t>
         </is>
       </c>
       <c r="B70" s="3" t="n"/>
@@ -7095,33 +7183,29 @@
       <c r="G70" s="3" t="n"/>
       <c r="H70" s="4" t="n"/>
     </row>
-    <row r="71" ht="16.5" customHeight="1">
+    <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="n">
         <v>62</v>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>¼″</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1 / дозирование</t>
+          <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>≈3 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -7131,14 +7215,14 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>Пневмо-Электро: трубки PTFE</t>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Профрезина</t>
+          <t>КемИнС</t>
         </is>
       </c>
       <c r="B72" s="3" t="n"/>
@@ -7149,50 +7233,50 @@
       <c r="G72" s="3" t="n"/>
       <c r="H72" s="4" t="n"/>
     </row>
-    <row r="73" ht="43.5" customHeight="1">
+    <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="n">
         <v>63</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
+          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>500×500×3</t>
+          <t>Ø ≈ 110 мм</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>1 лист</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>2 листа</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>отрез 0,5 м²</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Профрезина: техпластина EPDM 500×500×3</t>
+          <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Флюид-Лайн</t>
+          <t>Пневмо-Электро</t>
         </is>
       </c>
       <c r="B74" s="3" t="n"/>
@@ -7203,136 +7287,246 @@
       <c r="G74" s="3" t="n"/>
       <c r="H74" s="4" t="n"/>
     </row>
-    <row r="75" ht="30" customHeight="1">
+    <row r="75" ht="16.5" customHeight="1">
       <c r="A75" s="5" t="n">
         <v>64</v>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
+          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>¼″</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Реактор R-1 / дозирование</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>≈3 м</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>5 м</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро: трубки PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Профрезина</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="4" t="n"/>
+    </row>
+    <row r="77" ht="43.5" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>500×500×3</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Генератор G-1</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>1 лист</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>2 листа</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Профрезина: техпластина EPDM 500×500×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Флюид-Лайн</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="4" t="n"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
           <t>Игольчатый вентиль ¼″ под обжим, нерж., PTFE-сальник</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>¼″</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>FV-1: Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>Флюид-Лайн: игольчатые вентили</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой под обжим 12 мм, нерж. 316, сёдла PTFE</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
+      <c r="C80" s="12" t="inlineStr">
         <is>
           <t>12 мм</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>V-G2: Колонны C-1, C-2</t>
         </is>
       </c>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F76" s="14" t="inlineStr">
+      <c r="F80" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
         <is>
           <t>Флюид-Лайн: краны шаровые инструментальные</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>Обратный клапан ¼″ нерж., уплотнение PTFE/FFKM (не FKM)</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>¼″</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>NRV-4: Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>Флюид-Лайн: обратные клапаны Hy-Lok</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H77"/>
-  <mergeCells count="10">
+  <autoFilter ref="A1:H81"/>
+  <mergeCells count="12">
     <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A78:H78"/>
     <mergeCell ref="A55:H55"/>
     <mergeCell ref="A59:H59"/>
     <mergeCell ref="A65:H65"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A63:H63"/>
     <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A74:H74"/>
@@ -7402,8 +7596,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$96</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -238,10 +238,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -828,17 +828,17 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Игольчатый вентиль ¼″ под обжим, нерж., PTFE-сальник</t>
+          <t>Кран игольчатый нерж. AISI 316, внутр. резьба ¼″, PN 413 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>¼″</t>
+          <t>¼″ ВР</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>регулировка подачи P-3 → реактор</t>
+          <t>регулировка подачи P-3 → реактор; на трубку ¼″ — 2 обжимных фитинга ¼″ × ¼″ нар.</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -858,16 +858,11 @@
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>Флюид-Лайн: игольчатые вентили</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>grossner.ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>Гросснер: кран игольчатый ¼″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="43.5" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
@@ -878,17 +873,17 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Обратный клапан ¼″ нерж., уплотнение PTFE/FFKM (не FKM)</t>
+          <t>Клапан обратный муфтовый пружинный, AISI 316, внутр. резьба ¼″ (≈1 280 ₽)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>¼″</t>
+          <t>¼″ ВР (DN8)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>P-3 → реактор</t>
+          <t>P-3 → реактор: не пускает пары из реактора в линию дозирования; на трубку ¼″ — 2 обжимных фитинга ¼″ × ¼″ нар.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -908,12 +903,7 @@
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>Флюид-Лайн: обратные клапаны Hy-Lok</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>grossner.ru</t>
+          <t>Гросснер: клапан обратный муфтовый ¼″ 316</t>
         </is>
       </c>
     </row>
@@ -988,7 +978,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
@@ -998,7 +988,7 @@
           <t>Germeon: крышка DURAN GL45, 2 порта</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>wiegand.ru</t>
         </is>
@@ -1060,7 +1050,7 @@
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>altmaler.ru</t>
         </is>
@@ -1107,24 +1097,24 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="43.5" customHeight="1">
       <c r="A13" s="5" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Переходник нерж. резьба порта регулятора → кламп</t>
+          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>К25 × G1/2″</t>
+          <t>К25 × G½″ нар.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>порт регулятора (PSV-3, аргон A2, PI-3) — резьбу замерить</t>
+          <t>порт регулятора на крышке G-1 (гнездо G½″ вн.) → тройник К25 (PSV-3, аргон A2); резьбу уплотнить лентой PTFE</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1134,22 +1124,17 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>grossner.ru</t>
+          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1875,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="57" customHeight="1">
       <c r="A32" s="5" t="n">
         <v>28</v>
       </c>
@@ -1901,17 +1886,17 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой под обжим 12 мм, нерж. 316, сёдла PTFE</t>
+          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>12 мм</t>
+          <t>½″ ВР (DN15)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1</t>
+          <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1; на трубку 10×12 — 2 обжимных фитинга 12 мм × ½″ нар.</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -1931,7 +1916,7 @@
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>Флюид-Лайн: краны шаровые инструментальные</t>
+          <t>Гросснер: кран шаровой ½″ 316</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2855,7 @@
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="H56" s="17" t="inlineStr">
+      <c r="H56" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
@@ -3705,7 +3690,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H77" s="17" t="inlineStr">
+      <c r="H77" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
@@ -4404,7 +4389,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="43.5" customHeight="1">
+    <row r="96" ht="70.5" customHeight="1">
       <c r="A96" s="11" t="n">
         <v>86</v>
       </c>
@@ -4421,7 +4406,7 @@
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>газ CH₃NH₂ (10×12) и дозирование P-3 (¼″) — по месту</t>
+          <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -4442,11 +4427,6 @@
       <c r="I96" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
-        </is>
-      </c>
-      <c r="J96" s="16" t="inlineStr">
-        <is>
-          <t>fluid-line.ru</t>
         </is>
       </c>
     </row>
@@ -4468,94 +4448,90 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4576,7 +4552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4674,7 +4650,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
@@ -4851,17 +4827,17 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
+          <t>Клапан обратный муфтовый пружинный, AISI 316, внутр. резьба ¼″ (≈1 280 ₽)</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>¼″ ВР (DN8)</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>PSV-4: Нутч F-1</t>
+          <t>NRV-4: Реактор R-1 / дозирование</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -4871,7 +4847,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -4881,7 +4857,7 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: предохр. клапан угловой кламп</t>
+          <t>Гросснер: клапан обратный муфтовый ¼″ 316</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4867,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный угловой кламп, 0,3–0,5 бар</t>
+          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -4901,7 +4877,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>PSV-3: Генератор G-1</t>
+          <t>PSV-4: Нутч F-1</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4911,7 +4887,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -4925,23 +4901,23 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
+          <t>Клапан предохранительный угловой кламп, 0,3–0,5 бар</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>F-2: Фильтр F-2 / P-4</t>
+          <t>PSV-3: Генератор G-1</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -4951,7 +4927,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -4961,37 +4937,37 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: корпус 10″</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="57" customHeight="1">
+          <t>Гросснер: предохр. клапан угловой кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>V-P3: Реактор R-1 / дозирование; V-G1: Генератор G-1; V-P1: Генератор G-1; SP-1, V-S1: Слив BV-1 / выгрузка P-2; VV-2: Нутч F-1; V-F2: Нутч F-1; V-F3: Фильтр F-2 / P-4</t>
+          <t>F-2: Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -5001,7 +4977,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: корпус 10″</t>
         </is>
       </c>
     </row>
@@ -5011,17 +4987,17 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+          <t>Кран игольчатый нерж. AISI 316, внутр. резьба ¼″, PN 413 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>¼″ ВР</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>PI-5: Нутч F-1</t>
+          <t>FV-1: Реактор R-1 / дозирование</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -5031,7 +5007,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -5041,17 +5017,17 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1">
+          <t>Гросснер: кран игольчатый ¼″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="57" customHeight="1">
       <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5061,17 +5037,17 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>V-P3: Реактор R-1 / дозирование; V-G1: Генератор G-1; V-P1: Генератор G-1; SP-1, V-S1: Слив BV-1 / выгрузка P-2; VV-2: Нутч F-1; V-F2: Нутч F-1; V-F3: Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -5081,27 +5057,27 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1">
+          <t>Гросснер: кран кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°, AISI 316</t>
+          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>½″ ВР (DN15)</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>V-G2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -5121,7 +5097,7 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
+          <t>Гросснер: кран шаровой ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5131,27 +5107,27 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Фильтр F-2 / P-4</t>
+          <t>PI-5: Нутч F-1</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -5161,37 +5137,37 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Реактор R-1 / дозирование; Колонны C-1, C-2; Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -5201,39 +5177,39 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t>Гросснер: отвод кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+          <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>К119 → К64</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5241,7 +5217,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
+          <t>Гросснер: отвод кламп 90°</t>
         </is>
       </c>
     </row>
@@ -5251,27 +5227,27 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -5281,7 +5257,7 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: патроны</t>
         </is>
       </c>
     </row>
@@ -5291,27 +5267,27 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>К91 → К50,5</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Реактор R-1 / дозирование; Колонны C-1, C-2; Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -5321,7 +5297,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 91 × 50,5 316</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5331,17 +5307,17 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>К25 × G¼″ вн.</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -5351,7 +5327,7 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -5361,7 +5337,7 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
@@ -5371,17 +5347,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -5401,7 +5377,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
@@ -5411,27 +5387,27 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>К91 → К50,5</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Фильтр F-2 / P-4; Сжатый воздух</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -5441,7 +5417,7 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Гросснер: переход 91 × 50,5 316</t>
         </is>
       </c>
     </row>
@@ -5451,27 +5427,27 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 × G¼″ вн.</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1 / дозирование; Генератор G-1; Нутч F-1</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -5481,7 +5457,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
@@ -5491,27 +5467,27 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Генератор G-1; Колонны C-1, C-2; Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -5521,7 +5497,7 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
     </row>
@@ -5531,37 +5507,37 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Переходник нерж. резьба порта регулятора → кламп</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>К25 × G1/2″</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Фильтр F-2 / P-4; Сжатый воздух</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
@@ -5571,27 +5547,27 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К25 × G½″ нар.</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -5601,7 +5577,7 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5611,27 +5587,27 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Реактор R-1 / дозирование; Генератор G-1; Нутч F-1</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -5641,7 +5617,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
@@ -5651,27 +5627,27 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Генератор G-1; Колонны C-1, C-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -5681,7 +5657,7 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5667,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -5706,12 +5682,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -5721,7 +5697,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5707,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -5746,12 +5722,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -5761,7 +5737,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5747,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -5786,12 +5762,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -5801,7 +5777,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5792,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -5826,12 +5802,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -5851,7 +5827,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -5866,12 +5842,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -5881,7 +5857,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5891,27 +5867,27 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Ø76</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5921,7 +5897,7 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5931,27 +5907,27 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -5961,7 +5937,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5971,27 +5947,27 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 610 ₽)</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Генератор G-1; Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -6001,7 +5977,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
@@ -6011,27 +5987,27 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>Ø76</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -6041,7 +6017,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: хомут для труб</t>
         </is>
       </c>
     </row>
@@ -6051,27 +6027,27 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -6081,7 +6057,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
@@ -6091,27 +6067,27 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 610 ₽)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Генератор G-1; Нутч F-1</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -6121,7 +6097,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -6131,27 +6107,27 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -6161,7 +6137,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -6171,29 +6147,29 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6201,37 +6177,37 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16.5" customHeight="1">
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="11" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -6241,22 +6217,22 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16.5" customHeight="1">
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -6266,12 +6242,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6281,22 +6257,22 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16.5" customHeight="1">
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="11" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -6306,12 +6282,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -6321,22 +6297,22 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1">
       <c r="A45" s="5" t="n">
         <v>43</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -6346,12 +6322,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>6 / 22 / 8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>8 / 24 / 10</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6361,37 +6337,37 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="11" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>по Ø: ½″, 3″, K119</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -6401,27 +6377,27 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16.5" customHeight="1">
       <c r="A47" s="5" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″) × 400</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны C-1, C-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -6431,7 +6407,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6441,7 +6417,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6451,27 +6427,27 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6 / 22 / 8</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8 / 24 / 10</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6481,7 +6457,7 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
@@ -6491,27 +6467,27 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>3,5 м</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -6521,7 +6497,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6531,27 +6507,27 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>К91 (3″) × 400</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>C-1, C-2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -6561,7 +6537,7 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6571,27 +6547,27 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>F-1: Нутч F-1</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>≈10 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>13 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6601,7 +6577,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6611,27 +6587,27 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3,5 м</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6641,7 +6617,7 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6627,12 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -6666,12 +6642,12 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6681,7 +6657,7 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6691,434 +6667,460 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>DN ¾″ (ID 19)</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>вся установка</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>≈10 м</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>13 м</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: силикон армированный TSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>вся установка</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 19,05</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Слив BV-1 / выгрузка P-2</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
           <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>К25 × 6,35</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>BB-Engineering</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="4" t="n"/>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="4" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>G¼</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>G¼ × 8</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="43.5" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
+    <row r="61" ht="43.5" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>вся установка</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Germeon</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
-      <c r="G59" s="3" t="n"/>
-      <c r="H59" s="4" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="4" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>GL45 или по таре</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Germeon: крышка DURAN GL45, 2 порта</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Hydrohype</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="4" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>под корпус 10″</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Фильтр F-2 / P-4</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Industriation</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="4" t="n"/>
-    </row>
-    <row r="64" ht="16.5" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="4" t="n"/>
+    </row>
+    <row r="67" ht="16.5" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE 10×12, бухта</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>10×12</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Колонны C-1, C-2</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>≈8 м</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>10 м</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Industriation: PTFE 12/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Rizur</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n"/>
-      <c r="G65" s="3" t="n"/>
-      <c r="H65" s="4" t="n"/>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>¼″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель RizurLok-NP</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Сжатый воздух</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель переходной</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Titan Lock</t>
+          <t>Rizur</t>
         </is>
       </c>
       <c r="B68" s="3" t="n"/>
@@ -7131,405 +7133,364 @@
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>¼″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Слив BV-1 / выгрузка P-2</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель RizurLok-NP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Сжатый воздух</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Titan Lock</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
           <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>ID 6 мм</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Ампика</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
         </is>
       </c>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>КемИнС</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Ø ≈ 110 мм</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Нутч F-1</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr">
+      <c r="G76" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Пневмо-Электро</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="16.5" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="4" t="n"/>
+    </row>
+    <row r="78" ht="16.5" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>¼″</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>≈3 м</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>Пневмо-Электро: трубки PTFE</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Профрезина</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="4" t="n"/>
-    </row>
-    <row r="77" ht="43.5" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="4" t="n"/>
+    </row>
+    <row r="80" ht="43.5" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>500×500×3</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Флюид-Лайн</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="4" t="n"/>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Игольчатый вентиль ¼″ под обжим, нерж., PTFE-сальник</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>¼″</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>FV-1: Реактор R-1 / дозирование</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>Флюид-Лайн: игольчатые вентили</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="11" t="n">
-        <v>67</v>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>Кран шаровой под обжим 12 мм, нерж. 316, сёдла PTFE</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>12 мм</t>
-        </is>
-      </c>
-      <c r="D80" s="13" t="inlineStr">
-        <is>
-          <t>V-G2: Колонны C-1, C-2</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F80" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H80" s="15" t="inlineStr">
-        <is>
-          <t>Флюид-Лайн: краны шаровые инструментальные</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Обратный клапан ¼″ нерж., уплотнение PTFE/FFKM (не FKM)</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>¼″</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>NRV-4: Реактор R-1 / дозирование</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>Флюид-Лайн: обратные клапаны Hy-Lok</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H81"/>
-  <mergeCells count="12">
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A65:H65"/>
+  <autoFilter ref="A1:H80"/>
+  <mergeCells count="11">
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A64:H64"/>
     <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
@@ -7584,22 +7545,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -1588,7 +1588,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="43.5" customHeight="1">
+    <row r="25" ht="57" customHeight="1">
       <c r="A25" s="5" t="n">
         <v>21</v>
       </c>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>опора засыпки: низ колонн — на нём лежат сита / NaOH; верх — прижим засыпки. В кламп-стык между двумя прокладками EPDM K91</t>
+          <t>опора засыпки: низ C-1 и C-2 — на нём лежат сита / NaOH (сверху засыпку держит прокладка EPDM с сеткой на К50,5). В кламп-стык между двумя прокладками EPDM K91</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -3734,17 +3734,17 @@
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>колонны: 6 стыков + 4 на межкламповые фильтры</t>
+          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу)</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="70.5" customHeight="1">
+    <row r="87" ht="84" customHeight="1">
       <c r="A87" s="11" t="n">
         <v>78</v>
       </c>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
+          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — сверху держит засыпку (вместо межклампового фильтра), снизу и сверху задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="30" customHeight="1">
+    <row r="88" ht="43.5" customHeight="1">
       <c r="A88" s="5" t="n">
         <v>79</v>
       </c>
@@ -4103,17 +4103,17 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>колонны: 6 стыков + обе стороны межкламповых фильтров</t>
+          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу — по прокладке с каждой стороны фильтра)</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Сводная к заказу" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$92</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$78</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>штуцер P3 → V-P3 (запас на все 9 кранов ½″ — здесь)</t>
+          <t>штуцер P3 → V-P3 (запас на все 10 кранов ½″ — здесь)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 8 — здесь</t>
+          <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 7 — здесь</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="84" customHeight="1">
+    <row r="30" ht="97.5" customHeight="1">
       <c r="A30" s="11" t="n">
         <v>26</v>
       </c>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>C-2 → V-G2 → NRV-3 → ввод газа T2: не пускает пары эфира / MeSiCl₃ из реактора назад в колонны и G-1. Ставится в трубку 10×12 через 2 переходника кламп → ½″ нар. + обжим 12 мм. Генератор держать ≈0,15–0,25 бар (ниже уставки PSV-3)</t>
+          <t>C-2 → V-G2 → NRV-3 → ввод газа T2: не пускает пары эфира / MeSiCl₃ из реактора назад в колонны и G-1. Ставится в трубку 10×12 через 2 переходника кламп → ½″ нар. + обжим 12 мм. Генератор держать ≈0,15–0,25 бар (контроль по манометру G-1, лишнее — краном SV-G1 в коллектор)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>гребёнка нутча: PI-5, PSV-4, VV-2 (запас — здесь)</t>
+          <t>гребёнка нутча: PI-5, SV-F1, VV-2 (запас — здесь)</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2829,18 +2829,18 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
+    <row r="56" ht="57" customHeight="1">
       <c r="A56" s="5" t="n">
         <v>50</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>PSV-4</t>
+          <t>SV-F1</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>на тройник гребёнки; выход → переходник на резьбу (коллектор сбросов — у смежников)</t>
+          <t>сброс давления нутча вручную (вместо PSV-4): тройник гребёнки → кран → ёлочка → рукав ¾″ в коллектор сбросов (коллектор — у смежников)</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: предохр. клапан угловой кламп</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
@@ -2878,20 +2878,24 @@
       <c r="A57" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="B57" s="12" t="n"/>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>VV-2</t>
+        </is>
+      </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>выход PSV-4 → граница с коллектором сбросов смежников</t>
+          <t>вакуум нутча</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -2911,7 +2915,7 @@
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
@@ -2919,24 +2923,20 @@
       <c r="A58" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>VV-2</t>
-        </is>
-      </c>
+      <c r="B58" s="6" t="n"/>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>вакуум нутча</t>
+          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
@@ -2964,20 +2964,24 @@
       <c r="A59" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="B59" s="12" t="n"/>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>V-F2</t>
+        </is>
+      </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
+          <t>выход нутча (фильтрат)</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -2987,7 +2991,7 @@
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -2997,7 +3001,7 @@
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
@@ -3005,1172 +3009,1168 @@
       <c r="A60" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>V-F2</t>
-        </is>
-      </c>
+      <c r="B60" s="6" t="n"/>
       <c r="C60" s="7" t="inlineStr">
         <is>
+          <t>Хомут-держатель для труб нерж.</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>по Ø: ½″, 3″, K119</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут-держатель</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="4" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>P-4</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>фильтрат нутча → F-2</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>F-2</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: корпус 10″</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>по 2 шт. каждого рейтинга</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: патроны</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>под корпус 10″</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Hydrohype: кольца в оболочке FEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>V-F3</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>выход нутча (фильтрат)</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>выход F-2 → налив</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>Хомут-держатель для труб нерж.</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>по Ø: ½″, 3″, K119</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="inlineStr">
-        <is>
-          <t>1 компл.</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I61" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут-держатель</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
-      <c r="J62" s="4" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>P-4</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>фильтрат нутча → F-2</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Сжатый воздух к насосам P-2, P-4</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
+      <c r="J68" s="4" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>вход воздуха насоса (по 1 на насос)</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="12" t="n"/>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>G¼ × 8</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>выход регулятора и кламп ¼″ у насоса</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>BB-Engineering: S6510 8-1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>G¼</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>по порту</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H73" s="16" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: ёлочка НР</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости; без реактора — на штуцерах P1–P4 родные клампы, без E-1, гребёнки реактора и VP-1)</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="4" t="n"/>
+    </row>
+    <row r="75" ht="16.5" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>все соединения ½″ нашей обвязки</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, выгрузка P-2, переходы колонн и нутча</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>К64 (2″)</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="12" t="n"/>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>К91 (3″)</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу)</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="43.5" customHeight="1">
+      <c r="A80" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>где эфир и углеводороды: дозирование, слив и проба, выгрузка, нутч и его гребёнка, вакуум нутча, P-4, F-2</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>BV-1 → отвод, тройники 45° и прямой, переходы 50,5/25, выгрузка P-2, нутч</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="43.5" customHeight="1">
+      <c r="A82" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="B82" s="12" t="n"/>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I63" s="10" t="inlineStr">
-        <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="11" t="n">
-        <v>57</v>
-      </c>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="13" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>К25 × ¼″ BSP вн.</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>К64 (2″)</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>нутч: стыки переходов</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G64" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I64" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>F-2</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>10″</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: корпус 10″</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="11" t="n">
-        <v>59</v>
-      </c>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="13" t="inlineStr">
-        <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
-        </is>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>10″</t>
-        </is>
-      </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>по 2 шт. каждого рейтинга</t>
-        </is>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="12" t="n"/>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="43.5" customHeight="1">
+      <c r="A85" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>без углеводородов: P-1 → G-1 (4), порт G-1 → SV-G1 → рукав (2), выход газа и V-G1 (2), колонны (4), NRV-3 (2), воздух насосов (2)</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="84" customHeight="1">
+      <c r="A86" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" s="12" t="n"/>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — сверху держит засыпку (вместо межклампового фильтра), снизу и сверху задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="43.5" customHeight="1">
+      <c r="A87" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>К91 (3″)</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу — по прокладке с каждой стороны фильтра)</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: патроны</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>под корпус 10″</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
-        <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="11" t="n">
-        <v>61</v>
-      </c>
-      <c r="B68" s="12" t="inlineStr">
-        <is>
-          <t>V-F3</t>
-        </is>
-      </c>
-      <c r="C68" s="13" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E68" s="13" t="inlineStr">
-        <is>
-          <t>выход F-2 → налив</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Сжатый воздух к насосам P-2, P-4</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" s="3" t="n"/>
-      <c r="J69" s="4" t="n"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>вход воздуха насоса (по 1 на насос)</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель переходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="12" t="n"/>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t>К25 × ¼″ BSP вн.</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="inlineStr">
-        <is>
-          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>G¼ × 8</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>выход регулятора и кламп ¼″ у насоса</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I72" s="10" t="inlineStr">
-        <is>
-          <t>BB-Engineering: S6510 8-1/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>G¼</t>
-        </is>
-      </c>
-      <c r="E73" s="13" t="inlineStr">
-        <is>
-          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G73" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I73" s="15" t="inlineStr">
-        <is>
-          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>по порту</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H74" s="16" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: ёлочка НР</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости; без реактора — на штуцерах P1–P4 родные клампы, без E-1, гребёнки реактора и VP-1)</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
-      <c r="J75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="16.5" customHeight="1">
-      <c r="A76" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>все соединения ½″ нашей обвязки</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="13" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, выгрузка P-2, переходы колонн и нутча</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G77" s="14" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>К64 (2″)</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="13" t="inlineStr">
-        <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>К91 (3″)</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr">
-        <is>
-          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу)</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I79" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="43.5" customHeight="1">
-      <c r="A81" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E81" s="13" t="inlineStr">
-        <is>
-          <t>где эфир и углеводороды: дозирование, слив и проба, выгрузка, нутч и его гребёнка, вакуум нутча, P-4, F-2</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G81" s="14" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I81" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>BV-1 → отвод, тройники 45° и прямой, переходы 50,5/25, выгрузка P-2, нутч</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="4" t="n"/>
+    </row>
+    <row r="89" ht="84" customHeight="1">
+      <c r="A89" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>DN ¾″ (ID 19)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>≈14 м</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>18 м</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: силикон армированный TSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="43.5" customHeight="1">
+      <c r="A90" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="B90" s="12" t="n"/>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="43.5" customHeight="1">
-      <c r="A83" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E83" s="13" t="inlineStr">
-        <is>
-          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G83" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I83" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>К64 (2″)</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>нутч: стыки переходов</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="11" t="n">
-        <v>76</v>
-      </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="E85" s="13" t="inlineStr">
-        <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
-        </is>
-      </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="43.5" customHeight="1">
-      <c r="A86" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>без углеводородов: P-1 → G-1 (4), порт G-1 → SV-G1 → рукав (2), выход газа и V-G1 (2), колонны (4), NRV-3 (2), воздух насосов (2)</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="84" customHeight="1">
-      <c r="A87" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="B87" s="12" t="n"/>
-      <c r="C87" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="inlineStr">
-        <is>
-          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — сверху держит засыпку (вместо межклампового фильтра), снизу и сверху задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
-        </is>
-      </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I87" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="43.5" customHeight="1">
-      <c r="A88" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>К91 (3″)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу — по прокладке с каждой стороны фильтра)</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="4" t="n"/>
-    </row>
-    <row r="90" ht="70.5" customHeight="1">
-      <c r="A90" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>DN ¾″ (ID 19)</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 → коллектор сбросов 2 м; хомуты 25–40</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>≈12 м</t>
-        </is>
-      </c>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>16 м</t>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
@@ -4178,40 +4178,40 @@
           <t>КУПИТЬ</t>
         </is>
       </c>
-      <c r="I90" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: силикон армированный TSO</t>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
     <row r="91" ht="43.5" customHeight="1">
-      <c r="A91" s="11" t="n">
+      <c r="A91" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="13" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
-        </is>
-      </c>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t>К25 × 19,05</t>
-        </is>
-      </c>
-      <c r="E91" s="13" t="inlineStr">
-        <is>
-          <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1</t>
-        </is>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G91" s="14" t="inlineStr">
-        <is>
-          <t>14</t>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Хомут червячный нерж.</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>8–12 / 25–40 / 32–50</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>6 / 30 / 8</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
@@ -4219,40 +4219,40 @@
           <t>КУПИТЬ</t>
         </is>
       </c>
-      <c r="I91" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="43.5" customHeight="1">
-      <c r="A92" s="5" t="n">
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут червячный</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="70.5" customHeight="1">
+      <c r="A92" s="11" t="n">
         <v>82</v>
       </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>Хомут червячный нерж.</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>8–12 / 25–40 / 32–50</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (13 концов, вкл. конец у коллектора) / рукава 1″ (4)</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>6 / 26 / 8</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
-        <is>
-          <t>8 / 28 / 10</t>
+      <c r="B92" s="12" t="n"/>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>12 мм / ¼″</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>≈10</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>≈12</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
@@ -4260,62 +4260,21 @@
           <t>КУПИТЬ</t>
         </is>
       </c>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут червячный</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="70.5" customHeight="1">
-      <c r="A93" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
-        </is>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>12 мм / ¼″</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="inlineStr">
-        <is>
-          <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
-        </is>
-      </c>
-      <c r="F93" s="12" t="inlineStr">
-        <is>
-          <t>≈10</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>≈12</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
+  <autoFilter ref="A1:J92"/>
   <mergeCells count="9">
     <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A89:J89"/>
+    <mergeCell ref="A61:J61"/>
     <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A88:J88"/>
+    <mergeCell ref="A68:J68"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A33:J33"/>
@@ -4377,18 +4336,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId71"/>
@@ -4401,11 +4360,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4426,7 +4384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4735,23 +4693,23 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Клапан предохранительный угловой кламп, 0,3 бар</t>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>PSV-4: Нутч F-1</t>
+          <t>F-2: Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4771,27 +4729,27 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: предохр. клапан угловой кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1">
+          <t>Гросснер: корпус 10″</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
+          <t>Кран игольчатый нерж. AISI 316, внутр. резьба ¼″, PN 413 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>¼″ ВР</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>F-2: Фильтр F-2 / P-4</t>
+          <t>FV-1: Реактор R-1 / дозирование</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -4801,7 +4759,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -4811,37 +4769,37 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: корпус 10″</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t>Гросснер: кран игольчатый ¼″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70.5" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Кран игольчатый нерж. AISI 316, внутр. резьба ¼″, PN 413 (≈2 900 ₽)</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>¼″ ВР</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>FV-1: Реактор R-1 / дозирование</t>
+          <t>V-P3: Реактор R-1 / дозирование; SV-G1: Генератор G-1; V-G1: Генератор G-1; V-P1: Генератор G-1; SP-1, V-S1: Слив BV-1 / выгрузка P-2; SV-F1: Нутч F-1; VV-2: Нутч F-1; V-F2: Нутч F-1; V-F3: Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -4851,37 +4809,37 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран игольчатый ¼″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="70.5" customHeight="1">
+          <t>Гросснер: кран кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>½″ ВР (DN15)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>V-P3: Реактор R-1 / дозирование; SV-G1: Генератор G-1; V-G1: Генератор G-1; V-P1: Генератор G-1; SP-1, V-S1: Слив BV-1 / выгрузка P-2; VV-2: Нутч F-1; V-F2: Нутч F-1; V-F3: Фильтр F-2 / P-4</t>
+          <t>V-G2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -4891,7 +4849,7 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран шаровой ½″ 316</t>
         </is>
       </c>
     </row>
@@ -4901,17 +4859,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>½″ ВР (DN15)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>V-G2: Колонны C-1, C-2</t>
+          <t>PI-5: Нутч F-1</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -4921,7 +4879,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -4931,17 +4889,17 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран шаровой ½″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -4951,7 +4909,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>PI-5: Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -4961,7 +4919,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -4971,7 +4929,7 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+          <t>Гросснер: отвод кламп</t>
         </is>
       </c>
     </row>
@@ -4981,12 +4939,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -5011,37 +4969,37 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
+          <t>Гросснер: отвод кламп 90°</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°, AISI 316</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -5051,7 +5009,7 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
+          <t>Гросснер: патроны</t>
         </is>
       </c>
     </row>
@@ -5061,27 +5019,27 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Фильтр F-2 / P-4</t>
+          <t>Реактор R-1 / дозирование; Колонны C-1, C-2; Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -5091,7 +5049,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5101,27 +5059,27 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Реактор R-1 / дозирование; Колонны C-1, C-2; Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -5131,7 +5089,7 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
@@ -5141,12 +5099,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>К119 → К64</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -5171,7 +5129,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
+          <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
@@ -5181,27 +5139,27 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>К91 → К50,5</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -5211,7 +5169,7 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: переход 91 × 50,5 316</t>
         </is>
       </c>
     </row>
@@ -5221,29 +5179,29 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>К91 → К50,5</t>
+          <t>К25 × G¼″ вн.</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5251,7 +5209,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 91 × 50,5 316</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
@@ -5261,17 +5219,17 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>К25 × G¼″ вн.</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -5281,7 +5239,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -5291,7 +5249,7 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
     </row>
@@ -5306,22 +5264,22 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Фильтр F-2 / P-4; Сжатый воздух</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -5331,7 +5289,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
@@ -5341,27 +5299,27 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>К25 × G½″ нар.</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Фильтр F-2 / P-4; Сжатый воздух</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -5371,7 +5329,7 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5381,27 +5339,27 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>К25 × G½″ нар.</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Реактор R-1 / дозирование; Нутч F-1</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -5411,7 +5369,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
@@ -5421,27 +5379,27 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Реактор R-1 / дозирование; Нутч F-1</t>
+          <t>Генератор G-1; Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -5461,27 +5419,27 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1; Колонны C-1, C-2; Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -5491,7 +5449,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5464,7 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -5516,12 +5474,12 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -5541,12 +5499,12 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -5556,12 +5514,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -5571,7 +5529,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
         </is>
       </c>
     </row>
@@ -5581,12 +5539,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -5596,12 +5554,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -5611,7 +5569,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5584,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -5636,12 +5594,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -5666,7 +5624,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -5676,12 +5634,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -5706,7 +5664,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -5716,12 +5674,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -5741,12 +5699,12 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -5756,12 +5714,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5771,7 +5729,7 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
@@ -5781,27 +5739,27 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>Ø76</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -5811,7 +5769,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: хомут для труб</t>
         </is>
       </c>
     </row>
@@ -5821,27 +5779,27 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Ø76</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -5851,7 +5809,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5819,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5871,19 +5829,19 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5891,7 +5849,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5901,27 +5859,27 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -5931,7 +5889,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5941,29 +5899,29 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5971,7 +5929,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
     </row>
@@ -5981,29 +5939,29 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6011,7 +5969,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
@@ -6021,27 +5979,27 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -6051,7 +6009,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
         </is>
       </c>
     </row>
@@ -6061,12 +6019,12 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -6076,12 +6034,12 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -6091,22 +6049,22 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1">
       <c r="A43" s="5" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -6116,12 +6074,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6131,7 +6089,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6104,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -6156,12 +6114,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -6186,7 +6144,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -6196,12 +6154,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6215,18 +6173,18 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1">
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="11" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -6236,12 +6194,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6 / 30 / 8</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -6251,7 +6209,7 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
@@ -6261,27 +6219,27 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>6 / 26 / 8</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>8 / 28 / 10</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6291,7 +6249,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6301,27 +6259,27 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>по Ø: ½″, 3″, K119</t>
+          <t>К91 (3″) × 400</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>C-1, C-2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6331,7 +6289,7 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6299,17 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″) × 400</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны C-1, C-2</t>
+          <t>F-1: Нутч F-1</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -6381,27 +6339,27 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3,5 м</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -6411,7 +6369,7 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6421,27 +6379,27 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>3,5 м</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6451,7 +6409,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6466,22 +6424,22 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6501,12 +6459,12 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -6516,12 +6474,12 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>≈12 м</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>16 м</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6531,7 +6489,7 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
@@ -6541,27 +6499,27 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>К50,5 × 25,4</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6571,7 +6529,7 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
         </is>
       </c>
     </row>
@@ -6581,750 +6539,710 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К25 × 6,35</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
+          <t>Генератор G-1</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 6,35</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>BB-Engineering</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="4" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>G¼</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Сжатый воздух</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>G¼ × 8</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Сжатый воздух</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>BB-Engineering: S6510 8-1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="43.5" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>12 мм / ¼″</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>вся установка</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>≈10</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>≈12</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>BB-Engineering: обжимные фитинги</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Germeon</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="4" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>GL45 или по таре</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Реактор R-1 / дозирование</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>Germeon: крышка DURAN GL45, 2 порта</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Hydrohype</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="4" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>под корпус 10″</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Фильтр F-2 / P-4</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>Hydrohype: кольца в оболочке FEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Industriation</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="4" t="n"/>
+    </row>
+    <row r="65" ht="16.5" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Трубка PTFE 10×12, бухта</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>10×12</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Колонны C-1, C-2</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>≈8 м</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>10 м</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Industriation: PTFE 12/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Rizur</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="4" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>¼″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
           <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>К25 × 6,35</t>
-        </is>
-      </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель RizurLok-NP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Сжатый воздух</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Titan Lock</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="4" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>ID 6 мм</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K25 × 6,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>BB-Engineering</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="4" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>G¼</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Сжатый воздух</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>Titan Lock: шланги EPDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Ампика</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>G¼ × 8</t>
-        </is>
-      </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>Сжатый воздух</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>BB-Engineering: S6510 8-1/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="43.5" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>12 мм / ¼″</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>вся установка</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>≈10</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>≈12</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>BB-Engineering: обжимные фитинги</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Germeon</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>GL45 или по таре</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>КемИнС</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Ø ≈ 110 мм</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Нутч F-1</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>отрез 0,5 м²</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>КемИнС: фильтровальные ткани PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="16.5" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>¼″</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G62" s="16" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>Germeon: крышка DURAN GL45, 2 порта</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Hydrohype</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="4" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>под корпус 10″</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Фильтр F-2 / P-4</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Industriation</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n"/>
-      <c r="G65" s="3" t="n"/>
-      <c r="H65" s="4" t="n"/>
-    </row>
-    <row r="66" ht="16.5" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Трубка PTFE 10×12, бухта</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>10×12</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Колонны C-1, C-2</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>≈8 м</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>10 м</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>Industriation: PTFE 12/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Rizur</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="4" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>¼″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель RizurLok-NP</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>Сжатый воздух</t>
-        </is>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F69" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель переходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Titan Lock</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>ID 6 мм</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>≈3 м</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>5 м</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро: трубки PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Профрезина</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="4" t="n"/>
+    </row>
+    <row r="78" ht="43.5" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>500×500×3</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>4 м</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>Titan Lock: шланги EPDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Ампика</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>КемИнС</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Ø ≈ 110 мм</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Нутч F-1</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>отрез 0,5 м²</t>
-        </is>
-      </c>
-      <c r="G75" s="16" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>КемИнС: фильтровальные ткани PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="4" t="n"/>
-    </row>
-    <row r="77" ht="16.5" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>¼″</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Реактор R-1 / дозирование</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>≈3 м</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро: трубки PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Профрезина</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="4" t="n"/>
-    </row>
-    <row r="79" ht="43.5" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>500×500×3</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Генератор G-1</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H79"/>
+  <autoFilter ref="A1:H78"/>
   <mergeCells count="11">
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A75:H75"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
@@ -7380,20 +7298,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Сводная к заказу" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$93</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$79</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2104,33 +2104,33 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="57" customHeight="1">
       <c r="A38" s="5" t="n">
         <v>33</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>SP-1, V-S1</t>
+          <t>V-P2</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 1″, AISI 316L, PN10 (≈3 265 ₽)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>SP-1 — проба, V-S1 — бочка растворителя</t>
+          <t>перед P-2: после тройника V-S1, перед рукавом на насос — отсечь насос при обслуживании, перекрыть линию из реактора при заборе растворителя из бочки</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -2145,18 +2145,22 @@
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1">
+          <t>Гросснер: кран кламп 1″ 316L</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="12" t="n"/>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>SP-1, V-S1</t>
+        </is>
+      </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2166,12 +2170,12 @@
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>носик пробоотбора после SP-1</t>
+          <t>SP-1 — проба, V-S1 — бочка растворителя</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -2186,28 +2190,28 @@
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="43.5" customHeight="1">
+          <t>Гросснер: кран кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1">
       <c r="A40" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>P-2</t>
-        </is>
-      </c>
+      <c r="B40" s="6" t="n"/>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="n"/>
+          <t>Отвод кламп 90°</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>выгрузка суспензии на нутч</t>
+          <t>носик пробоотбора после SP-1</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -2217,7 +2221,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -2227,7 +2231,7 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+          <t>Гросснер: отвод кламп</t>
         </is>
       </c>
     </row>
@@ -2235,30 +2239,30 @@
       <c r="A41" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="12" t="n"/>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>P-2</t>
+        </is>
+      </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>¼″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин, частицы до 0,4 мм</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n"/>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
+          <t>выгрузка суспензии на нутч</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -2268,38 +2272,38 @@
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>Rizur: ниппель RizurLok-NP</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="43.5" customHeight="1">
       <c r="A42" s="5" t="n">
         <v>37</v>
       </c>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>P-2: вход и выход → рукав 1″</t>
+          <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -2309,7 +2313,7 @@
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
     </row>
@@ -2320,27 +2324,27 @@
       <c r="B43" s="12" t="n"/>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
+          <t>P-2: вход и выход → рукав 1″</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -2350,1931 +2354,1972 @@
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="43.5" customHeight="1">
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="n">
         <v>39</v>
       </c>
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="7" t="inlineStr">
         <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="43.5" customHeight="1">
+      <c r="A45" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>слив → P-2 (1,5 м), P-2 → нутч (2,5 м); хомуты 32–50; армирование — чтобы не сплющивался на всасе</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="4" t="n"/>
-    </row>
-    <row r="46" ht="43.5" customHeight="1">
-      <c r="A46" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="43.5" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="13" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B48" s="12" t="n"/>
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>К50,5 → К25</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="7" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>К64 → К50,5</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>крышка нутча и низ нутча</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="13" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>К119 → К64</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1">
-      <c r="A50" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="7" t="inlineStr">
+    <row r="51" ht="16.5" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>видно уровень суспензии</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Гросснер: диоптр кламп</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>F-1</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>К119 (4″) × 500</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
         <is>
           <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="43.5" customHeight="1">
-      <c r="A52" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="7" t="inlineStr">
+    <row r="53" ht="43.5" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="43.5" customHeight="1">
-      <c r="A53" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="13" t="inlineStr">
+    <row r="54" ht="43.5" customHeight="1">
+      <c r="A54" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>Ø ≈ 110 мм</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>фильтрующий слой нутча под Na₂SO₄ (сетка фильтра 0,5 мм сама осадок не держит); расходник — по 1 кругу на партию</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="H53" s="16" t="inlineStr">
+      <c r="H54" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="I53" s="15" t="inlineStr">
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="7" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>гребёнка нутча: PI-5, SV-F1, VV-2 (запас — здесь)</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>PI-5</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>на отвод тройника гребёнки</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
         <is>
           <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="57" customHeight="1">
-      <c r="A56" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="57" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>SV-F1</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>сброс давления нутча вручную (вместо PSV-4): тройник гребёнки → кран → ёлочка → рукав ¾″ в коллектор сбросов (коллектор — у смежников)</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>VV-2</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>вакуум нутча</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="7" t="inlineStr">
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>К25 × ¼″</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>V-F2</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>выход нутча (фильтрат)</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I59" s="15" t="inlineStr">
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="7" t="inlineStr">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>крепление гребёнки нутча и нутча к раме — по месту</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
-      <c r="J61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="4" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>P-4</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE (как P-2)</t>
         </is>
       </c>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>фильтрат нутча → F-2</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="13" t="inlineStr">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G63" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>F-2</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Корпус микропористого фильтра 10″ на клампах</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>10″</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>Гросснер: корпус 10″</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="13" t="inlineStr">
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>10″</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>по 2 шт. каждого рейтинга</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>Гросснер: патроны</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="7" t="inlineStr">
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>под корпус 10″</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>V-F3</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>выход F-2 → налив</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="G68" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Сжатый воздух к насосам P-2, P-4</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="4" t="n"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="4" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>⅛″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>вход воздуха насоса (по 1 на насос)</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>Rizur: ниппель переходной</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="13" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="12" t="n"/>
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E70" s="13" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G70" s="14" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="7" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>G¼ × 8</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>выход регулятора и кламп ¼″ у насоса</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G71" s="8" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="13" t="inlineStr">
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="13" t="inlineStr">
         <is>
           <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>G¼</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
         </is>
       </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G72" s="14" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="7" t="inlineStr">
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>по порту</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H73" s="16" t="inlineStr">
+      <c r="H74" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>Гросснер: ёлочка НР</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости; без реактора — на штуцерах P1–P4 родные клампы, без E-1, гребёнки реактора и VP-1)</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
-      <c r="J74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="16.5" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="16.5" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>все соединения ½″ нашей обвязки</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="11" t="n">
-        <v>67</v>
-      </c>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="13" t="inlineStr">
+    <row r="77" ht="43.5" customHeight="1">
+      <c r="A77" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="12" t="n"/>
+      <c r="C77" s="13" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D77" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E76" s="13" t="inlineStr">
-        <is>
-          <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, выгрузка P-2, переходы колонн и нутча</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, кран V-P2, выгрузка P-2, переходы колонн и нутча</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>К64 (2″)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="12" t="n"/>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>К91 (3″)</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу)</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="43.5" customHeight="1">
+      <c r="A81" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>где эфир и углеводороды: дозирование, слив и проба, выгрузка, нутч и его гребёнка, вакуум нутча, P-4, F-2</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>BV-1 → отвод, тройники 45° и прямой, кран V-P2, переходы 50,5/25, выгрузка P-2, нутч</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="43.5" customHeight="1">
+      <c r="A83" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="B83" s="12" t="n"/>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>К64 (2″)</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>нутч: стыки переходов</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="B85" s="12" t="n"/>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="43.5" customHeight="1">
+      <c r="A86" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>без углеводородов: P-1 → G-1 (4), порт G-1 → SV-G1 → рукав (2), выход газа и V-G1 (2), колонны (4), NRV-3 (2), воздух насосов (2)</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G76" s="14" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>К64 (2″)</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="84" customHeight="1">
+      <c r="A87" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="B87" s="12" t="n"/>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — сверху держит засыпку (вместо межклампового фильтра), снизу и сверху задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="43.5" customHeight="1">
+      <c r="A88" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>К91 (3″)</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу)</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу — по прокладке с каждой стороны фильтра)</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G78" s="14" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I78" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="43.5" customHeight="1">
-      <c r="A80" s="11" t="n">
-        <v>71</v>
-      </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E80" s="13" t="inlineStr">
-        <is>
-          <t>где эфир и углеводороды: дозирование, слив и проба, выгрузка, нутч и его гребёнка, вакуум нутча, P-4, F-2</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G80" s="14" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I80" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>BV-1 → отвод, тройники 45° и прямой, переходы 50,5/25, выгрузка P-2, нутч</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="84" customHeight="1">
+      <c r="A90" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>DN ¾″ (ID 19)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>≈14 м</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>18 м</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: силикон армированный TSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="43.5" customHeight="1">
+      <c r="A91" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="B91" s="12" t="n"/>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="43.5" customHeight="1">
-      <c r="A82" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="B82" s="12" t="n"/>
-      <c r="C82" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E82" s="13" t="inlineStr">
-        <is>
-          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G82" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I82" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B83" s="6" t="n"/>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>К64 (2″)</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>нутч: стыки переходов</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="B84" s="12" t="n"/>
-      <c r="C84" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="E84" s="13" t="inlineStr">
-        <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G84" s="14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="43.5" customHeight="1">
-      <c r="A85" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>без углеводородов: P-1 → G-1 (4), порт G-1 → SV-G1 → рукав (2), выход газа и V-G1 (2), колонны (4), NRV-3 (2), воздух насосов (2)</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="84" customHeight="1">
-      <c r="A86" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="B86" s="12" t="n"/>
-      <c r="C86" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E86" s="13" t="inlineStr">
-        <is>
-          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — сверху держит засыпку (вместо межклампового фильтра), снизу и сверху задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
-        </is>
-      </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G86" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="43.5" customHeight="1">
-      <c r="A87" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>К91 (3″)</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу — по прокладке с каждой стороны фильтра)</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n"/>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="4" t="n"/>
-    </row>
-    <row r="89" ht="84" customHeight="1">
-      <c r="A89" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>DN ¾″ (ID 19)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>≈14 м</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>18 м</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: силикон армированный TSO</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="43.5" customHeight="1">
-      <c r="A90" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="B90" s="12" t="n"/>
-      <c r="C90" s="13" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
-        </is>
-      </c>
-      <c r="D90" s="12" t="inlineStr">
-        <is>
-          <t>К25 × 19,05</t>
-        </is>
-      </c>
-      <c r="E90" s="13" t="inlineStr">
-        <is>
-          <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
-        </is>
-      </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G90" s="14" t="inlineStr">
+      <c r="G91" s="14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I90" s="15" t="inlineStr">
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="43.5" customHeight="1">
-      <c r="A91" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="7" t="inlineStr">
+    <row r="92" ht="43.5" customHeight="1">
+      <c r="A92" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>Хомут червячный нерж.</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D92" s="6" t="inlineStr">
         <is>
           <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>6 / 30 / 8</t>
         </is>
       </c>
-      <c r="G91" s="8" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>8 / 32 / 10</t>
         </is>
       </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I91" s="10" t="inlineStr">
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="70.5" customHeight="1">
-      <c r="A92" s="11" t="n">
-        <v>82</v>
-      </c>
-      <c r="B92" s="12" t="n"/>
-      <c r="C92" s="13" t="inlineStr">
+    <row r="93" ht="70.5" customHeight="1">
+      <c r="A93" s="11" t="n">
+        <v>83</v>
+      </c>
+      <c r="B93" s="12" t="n"/>
+      <c r="C93" s="13" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D93" s="12" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="E92" s="13" t="inlineStr">
+      <c r="E93" s="13" t="inlineStr">
         <is>
           <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
         </is>
       </c>
-      <c r="F92" s="12" t="inlineStr">
+      <c r="F93" s="12" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="G92" s="14" t="inlineStr">
+      <c r="G93" s="14" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J92"/>
+  <autoFilter ref="A1:J93"/>
   <mergeCells count="9">
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A89:J89"/>
     <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A88:J88"/>
-    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A69:J69"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A33:J33"/>
@@ -4321,7 +4366,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId45"/>
@@ -4336,18 +4381,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId71"/>
@@ -4360,10 +4405,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4384,7 +4430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4773,33 +4819,33 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="70.5" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 1″, AISI 316L, PN10 (≈3 265 ₽)</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>V-P3: Реактор R-1 / дозирование; SV-G1: Генератор G-1; V-G1: Генератор G-1; V-P1: Генератор G-1; SP-1, V-S1: Слив BV-1 / выгрузка P-2; SV-F1: Нутч F-1; VV-2: Нутч F-1; V-F2: Нутч F-1; V-F3: Фильтр F-2 / P-4</t>
+          <t>V-P2: Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -4809,37 +4855,37 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>Гросснер: кран кламп 1″ 316L</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70.5" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>½″ ВР (DN15)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>V-G2: Колонны C-1, C-2</t>
+          <t>V-P3: Реактор R-1 / дозирование; SV-G1: Генератор G-1; V-G1: Генератор G-1; V-P1: Генератор G-1; SP-1, V-S1: Слив BV-1 / выгрузка P-2; SV-F1: Нутч F-1; VV-2: Нутч F-1; V-F2: Нутч F-1; V-F3: Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -4849,7 +4895,7 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран шаровой ½″ 316</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
@@ -4859,17 +4905,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>½″ ВР (DN15)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>PI-5: Нутч F-1</t>
+          <t>V-G2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -4879,7 +4925,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -4889,17 +4935,17 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1">
+          <t>Гросснер: кран шаровой ½″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -4909,7 +4955,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>PI-5: Нутч F-1</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -4919,7 +4965,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -4929,7 +4975,7 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4985,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°, AISI 316</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -4969,37 +5015,37 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>Гросснер: отвод кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Фильтр F-2 / P-4</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -5009,7 +5055,7 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
+          <t>Гросснер: отвод кламп 90°</t>
         </is>
       </c>
     </row>
@@ -5019,27 +5065,27 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1 / дозирование; Колонны C-1, C-2; Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>Фильтр F-2 / P-4</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -5049,7 +5095,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: патроны</t>
         </is>
       </c>
     </row>
@@ -5059,27 +5105,27 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316 (≈2 300 ₽)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>К119 → К64</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Реактор R-1 / дозирование; Колонны C-1, C-2; Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -5089,7 +5135,7 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5145,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -5129,7 +5175,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
@@ -5139,27 +5185,27 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>К91 → К50,5</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -5169,7 +5215,7 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 91 × 50,5 316</t>
+          <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
@@ -5179,27 +5225,27 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+          <t>Переход кламп концентрический DIN DN65 × DN25, AISI 316 (≈6 910 ₽)</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>К25 × G¼″ вн.</t>
+          <t>К91 → К50,5</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -5209,7 +5255,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
+          <t>Гросснер: переход 91 × 50,5 316</t>
         </is>
       </c>
     </row>
@@ -5219,17 +5265,17 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>К25 × G¼″ вн.</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -5239,7 +5285,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -5249,7 +5295,7 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
@@ -5264,22 +5310,22 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Фильтр F-2 / P-4; Сжатый воздух</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -5289,7 +5335,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
     </row>
@@ -5299,27 +5345,27 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>К25 × G½″ нар.</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Фильтр F-2 / P-4; Сжатый воздух</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -5329,7 +5375,7 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
@@ -5339,27 +5385,27 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 × G½″ нар.</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1 / дозирование; Нутч F-1</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -5369,7 +5415,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5379,27 +5425,27 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Генератор G-1; Колонны C-1, C-2</t>
+          <t>Реактор R-1 / дозирование; Нутч F-1</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -5419,27 +5465,27 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Генератор G-1; Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -5449,7 +5495,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5510,7 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -5474,12 +5520,12 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -5499,12 +5545,12 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -5514,12 +5560,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -5529,7 +5575,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5585,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -5554,12 +5600,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -5569,7 +5615,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5630,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -5594,12 +5640,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -5624,7 +5670,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -5634,12 +5680,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -5664,7 +5710,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -5674,12 +5720,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -5699,12 +5745,12 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -5714,12 +5760,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5729,7 +5775,7 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5739,27 +5785,27 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Ø76</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -5769,7 +5815,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
@@ -5779,27 +5825,27 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>Ø76</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -5809,7 +5855,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: хомут для труб</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5865,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5829,17 +5875,17 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -5849,7 +5895,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5859,27 +5905,27 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -5889,7 +5935,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5899,27 +5945,27 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -5929,7 +5975,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5939,27 +5985,27 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -5969,7 +6015,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
     </row>
@@ -5979,27 +6025,27 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -6009,7 +6055,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6065,12 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -6034,12 +6080,12 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -6049,22 +6095,22 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16.5" customHeight="1">
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -6074,12 +6120,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6089,7 +6135,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6150,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -6114,12 +6160,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -6144,7 +6190,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -6154,12 +6200,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6173,18 +6219,18 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="11" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -6194,12 +6240,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -6209,7 +6255,7 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6219,27 +6265,27 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>по Ø: ½″, 3″, K119</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>6 / 30 / 8</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6249,7 +6295,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
@@ -6259,27 +6305,27 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″) × 400</t>
+          <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6289,7 +6335,7 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6299,17 +6345,17 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К91 (3″) × 400</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1</t>
+          <t>C-1, C-2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -6339,27 +6385,27 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>F-1: Нутч F-1</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>3,5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -6369,7 +6415,7 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6379,27 +6425,27 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>3,5 м</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6409,7 +6455,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6424,22 +6470,22 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>≈14 м</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6459,12 +6505,12 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -6474,12 +6520,12 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6489,7 +6535,7 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6499,27 +6545,27 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6529,7 +6575,7 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
@@ -6539,710 +6585,750 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Слив BV-1 / выгрузка P-2</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
           <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>К25 × 6,35</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="F56" s="14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>BB-Engineering</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
-      <c r="H56" s="4" t="n"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="4" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>G¼</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>G¼ × 8</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F58" s="14" t="inlineStr">
+      <c r="F59" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="43.5" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
+    <row r="60" ht="43.5" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>вся установка</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Germeon</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="4" t="n"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="4" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>GL45 или по таре</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr">
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Germeon: крышка DURAN GL45, 2 порта</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Hydrohype</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="4" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="4" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>под корпус 10″</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>Фильтр F-2 / P-4</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Industriation</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="4" t="n"/>
-    </row>
-    <row r="65" ht="16.5" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="4" t="n"/>
+    </row>
+    <row r="66" ht="16.5" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE 10×12, бухта</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>10×12</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>Колонны C-1, C-2</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>≈8 м</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>10 м</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>Industriation: PTFE 12/10</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Rizur</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="4" t="n"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="4" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="11" t="n">
-        <v>61</v>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>⅛″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="inlineStr">
         <is>
           <t>Rizur: ниппель переходной</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Titan Lock</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
-      <c r="H69" s="4" t="n"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="4" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>ID 6 мм</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Ампика</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="4" t="n"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
         </is>
       </c>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>КемИнС</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="4" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="4" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>Ø ≈ 110 мм</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>Нутч F-1</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="G74" s="16" t="inlineStr">
+      <c r="G75" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Пневмо-Электро</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="16.5" customHeight="1">
-      <c r="A76" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="4" t="n"/>
+    </row>
+    <row r="77" ht="16.5" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>¼″</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>≈3 м</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>Пневмо-Электро: трубки PTFE</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Профрезина</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="4" t="n"/>
-    </row>
-    <row r="78" ht="43.5" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="4" t="n"/>
+    </row>
+    <row r="79" ht="43.5" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>500×500×3</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H78"/>
+  <autoFilter ref="A1:H79"/>
   <mergeCells count="11">
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
@@ -7298,19 +7384,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Сводная к заказу" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$94</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>опора засыпки: низ C-1 и C-2 — на нём лежат сита / NaOH (сверху засыпку держит прокладка EPDM с сеткой на К50,5). В кламп-стык между двумя прокладками EPDM K91</t>
+          <t>опора засыпки: низ C-1 и C-2 — на нём лежат сита / NaOH (сверху засыпку держит прокладка EPDM с сеткой К91). В кламп-стык между двумя прокладками EPDM K91</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -4049,14 +4049,14 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="84" customHeight="1">
+    <row r="87" ht="30" customHeight="1">
       <c r="A87" s="11" t="n">
         <v>78</v>
       </c>
       <c r="B87" s="12" t="n"/>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>колонны C-1, C-2, верх и низ: стык переходов 3″/1″ → 1″/½″ — сверху держит засыпку (вместо межклампового фильтра), снизу и сверху задерживает пыль сит 3A и NaOH, не пускает её в трубки, NRV-3 и реактор (у Гросснера сетчатые только К50,5–К91, на К25 и К119 нет)</t>
+          <t>колонны: стыки переходов 3″/1″ → 1″/½″ (верх и низ)</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -4086,242 +4086,283 @@
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="43.5" customHeight="1">
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="57" customHeight="1">
       <c r="A88" s="5" t="n">
         <v>79</v>
       </c>
       <c r="B88" s="6" t="n"/>
       <c r="C88" s="7" t="inlineStr">
         <is>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈1 425 ₽</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>К91 (3″)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>колонны C-1, C-2: сверху (диоптр → переход) держит засыпку вместо межклампового фильтра; снизу — на межкламповом фильтре со стороны засыпки, задерживает пыль сит 3A и NaOH</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой EPDM К91 0,1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="43.5" customHeight="1">
+      <c r="A89" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="B89" s="12" t="n"/>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
           <t>Прокладка кламп EPDM</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
         <is>
           <t>К91 (3″)</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>колонны: 6 стыков + 2 на межкламповые фильтры (снизу — по прокладке с каждой стороны фильтра)</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>колонны: царга → диоптр (2), низ фильтра со стороны перехода (2); остальные К91 — с сеткой (строка ниже)</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
         <is>
           <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="4" t="n"/>
-    </row>
-    <row r="90" ht="84" customHeight="1">
-      <c r="A90" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="4" t="n"/>
+    </row>
+    <row r="91" ht="84" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>≈14 м</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>18 м</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I90" s="10" t="inlineStr">
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="43.5" customHeight="1">
-      <c r="A91" s="11" t="n">
-        <v>81</v>
-      </c>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="13" t="inlineStr">
+    <row r="92" ht="43.5" customHeight="1">
+      <c r="A92" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="B92" s="12" t="n"/>
+      <c r="C92" s="13" t="inlineStr">
         <is>
           <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D92" s="12" t="inlineStr">
         <is>
           <t>К25 × 19,05</t>
         </is>
       </c>
-      <c r="E91" s="13" t="inlineStr">
+      <c r="E92" s="13" t="inlineStr">
         <is>
           <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
         </is>
       </c>
-      <c r="F91" s="12" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G91" s="14" t="inlineStr">
+      <c r="G92" s="14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I91" s="15" t="inlineStr">
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="43.5" customHeight="1">
-      <c r="A92" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="7" t="inlineStr">
+    <row r="93" ht="43.5" customHeight="1">
+      <c r="A93" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>Хомут червячный нерж.</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>6 / 30 / 8</t>
         </is>
       </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>8 / 32 / 10</t>
         </is>
       </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I92" s="10" t="inlineStr">
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="70.5" customHeight="1">
-      <c r="A93" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="13" t="inlineStr">
+    <row r="94" ht="70.5" customHeight="1">
+      <c r="A94" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="B94" s="12" t="n"/>
+      <c r="C94" s="13" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="E93" s="13" t="inlineStr">
+      <c r="E94" s="13" t="inlineStr">
         <is>
           <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
         </is>
       </c>
-      <c r="F93" s="12" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="G93" s="14" t="inlineStr">
+      <c r="G94" s="14" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
+  <autoFilter ref="A1:J94"/>
   <mergeCells count="9">
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A89:J89"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A69:J69"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A90:J90"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
   <hyperlinks>
@@ -4406,10 +4447,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4430,7 +4472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5550,7 +5592,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -5560,12 +5602,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -5585,12 +5627,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -5615,7 +5657,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM 0,1 мм</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
@@ -5625,12 +5667,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈1 425 ₽ (≈1 425 ₽)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -5640,12 +5682,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -5655,7 +5697,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой EPDM К91 0,1 мм</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5712,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -5680,12 +5722,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -5710,7 +5752,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -5720,12 +5762,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -5750,7 +5792,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -5760,12 +5802,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5785,12 +5827,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -5800,12 +5842,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -5815,7 +5857,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5825,27 +5867,27 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Ø76</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -5855,7 +5897,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
@@ -5865,27 +5907,27 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>Ø76</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -5895,7 +5937,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: хомут для труб</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5947,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
@@ -5915,17 +5957,17 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -5935,7 +5977,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5945,27 +5987,27 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -5975,7 +6017,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5985,27 +6027,27 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -6015,7 +6057,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -6025,27 +6067,27 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -6055,7 +6097,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
     </row>
@@ -6065,27 +6107,27 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -6095,7 +6137,7 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
@@ -6105,12 +6147,12 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -6120,12 +6162,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6135,22 +6177,22 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16.5" customHeight="1">
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="11" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -6160,12 +6202,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -6175,7 +6217,7 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6232,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -6200,12 +6242,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6230,7 +6272,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -6240,12 +6282,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -6259,18 +6301,18 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="16.5" customHeight="1">
       <c r="A47" s="5" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -6280,12 +6322,12 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6295,7 +6337,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6305,27 +6347,27 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>по Ø: ½″, 3″, K119</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>6 / 30 / 8</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6335,7 +6377,7 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
@@ -6345,27 +6387,27 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″) × 400</t>
+          <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -6375,7 +6417,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6385,17 +6427,17 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К91 (3″) × 400</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1</t>
+          <t>C-1, C-2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
@@ -6425,27 +6467,27 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>F-1: Нутч F-1</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>3,5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6455,7 +6497,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6465,27 +6507,27 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>3,5 м</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6495,7 +6537,7 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6510,22 +6552,22 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>≈14 м</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6545,12 +6587,12 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
@@ -6560,12 +6602,12 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6575,7 +6617,7 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6585,27 +6627,27 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -6615,7 +6657,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
@@ -6625,710 +6667,750 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Слив BV-1 / выгрузка P-2</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
           <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>К25 × 6,35</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>BB-Engineering</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="4" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="4" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>G¼</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>G¼ × 8</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="43.5" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
+    <row r="61" ht="43.5" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>вся установка</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Germeon</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="4" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>GL45 или по таре</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Germeon: крышка DURAN GL45, 2 порта</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Hydrohype</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="4" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="4" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>под корпус 10″</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Фильтр F-2 / P-4</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Industriation</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n"/>
-      <c r="G65" s="3" t="n"/>
-      <c r="H65" s="4" t="n"/>
-    </row>
-    <row r="66" ht="16.5" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="4" t="n"/>
+    </row>
+    <row r="67" ht="16.5" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE 10×12, бухта</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>10×12</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Колонны C-1, C-2</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>≈8 м</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>10 м</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Industriation: PTFE 12/10</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Rizur</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="4" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="4" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C70" s="12" t="inlineStr">
         <is>
           <t>⅛″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F69" s="14" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="inlineStr">
         <is>
           <t>Rizur: ниппель переходной</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Titan Lock</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>ID 6 мм</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Ампика</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
         </is>
       </c>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>КемИнС</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Ø ≈ 110 мм</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Нутч F-1</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="G75" s="16" t="inlineStr">
+      <c r="G76" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Пневмо-Электро</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="4" t="n"/>
-    </row>
-    <row r="77" ht="16.5" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="4" t="n"/>
+    </row>
+    <row r="78" ht="16.5" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>¼″</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>≈3 м</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>Пневмо-Электро: трубки PTFE</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Профрезина</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="4" t="n"/>
-    </row>
-    <row r="79" ht="43.5" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="4" t="n"/>
+    </row>
+    <row r="80" ht="43.5" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>500×500×3</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H79"/>
+  <autoFilter ref="A1:H80"/>
   <mergeCells count="11">
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
@@ -7385,19 +7467,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Сводная к заказу" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$93</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$79</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="57" customHeight="1">
+    <row r="88" ht="70.5" customHeight="1">
       <c r="A88" s="5" t="n">
         <v>79</v>
       </c>
@@ -4107,17 +4107,17 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>колонны C-1, C-2: сверху (диоптр → переход) держит засыпку вместо межклампового фильтра; снизу — на межкламповом фильтре со стороны засыпки, задерживает пыль сит 3A и NaOH</t>
+          <t>все стыки К91 колонн C-1, C-2: царга → диоптр (2), верх диоптр → переход (2, держит засыпку), межкламповые фильтры снизу — по прокладке с каждой стороны (4); задерживает пыль сит 3A и NaOH</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
@@ -4131,91 +4131,91 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="43.5" customHeight="1">
-      <c r="A89" s="11" t="n">
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="84" customHeight="1">
+      <c r="A90" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B89" s="12" t="n"/>
-      <c r="C89" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>К91 (3″)</t>
-        </is>
-      </c>
-      <c r="E89" s="13" t="inlineStr">
-        <is>
-          <t>колонны: царга → диоптр (2), низ фильтра со стороны перехода (2); остальные К91 — с сеткой (строка ниже)</t>
-        </is>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G89" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="4" t="n"/>
-    </row>
-    <row r="91" ht="84" customHeight="1">
-      <c r="A91" s="5" t="n">
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>DN ¾″ (ID 19)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>≈14 м</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>18 м</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: силикон армированный TSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="43.5" customHeight="1">
+      <c r="A91" s="11" t="n">
         <v>81</v>
       </c>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>DN ¾″ (ID 19)</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>≈14 м</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>18 м</t>
+      <c r="B91" s="12" t="n"/>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
@@ -4223,40 +4223,40 @@
           <t>КУПИТЬ</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: силикон армированный TSO</t>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
     <row r="92" ht="43.5" customHeight="1">
-      <c r="A92" s="11" t="n">
+      <c r="A92" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B92" s="12" t="n"/>
-      <c r="C92" s="13" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
-        </is>
-      </c>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>К25 × 19,05</t>
-        </is>
-      </c>
-      <c r="E92" s="13" t="inlineStr">
-        <is>
-          <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
-        </is>
-      </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G92" s="14" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Хомут червячный нерж.</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>8–12 / 25–40 / 32–50</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>6 / 30 / 8</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
@@ -4264,40 +4264,40 @@
           <t>КУПИТЬ</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="43.5" customHeight="1">
-      <c r="A93" s="5" t="n">
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут червячный</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="70.5" customHeight="1">
+      <c r="A93" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>Хомут червячный нерж.</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>8–12 / 25–40 / 32–50</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>6 / 30 / 8</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>8 / 32 / 10</t>
+      <c r="B93" s="12" t="n"/>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>12 мм / ¼″</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>≈10</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>≈12</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
@@ -4305,64 +4305,23 @@
           <t>КУПИТЬ</t>
         </is>
       </c>
-      <c r="I93" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут червячный</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="70.5" customHeight="1">
-      <c r="A94" s="11" t="n">
-        <v>84</v>
-      </c>
-      <c r="B94" s="12" t="n"/>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
-        </is>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>12 мм / ¼″</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="inlineStr">
-        <is>
-          <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
-        </is>
-      </c>
-      <c r="F94" s="12" t="inlineStr">
-        <is>
-          <t>≈10</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>≈12</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J93"/>
   <mergeCells count="9">
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A89:J89"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A69:J69"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A90:J90"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
   <hyperlinks>
@@ -4447,11 +4406,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4472,7 +4430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5627,7 +5585,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈1 425 ₽ (≈1 425 ₽)</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -5642,12 +5600,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -5657,7 +5615,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: прокладка с сеткой EPDM К91 0,1 мм</t>
         </is>
       </c>
     </row>
@@ -5667,12 +5625,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈1 425 ₽ (≈1 425 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -5682,12 +5640,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -5697,7 +5655,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM К91 0,1 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5670,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -5722,12 +5680,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -5752,7 +5710,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -5762,12 +5720,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -5792,7 +5750,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -5802,12 +5760,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5827,12 +5785,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -5842,12 +5800,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -5857,7 +5815,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
@@ -5867,27 +5825,27 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>Ø76</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -5897,7 +5855,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: хомут для труб</t>
         </is>
       </c>
     </row>
@@ -5907,27 +5865,27 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Ø76</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -5937,7 +5895,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5905,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
@@ -5957,17 +5915,17 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -5977,7 +5935,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5987,27 +5945,27 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -6017,7 +5975,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -6027,29 +5985,29 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6057,7 +6015,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
     </row>
@@ -6067,27 +6025,27 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -6097,7 +6055,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
@@ -6107,27 +6065,27 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -6137,7 +6095,7 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
         </is>
       </c>
     </row>
@@ -6147,12 +6105,12 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -6162,12 +6120,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6177,22 +6135,22 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1">
       <c r="A44" s="11" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -6202,12 +6160,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -6217,7 +6175,7 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6190,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -6242,12 +6200,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6272,7 +6230,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -6282,12 +6240,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -6301,18 +6259,18 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -6322,12 +6280,12 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6 / 30 / 8</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6337,7 +6295,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
@@ -6347,27 +6305,27 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6377,7 +6335,7 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6387,27 +6345,27 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>по Ø: ½″, 3″, K119</t>
+          <t>К91 (3″) × 400</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>C-1, C-2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -6417,7 +6375,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6427,17 +6385,17 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″) × 400</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны C-1, C-2</t>
+          <t>F-1: Нутч F-1</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
@@ -6467,27 +6425,27 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3,5 м</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6497,7 +6455,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6507,27 +6465,27 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>3,5 м</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6537,7 +6495,7 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6552,22 +6510,22 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6587,12 +6545,12 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
@@ -6602,12 +6560,12 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>≈14 м</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6617,7 +6575,7 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
@@ -6627,27 +6585,27 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>К50,5 × 25,4</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -6657,7 +6615,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
         </is>
       </c>
     </row>
@@ -6667,750 +6625,710 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К25 × 6,35</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
+          <t>Генератор G-1</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 6,35</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>BB-Engineering</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="4" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>G¼</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Сжатый воздух</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>G¼ × 8</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Сжатый воздух</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>BB-Engineering: S6510 8-1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="43.5" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>12 мм / ¼″</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>вся установка</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>≈10</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>≈12</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>BB-Engineering: обжимные фитинги</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Germeon</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="4" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>GL45 или по таре</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Реактор R-1 / дозирование</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Germeon: крышка DURAN GL45, 2 порта</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Hydrohype</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="4" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>под корпус 10″</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Фильтр F-2 / P-4</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Hydrohype: кольца в оболочке FEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Industriation</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="4" t="n"/>
+    </row>
+    <row r="66" ht="16.5" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Трубка PTFE 10×12, бухта</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>10×12</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Колонны C-1, C-2</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>≈8 м</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>10 м</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Industriation: PTFE 12/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Rizur</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="4" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>¼″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
           <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>К25 × 6,35</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель RizurLok-NP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Сжатый воздух</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Titan Lock</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="4" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>ID 6 мм</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K25 × 6,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>BB-Engineering</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n"/>
-      <c r="G58" s="3" t="n"/>
-      <c r="H58" s="4" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>G¼</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Сжатый воздух</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="11" t="n">
-        <v>57</v>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>G¼ × 8</t>
-        </is>
-      </c>
-      <c r="D60" s="13" t="inlineStr">
-        <is>
-          <t>Сжатый воздух</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H60" s="15" t="inlineStr">
-        <is>
-          <t>BB-Engineering: S6510 8-1/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="43.5" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>12 мм / ¼″</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>вся установка</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>≈10</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>≈12</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>BB-Engineering: обжимные фитинги</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Germeon</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="4" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>GL45 или по таре</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>Titan Lock: шланги EPDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Ампика</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>КемИнС</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="4" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Ø ≈ 110 мм</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Нутч F-1</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>отрез 0,5 м²</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>КемИнС: фильтровальные ткани PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="4" t="n"/>
+    </row>
+    <row r="77" ht="16.5" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>¼″</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G63" s="16" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="inlineStr">
-        <is>
-          <t>Germeon: крышка DURAN GL45, 2 порта</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Hydrohype</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="4" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>под корпус 10″</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Фильтр F-2 / P-4</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Industriation</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="4" t="n"/>
-    </row>
-    <row r="67" ht="16.5" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Трубка PTFE 10×12, бухта</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>10×12</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Колонны C-1, C-2</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>≈8 м</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>10 м</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>Industriation: PTFE 12/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Rizur</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="4" t="n"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>¼″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель RizurLok-NP</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>Сжатый воздух</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F70" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H70" s="15" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель переходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Titan Lock</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="4" t="n"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>ID 6 мм</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>≈3 м</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>5 м</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро: трубки PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Профрезина</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="4" t="n"/>
+    </row>
+    <row r="79" ht="43.5" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>500×500×3</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>4 м</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>Titan Lock: шланги EPDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Ампика</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="4" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>КемИнС</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Ø ≈ 110 мм</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Нутч F-1</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>отрез 0,5 м²</t>
-        </is>
-      </c>
-      <c r="G76" s="16" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>КемИнС: фильтровальные ткани PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="4" t="n"/>
-    </row>
-    <row r="78" ht="16.5" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>¼″</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Реактор R-1 / дозирование</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>≈3 м</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро: трубки PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Профрезина</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n"/>
-      <c r="G79" s="3" t="n"/>
-      <c r="H79" s="4" t="n"/>
-    </row>
-    <row r="80" ht="43.5" customHeight="1">
-      <c r="A80" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>500×500×3</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Генератор G-1</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H80"/>
+  <autoFilter ref="A1:H79"/>
   <mergeCells count="11">
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
@@ -7467,20 +7385,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Сводная к заказу" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$94</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="70.5" customHeight="1">
+    <row r="88" ht="57" customHeight="1">
       <c r="A88" s="5" t="n">
         <v>79</v>
       </c>
@@ -4107,221 +4107,262 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>все стыки К91 колонн C-1, C-2: царга → диоптр (2), верх диоптр → переход (2, держит засыпку), межкламповые фильтры снизу — по прокладке с каждой стороны (4); задерживает пыль сит 3A и NaOH</t>
+          <t>верх колонн C-1, C-2 (диоптр → переход 3″/1″): держит засыпку вместо межклампового фильтра, задерживает пыль сит 3A и NaOH — по 1 на колонну</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой EPDM К91 0,1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="43.5" customHeight="1">
+      <c r="A89" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="B89" s="12" t="n"/>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>К91 (3″)</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>колонны: царга → диоптр (2), межкламповые фильтры снизу — по прокладке с каждой стороны (4)</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой EPDM К91 0,1 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="4" t="n"/>
-    </row>
-    <row r="90" ht="84" customHeight="1">
-      <c r="A90" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="4" t="n"/>
+    </row>
+    <row r="91" ht="84" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>≈14 м</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>18 м</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I90" s="10" t="inlineStr">
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="43.5" customHeight="1">
-      <c r="A91" s="11" t="n">
-        <v>81</v>
-      </c>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="13" t="inlineStr">
+    <row r="92" ht="43.5" customHeight="1">
+      <c r="A92" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="B92" s="12" t="n"/>
+      <c r="C92" s="13" t="inlineStr">
         <is>
           <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D92" s="12" t="inlineStr">
         <is>
           <t>К25 × 19,05</t>
         </is>
       </c>
-      <c r="E91" s="13" t="inlineStr">
+      <c r="E92" s="13" t="inlineStr">
         <is>
           <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
         </is>
       </c>
-      <c r="F91" s="12" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G91" s="14" t="inlineStr">
+      <c r="G92" s="14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I91" s="15" t="inlineStr">
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="43.5" customHeight="1">
-      <c r="A92" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="7" t="inlineStr">
+    <row r="93" ht="43.5" customHeight="1">
+      <c r="A93" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>Хомут червячный нерж.</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>6 / 30 / 8</t>
         </is>
       </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>8 / 32 / 10</t>
         </is>
       </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I92" s="10" t="inlineStr">
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="70.5" customHeight="1">
-      <c r="A93" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="13" t="inlineStr">
+    <row r="94" ht="70.5" customHeight="1">
+      <c r="A94" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="B94" s="12" t="n"/>
+      <c r="C94" s="13" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="E93" s="13" t="inlineStr">
+      <c r="E94" s="13" t="inlineStr">
         <is>
           <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
         </is>
       </c>
-      <c r="F93" s="12" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="G93" s="14" t="inlineStr">
+      <c r="G94" s="14" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
+  <autoFilter ref="A1:J94"/>
   <mergeCells count="9">
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A89:J89"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A69:J69"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A90:J90"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
   <hyperlinks>
@@ -4406,10 +4447,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4430,7 +4472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5585,7 +5627,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈1 425 ₽ (≈1 425 ₽)</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -5600,14 +5642,14 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5615,7 +5657,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM К91 0,1 мм</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
@@ -5625,12 +5667,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈1 425 ₽ (≈1 425 ₽)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -5640,12 +5682,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -5655,7 +5697,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой EPDM К91 0,1 мм</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5712,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -5680,12 +5722,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -5710,7 +5752,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -5720,12 +5762,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -5750,7 +5792,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -5760,12 +5802,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5785,12 +5827,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -5800,12 +5842,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -5815,7 +5857,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5825,27 +5867,27 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Ø76</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -5855,7 +5897,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
@@ -5865,27 +5907,27 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>Ø76</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -5895,7 +5937,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: хомут для труб</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5947,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
@@ -5915,17 +5957,17 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Слив BV-1 / выгрузка P-2; Нутч F-1</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -5935,7 +5977,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5945,27 +5987,27 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -5975,7 +6017,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -5985,27 +6027,27 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -6015,7 +6057,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 3″ 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -6025,27 +6067,27 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈3 925 ₽)</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -6055,7 +6097,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: фильтр межкламповый 3″ 316</t>
         </is>
       </c>
     </row>
@@ -6065,27 +6107,27 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>К91 (3″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -6095,7 +6137,7 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN65 (91)</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
@@ -6105,12 +6147,12 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 190 ₽)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К91 (3″)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -6120,12 +6162,12 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6135,22 +6177,22 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16.5" customHeight="1">
+          <t>Гросснер: хомут усиленный DN65 (91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="11" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -6160,12 +6202,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -6175,7 +6217,7 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6232,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -6200,12 +6242,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6230,7 +6272,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -6240,12 +6282,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -6259,18 +6301,18 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="16.5" customHeight="1">
       <c r="A47" s="5" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -6280,12 +6322,12 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6295,7 +6337,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6305,27 +6347,27 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>по Ø: ½″, 3″, K119</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>6 / 30 / 8</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6335,7 +6377,7 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
@@ -6345,27 +6387,27 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>К91 (3″) × 400</t>
+          <t>по Ø: ½″, 3″, K119</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны C-1, C-2</t>
+          <t>Нутч F-1</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -6375,7 +6417,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6385,17 +6427,17 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Царга кламп (труба 76,2 × 1,6), AISI 316</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К91 (3″) × 400</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1</t>
+          <t>C-1, C-2: Колонны C-1, C-2</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
@@ -6425,27 +6467,27 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Генератор G-1</t>
+          <t>F-1: Нутч F-1</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>3,5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6455,7 +6497,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6465,27 +6507,27 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>Генератор G-1</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>3,5 м</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6495,7 +6537,7 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6510,22 +6552,22 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>вся установка</t>
+          <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>≈14 м</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6545,12 +6587,12 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
@@ -6560,12 +6602,12 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6575,7 +6617,7 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6585,27 +6627,27 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Слив BV-1 / выгрузка P-2</t>
+          <t>вся установка</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -6615,7 +6657,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
@@ -6625,710 +6667,750 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Слив BV-1 / выгрузка P-2</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
           <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>К25 × 6,35</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>BB-Engineering</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="4" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="4" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>G¼</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>G¼ × 8</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="43.5" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
+    <row r="61" ht="43.5" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>вся установка</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Germeon</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="4" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Крышка-переходник на тару с 2 вводами (заборная трубка PTFE до дна + аргон ¼″), PTFE</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>GL45 или по таре</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Germeon: крышка DURAN GL45, 2 порта</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Hydrohype</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="4" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="4" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>под корпус 10″</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Фильтр F-2 / P-4</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Industriation</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n"/>
-      <c r="G65" s="3" t="n"/>
-      <c r="H65" s="4" t="n"/>
-    </row>
-    <row r="66" ht="16.5" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="4" t="n"/>
+    </row>
+    <row r="67" ht="16.5" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE 10×12, бухта</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>10×12</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Колонны C-1, C-2</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>≈8 м</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>10 м</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Industriation: PTFE 12/10</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Rizur</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="4" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="4" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>Слив BV-1 / выгрузка P-2</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C70" s="12" t="inlineStr">
         <is>
           <t>⅛″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>Сжатый воздух</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F69" s="14" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="inlineStr">
         <is>
           <t>Rizur: ниппель переходной</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Titan Lock</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>ID 6 мм</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Ампика</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
         </is>
       </c>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>P-2: Слив BV-1 / выгрузка P-2; P-4: Фильтр F-2 / P-4</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>КемИнС</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Ø ≈ 110 мм</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Нутч F-1</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="G75" s="16" t="inlineStr">
+      <c r="G76" s="16" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Пневмо-Электро</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="4" t="n"/>
-    </row>
-    <row r="77" ht="16.5" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="4" t="n"/>
+    </row>
+    <row r="78" ht="16.5" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>¼″</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1 / дозирование</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>≈3 м</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>Пневмо-Электро: трубки PTFE</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Профрезина</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="4" t="n"/>
-    </row>
-    <row r="79" ht="43.5" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="4" t="n"/>
+    </row>
+    <row r="80" ht="43.5" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>500×500×3</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>Генератор G-1</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H79"/>
+  <autoFilter ref="A1:H80"/>
   <mergeCells count="11">
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
@@ -7385,19 +7467,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>корпуса колонн, низ</t>
+          <t>корпуса колонн, над диоптром (основная засыпка)</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>верх колонн — видно засыпку и фронт влаги</t>
+          <t>низ колонн, над межкламповым фильтром — видно состояние набивки (сита 3A / NaOH): газ входит снизу, фронт влаги идёт отсюда</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>колонны: царга → диоптр (2), межкламповые фильтры снизу — по прокладке с каждой стороны (4)</t>
+          <t>колонны: диоптр → царга (2), межкламповые фильтры снизу — по прокладке с каждой стороны (4)</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>верх колонн C-1, C-2 (диоптр → переход 50,5/25): держит засыпку вместо межклампового фильтра, задерживает пыль сит 3A и NaOH — по 1 на колонну</t>
+          <t>верх колонн C-1, C-2 (царга → переход 50,5/25): держит засыпку вместо межклампового фильтра, задерживает пыль сит 3A и NaOH — по 1 на колонну</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>опора засыпки: низ C-1 и C-2 — на нём лежат сита / NaOH (сверху засыпку держит прокладка EPDM с сеткой K50,5). В кламп-стык между двумя прокладками EPDM K50,5</t>
+          <t>опора засыпки: низ C-1 и C-2, под диоптром (диоптр → фильтр → переход 50,5/25) — на нём лежат сита / NaOH; сверху засыпку держит прокладка EPDM с сеткой K50,5. 2 шт. + 1 запасной</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="57" customHeight="1">
+    <row r="75" ht="70.5" customHeight="1">
       <c r="A75" s="11" t="n">
         <v>66</v>
       </c>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, кран V-P2, выгрузка P-2, переходы нутча; колонны C-1, C-2: 6 стыков + 2 на межкламповые фильтры (снизу)</t>
+          <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, кран V-P2, выгрузка P-2, переходы нутча; колонны C-1, C-2: по 4 стыка на колонну — фильтр/переход, диоптр/фильтр, диоптр/царга, царга/верхний переход (8)</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>колонны: диоптр → царга (2), межкламповые фильтры снизу — по прокладке с каждой стороны (4)</t>
+          <t>колонны: диоптр → царга (2), межкламповый фильтр снизу — с двух сторон: диоптр/фильтр и фильтр/переход (4)</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -2533,7 +2533,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1">
+    <row r="49" ht="43.5" customHeight="1">
       <c r="A49" s="5" t="n">
         <v>43</v>
       </c>
@@ -2550,17 +2550,17 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>видно уровень суспензии</t>
+          <t>2 диоптра: верхний — уровень суспензии; нижний — над межкламповым фильтром, видно осадок и слой Na₂SO₄ на ткани</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>опора слоя (ткань PTFE/PP + Na₂SO₄)</t>
+          <t>опора слоя (ткань PTFE/PP + Na₂SO₄), под нижним диоптром — отдельная деталь между двумя стыками</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -3634,7 +3634,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1">
+    <row r="77" ht="57" customHeight="1">
       <c r="A77" s="11" t="n">
         <v>68</v>
       </c>
@@ -3651,17 +3651,17 @@
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр (с PTFE — только болтовые)</t>
+          <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход (с PTFE — только болтовые)</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="30" customHeight="1">
+    <row r="82" ht="43.5" customHeight="1">
       <c r="A82" s="5" t="n">
         <v>73</v>
       </c>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>нутч: 4 стыка + 1 на межкламповый фильтр</t>
+          <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$90</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>штуцер P3 → V-P3 (запас на все 10 кранов ½″ — здесь)</t>
+          <t>штуцер P3 → V-P3 (запас на все 10 кранов ½″ — здесь, в 316: подходит и вместо крана 304)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 304, PN10 (≈1 910 ₽) — среда без хлоридов</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t>Гросснер: кран кламп ½″ AISI 304</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="43.5" customHeight="1">
       <c r="A14" s="5" t="n">
         <v>11</v>
       </c>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 304, PN10 (≈1 910 ₽) — среда без хлоридов</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ AISI 304</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="43.5" customHeight="1">
       <c r="A19" s="11" t="n">
         <v>16</v>
       </c>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 304, PN10 (≈1 910 ₽) — среда без хлоридов</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ AISI 304</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 316L (≈2 600 ₽)</t>
+          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
+          <t>Кран шаровой нержавеющий, AISI 304, сёдла PTFE, внутр. резьба ½″ (≈485 ₽)</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -4298,7 +4298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5167,13 +5167,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="178.5" customHeight="1">
+    <row r="27" ht="97.5" customHeight="1">
       <c r="A27" s="11" t="n">
         <v>19</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 304, PN10 — среда без хлоридов (≈1 910 ₽)</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -5183,17 +5183,17 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>V-P3: Реактор R-1; SV-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-P1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; SP-1, V-S1: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; SV-F1: Нутч F-1 (K119) и гребёнка газов нутча; VV-2: Нутч F-1 (K119) и гребёнка газов нутча; V-F2: Нутч F-1 (K119) и гребёнка газов нутча; V-F3: Фильтрация F-2 и фасовка (P-4)</t>
+          <t>SV-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-P1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -5203,37 +5203,37 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t>Гросснер: кран кламп ½″ AISI 304</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="97.5" customHeight="1">
       <c r="A28" s="5" t="n">
         <v>20</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
+          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>½″ ВР (DN15)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>V-G2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>V-P3: Реактор R-1; SP-1, V-S1: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; SV-F1: Нутч F-1 (K119) и гребёнка газов нутча; VV-2: Нутч F-1 (K119) и гребёнка газов нутча; V-F2: Нутч F-1 (K119) и гребёнка газов нутча; V-F3: Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран шаровой ½″ 316</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
@@ -5253,17 +5253,17 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+          <t>Кран шаровой нержавеющий, AISI 304, сёдла PTFE, внутр. резьба ½″ (≈485 ₽)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>½″ ВР (DN15)</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>PI-5: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>V-G2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+          <t>Гросснер: кран шаровой ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>PI-5: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
     </row>
@@ -5333,12 +5333,12 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°, AISI 316</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
+          <t>Гросснер: отвод кламп</t>
         </is>
       </c>
     </row>
@@ -5373,27 +5373,27 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -5403,37 +5403,37 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="70.5" customHeight="1">
+          <t>Гросснер: отвод кламп 90°</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="11" t="n">
         <v>25</v>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Реактор R-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -5443,37 +5443,37 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
+          <t>Гросснер: патроны</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="70.5" customHeight="1">
       <c r="A34" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>К119 → К64</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Реактор R-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>К25 × G¼″ вн.</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
+          <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
@@ -5573,17 +5573,17 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>К25 × G¼″ вн.</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
@@ -5618,22 +5618,22 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Фильтрация F-2 и фасовка (P-4); Сжатый воздух к насосам P-2, P-4</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
     </row>
@@ -5653,27 +5653,27 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>К25 × G½″ нар.</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>Фильтрация F-2 и фасовка (P-4); Сжатый воздух к насосам P-2, P-4</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
@@ -5693,27 +5693,27 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 × G½″ нар.</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -5723,37 +5723,37 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="57" customHeight="1">
+          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="11" t="n">
         <v>33</v>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Реактор R-1; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -5767,33 +5767,33 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="57" customHeight="1">
       <c r="A42" s="5" t="n">
         <v>34</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
@@ -5893,12 +5893,12 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -6093,27 +6093,27 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Ø38</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -6123,37 +6123,37 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="43.5" customHeight="1">
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="11" t="n">
         <v>43</v>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>Ø38</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
+          <t>Гросснер: хомут для труб</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="43.5" customHeight="1">
       <c r="A52" s="5" t="n">
         <v>44</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
@@ -6213,27 +6213,27 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -6253,27 +6253,27 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый K50,5 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: фильтр межкламповый K50,5 316</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -6363,22 +6363,22 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16.5" customHeight="1">
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
       <c r="A57" s="11" t="n">
         <v>49</v>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
@@ -6487,33 +6487,33 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
+    <row r="60" ht="16.5" customHeight="1">
       <c r="A60" s="5" t="n">
         <v>52</v>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6533,27 +6533,27 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>по Ø: ½″, K119</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>6 / 30 / 8</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
@@ -6573,27 +6573,27 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 316L (≈2 600 ₽)</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1½″) × 400</t>
+          <t>по Ø: ½″, K119</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп 1½″ × 400</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6613,17 +6613,17 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К50,5 (1½″) × 400</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="H63" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: царга кламп 1½″ × 400</t>
         </is>
       </c>
     </row>
@@ -6653,27 +6653,27 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6693,29 +6693,29 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
+          <t>2,5 м</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6738,22 +6738,22 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>≈14 м</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6813,27 +6813,27 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
@@ -6853,214 +6853,254 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
           <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>К25 × 6,35</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F69" s="14" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>КемИнС</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>Ø ≈ 110 мм</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr">
+      <c r="G72" s="17" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Пневмо-Электро</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="16.5" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="16.5" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>¼″</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>≈3 м</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Пневмо-Электро: трубки PTFE</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Профрезина</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="43.5" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="43.5" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>500×500×3</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H75"/>
+  <autoFilter ref="A1:H76"/>
   <mergeCells count="10">
-    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A75:H75"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <hyperlinks>
@@ -7125,9 +7165,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>штуцер P3 → V-P3 (запас на все 10 кранов ½″ — здесь, в 316: подходит и вместо крана 304)</t>
+          <t>штуцер P3 → V-P3 (запас на все 10 кранов ½″ — здесь)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 304, PN10 (≈1 910 ₽) — среда без хлоридов</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп ½″ AISI 304</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="43.5" customHeight="1">
+          <t>Гросснер: кран кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="n">
         <v>11</v>
       </c>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 304, PN10 (≈1 910 ₽) — среда без хлоридов</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп ½″ AISI 304</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="43.5" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="11" t="n">
         <v>16</v>
       </c>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 304, PN10 (≈1 910 ₽) — среда без хлоридов</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп ½″ AISI 304</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="4" t="n"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="57" customHeight="1">
       <c r="A22" s="5" t="n">
         <v>18</v>
       </c>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>корпуса колонн, над диоптром (основная засыпка)</t>
+          <t>корпуса колонн, над диоптром (основная засыпка). AISI 304: стойкость к метиламину — «A» (Graco, ISM, Filter Sciences); хлоридов в колоннах нет</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 304, сёдла PTFE, внутр. резьба ½″ (≈485 ₽)</t>
+          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 304, PN10 — среда без хлоридов (≈1 910 ₽)</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп ½″ AISI 304</t>
+          <t>Гросснер: кран кламп</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 304, сёдла PTFE, внутр. резьба ½″ (≈485 ₽)</t>
+          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$90</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$75</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="97.5" customHeight="1">
+    <row r="27" ht="178.5" customHeight="1">
       <c r="A27" s="11" t="n">
         <v>19</v>
       </c>
@@ -5183,17 +5183,17 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>SV-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-P1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>V-P3: Реактор R-1; SV-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-P1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; SP-1, V-S1: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; SV-F1: Нутч F-1 (K119) и гребёнка газов нутча; VV-2: Нутч F-1 (K119) и гребёнка газов нутча; V-F2: Нутч F-1 (K119) и гребёнка газов нутча; V-F3: Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -5203,37 +5203,37 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="97.5" customHeight="1">
+          <t>Гросснер: кран кламп ½″ 316L</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="n">
         <v>20</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп, сёдла PTFE, AISI 316</t>
+          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>½″ ВР (DN15)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>V-P3: Реактор R-1; SP-1, V-S1: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; SV-F1: Нутч F-1 (K119) и гребёнка газов нутча; VV-2: Нутч F-1 (K119) и гребёнка газов нутча; V-F2: Нутч F-1 (K119) и гребёнка газов нутча; V-F3: Фильтрация F-2 и фасовка (P-4)</t>
+          <t>V-G2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп</t>
+          <t>Гросснер: кран шаровой ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5253,17 +5253,17 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>½″ ВР (DN15)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>V-G2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>PI-5: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран шаровой ½″ 316</t>
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>PI-5: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+          <t>Гросснер: отвод кламп</t>
         </is>
       </c>
     </row>
@@ -5333,12 +5333,12 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
+          <t>Гросснер: отвод кламп 90°</t>
         </is>
       </c>
     </row>
@@ -5373,27 +5373,27 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°, AISI 316</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -5403,37 +5403,37 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t>Гросснер: патроны</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="70.5" customHeight="1">
       <c r="A33" s="11" t="n">
         <v>25</v>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
+          <t>Реактор R-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -5443,37 +5443,37 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="70.5" customHeight="1">
+          <t>Гросснер: переход 1″ × ½″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>К119 → К64</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
+          <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>К25 × G¼″ вн.</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
@@ -5573,17 +5573,17 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>К25 × G¼″ вн.</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
     </row>
@@ -5618,22 +5618,22 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Фильтрация F-2 и фасовка (P-4); Сжатый воздух к насосам P-2, P-4</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
@@ -5653,27 +5653,27 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>К25 × G½″ нар.</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Фильтрация F-2 и фасовка (P-4); Сжатый воздух к насосам P-2, P-4</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
         </is>
       </c>
     </row>
@@ -5693,27 +5693,27 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>К25 × G½″ нар.</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>Реактор R-1; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -5723,37 +5723,37 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
+          <t>Гросснер: кламп – резьба наружная</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="57" customHeight="1">
       <c r="A41" s="11" t="n">
         <v>33</v>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Реактор R-1; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -5767,33 +5767,33 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="57" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="n">
         <v>34</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
         </is>
       </c>
     </row>
@@ -5893,12 +5893,12 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
@@ -6093,27 +6093,27 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>Ø38</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -6123,37 +6123,37 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
+          <t>Гросснер: хомут для труб</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="43.5" customHeight="1">
       <c r="A51" s="11" t="n">
         <v>43</v>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Ø38</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="43.5" customHeight="1">
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="n">
         <v>44</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -6213,27 +6213,27 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -6253,29 +6253,29 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: фильтр межкламповый K50,5 316</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый K50,5 316</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -6363,22 +6363,22 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16.5" customHeight="1">
       <c r="A57" s="11" t="n">
         <v>49</v>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
@@ -6487,33 +6487,33 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="16.5" customHeight="1">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="n">
         <v>52</v>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6 / 30 / 8</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
@@ -6533,27 +6533,27 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>по Ø: ½″, K119</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6573,27 +6573,27 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>по Ø: ½″, K119</t>
+          <t>К50,5 (1½″) × 400</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: царга кламп 1½″ × 400</t>
         </is>
       </c>
     </row>
@@ -6613,17 +6613,17 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1½″) × 400</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="H63" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп 1½″ × 400</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6653,27 +6653,27 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2,5 м</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6693,27 +6693,27 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6738,22 +6738,22 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>≈14 м</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
@@ -6813,27 +6813,27 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>К50,5 × 25,4</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
         </is>
       </c>
     </row>
@@ -6853,27 +6853,27 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К25 × 6,35</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -6883,224 +6883,184 @@
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="5" t="n">
+          <t>Гросснер: штуцер K25 × 6,35</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>КемИнС</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="4" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>К25 × 6,35</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Ø ≈ 110 мм</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>отрез 0,5 м²</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>КемИнС: фильтровальные ткани PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="16.5" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>¼″</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Реактор R-1</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>≈3 м</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>5 м</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро: трубки PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Профрезина</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="4" t="n"/>
+    </row>
+    <row r="75" ht="43.5" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>500×500×3</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K25 × 6,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>КемИнС</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="4" t="n"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Ø ≈ 110 мм</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>отрез 0,5 м²</t>
-        </is>
-      </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>КемИнС: фильтровальные ткани PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="4" t="n"/>
-    </row>
-    <row r="74" ht="16.5" customHeight="1">
-      <c r="A74" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>¼″</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Реактор R-1</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>≈3 м</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро: трубки PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Профрезина</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="43.5" customHeight="1">
-      <c r="A76" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>500×500×3</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H76"/>
+  <autoFilter ref="A1:H75"/>
   <mergeCells count="10">
+    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A75:H75"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <hyperlinks>
@@ -7165,10 +7125,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Сводная к заказу" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1796,34 +1796,34 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="43.5" customHeight="1">
       <c r="A30" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 38,1 мм (≈320 ₽)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Ø38</t>
+          <t>Ø38,1 (1½″)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>крепление C-1, C-2 к раме или стенду</t>
+          <t>крепление колонн C-1, C-2 к раме или стенду — по 2 на колонну (на царгу, выше и ниже середины)</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
+          <t>Гросснер: хомут трубный 38,1 мм</t>
         </is>
       </c>
     </row>
@@ -2967,1234 +2967,1279 @@
       <c r="A59" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B59" s="6" t="n"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>F-1</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 101,6 мм (≈625 ₽)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Ø101,6 (K119, 4″)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>крепление нутча F-1 к раме / опоре — 2 шт. на царги K119</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут трубный 101,6 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16.5" customHeight="1">
+      <c r="A60" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
           <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>по Ø: ½″, K119</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>крепление гребёнки нутча и нутча к раме — по месту</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>по Ø: ½″</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>крепление гребёнки нутча к раме — по месту</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
-      <c r="J60" s="4" t="n"/>
-    </row>
-    <row r="61" ht="43.5" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="4" t="n"/>
+    </row>
+    <row r="62" ht="43.5" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>P-4</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>фильтрат нутча → F-2</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="13" t="inlineStr">
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>F-2</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Корпус микропористого фильтра 10″ на клампах</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>10″</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>Гросснер: корпус 10″</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="11" t="n">
-        <v>57</v>
-      </c>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="13" t="inlineStr">
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>10″</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>по 2 шт. каждого рейтинга</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G64" s="14" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I64" s="15" t="inlineStr">
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
         <is>
           <t>Гросснер: патроны</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="7" t="inlineStr">
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>под корпус 10″</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="11" t="n">
-        <v>59</v>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>V-F3</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>выход F-2 → налив</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="F67" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G66" s="14" t="inlineStr">
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Сжатый воздух к насосам P-2, P-4</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="n"/>
-      <c r="J67" s="4" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
+      <c r="J68" s="4" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>⅛″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>вход воздуха насоса (по 1 на насос)</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>Rizur: ниппель переходной</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="11" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="13" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="12" t="n"/>
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
         <is>
           <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G69" s="14" t="inlineStr">
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I69" s="15" t="inlineStr">
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="7" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>G¼ × 8</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>выход регулятора и кламп ¼″ у насоса</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="12" t="n"/>
-      <c r="C71" s="13" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="13" t="inlineStr">
         <is>
           <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
         <is>
           <t>G¼</t>
         </is>
       </c>
-      <c r="E71" s="13" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
         </is>
       </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="7" t="inlineStr">
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>по порту</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H72" s="17" t="inlineStr">
+      <c r="H73" s="17" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="I72" s="10" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>Гросснер: ёлочка НР</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости; без реактора — на штуцерах P1–P4 родные клампы, без E-1, гребёнки реактора и VP-1)</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="4" t="n"/>
-    </row>
-    <row r="74" ht="16.5" customHeight="1">
-      <c r="A74" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="4" t="n"/>
+    </row>
+    <row r="75" ht="16.5" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>все соединения ½″ нашей обвязки</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="70.5" customHeight="1">
-      <c r="A75" s="11" t="n">
-        <v>66</v>
-      </c>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="13" t="inlineStr">
+    <row r="76" ht="70.5" customHeight="1">
+      <c r="A76" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D76" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E75" s="13" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, кран V-P2, выгрузка P-2, переходы нутча; колонны C-1, C-2: по 4 стыка на колонну — фильтр/переход, диоптр/фильтр, диоптр/царга, царга/верхний переход (8)</t>
         </is>
       </c>
-      <c r="F75" s="12" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G75" s="14" t="inlineStr">
+      <c r="G76" s="14" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I75" s="15" t="inlineStr">
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="7" t="inlineStr">
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>К64 (2″)</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="57" customHeight="1">
-      <c r="A77" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="13" t="inlineStr">
+    <row r="78" ht="57" customHeight="1">
+      <c r="A78" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="12" t="n"/>
+      <c r="C78" s="13" t="inlineStr">
         <is>
           <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D78" s="12" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход (с PTFE — только болтовые)</t>
         </is>
       </c>
-      <c r="F77" s="12" t="inlineStr">
+      <c r="F78" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G77" s="14" t="inlineStr">
+      <c r="G78" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="43.5" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="7" t="inlineStr">
+    <row r="79" ht="43.5" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>где эфир и углеводороды: дозирование, слив и проба, выгрузка, нутч и его гребёнка, вакуум нутча, P-4, F-2</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="13" t="inlineStr">
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E79" s="13" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>BV-1 → отвод, тройники 45° и прямой, кран V-P2, переходы 50,5/25, выгрузка P-2, нутч</t>
         </is>
       </c>
-      <c r="F79" s="12" t="inlineStr">
+      <c r="F80" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G79" s="14" t="inlineStr">
+      <c r="G80" s="14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I79" s="15" t="inlineStr">
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="43.5" customHeight="1">
-      <c r="A80" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="7" t="inlineStr">
+    <row r="81" ht="43.5" customHeight="1">
+      <c r="A81" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="13" t="inlineStr">
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="B82" s="12" t="n"/>
+      <c r="C82" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>К64 (2″)</t>
         </is>
       </c>
-      <c r="E81" s="13" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>нутч: стыки переходов</t>
         </is>
       </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G81" s="14" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I81" s="15" t="inlineStr">
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="43.5" customHeight="1">
-      <c r="A82" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="7" t="inlineStr">
+    <row r="83" ht="43.5" customHeight="1">
+      <c r="A83" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="43.5" customHeight="1">
-      <c r="A83" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="13" t="inlineStr">
+    <row r="84" ht="43.5" customHeight="1">
+      <c r="A84" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="12" t="n"/>
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп EPDM</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E83" s="13" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>без углеводородов: P-1 → G-1 (4), порт G-1 → SV-G1 → рукав (2), выход газа и V-G1 (2), колонны (4), NRV-3 (2), воздух насосов (2)</t>
         </is>
       </c>
-      <c r="F83" s="12" t="inlineStr">
+      <c r="F84" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G83" s="14" t="inlineStr">
+      <c r="G84" s="14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I83" s="15" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
         <is>
           <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="43.5" customHeight="1">
-      <c r="A84" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="7" t="inlineStr">
+    <row r="85" ht="43.5" customHeight="1">
+      <c r="A85" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп EPDM</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1½″)</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>колонны: диоптр → царга (2), межкламповый фильтр снизу — с двух сторон: диоптр/фильтр и фильтр/переход (4)</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
         <is>
           <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="57" customHeight="1">
-      <c r="A85" s="11" t="n">
-        <v>76</v>
-      </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="13" t="inlineStr">
+    <row r="86" ht="57" customHeight="1">
+      <c r="A86" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" s="12" t="n"/>
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D86" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1½″)</t>
         </is>
       </c>
-      <c r="E85" s="13" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>верх колонн C-1, C-2 (царга → переход 50,5/25): держит засыпку вместо межклампового фильтра, задерживает пыль сит 3A и NaOH — по 1 на колонну</t>
         </is>
       </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
         <is>
           <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" s="3" t="n"/>
-      <c r="J86" s="4" t="n"/>
-    </row>
-    <row r="87" ht="84" customHeight="1">
-      <c r="A87" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="B87" s="3" t="n"/>
+      <c r="C87" s="3" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+      <c r="I87" s="3" t="n"/>
+      <c r="J87" s="4" t="n"/>
+    </row>
+    <row r="88" ht="84" customHeight="1">
+      <c r="A88" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>≈14 м</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>18 м</t>
         </is>
       </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I87" s="10" t="inlineStr">
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="43.5" customHeight="1">
-      <c r="A88" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="B88" s="12" t="n"/>
-      <c r="C88" s="13" t="inlineStr">
+    <row r="89" ht="43.5" customHeight="1">
+      <c r="A89" s="11" t="n">
+        <v>79</v>
+      </c>
+      <c r="B89" s="12" t="n"/>
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
-      <c r="D88" s="12" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
         <is>
           <t>К25 × 19,05</t>
         </is>
       </c>
-      <c r="E88" s="13" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
         </is>
       </c>
-      <c r="F88" s="12" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G88" s="14" t="inlineStr">
+      <c r="G89" s="14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="43.5" customHeight="1">
-      <c r="A89" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="7" t="inlineStr">
+    <row r="90" ht="43.5" customHeight="1">
+      <c r="A90" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>Хомут червячный нерж.</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>6 / 30 / 8</t>
         </is>
       </c>
-      <c r="G89" s="8" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>8 / 32 / 10</t>
         </is>
       </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="70.5" customHeight="1">
-      <c r="A90" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="B90" s="12" t="n"/>
-      <c r="C90" s="13" t="inlineStr">
+    <row r="91" ht="70.5" customHeight="1">
+      <c r="A91" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="B91" s="12" t="n"/>
+      <c r="C91" s="13" t="inlineStr">
         <is>
           <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D91" s="12" t="inlineStr">
         <is>
           <t>12 мм / ¼″</t>
         </is>
       </c>
-      <c r="E90" s="13" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
         </is>
       </c>
-      <c r="F90" s="12" t="inlineStr">
+      <c r="F91" s="12" t="inlineStr">
         <is>
           <t>≈10</t>
         </is>
       </c>
-      <c r="G90" s="14" t="inlineStr">
+      <c r="G91" s="14" t="inlineStr">
         <is>
           <t>≈12</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I90" s="15" t="inlineStr">
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J90"/>
+  <autoFilter ref="A1:J91"/>
   <mergeCells count="9">
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A74:J74"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A67:J67"/>
     <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A87:J87"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A86:J86"/>
-    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A68:J68"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
@@ -4251,18 +4296,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId69"/>
@@ -4274,10 +4319,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4298,7 +4344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6087,33 +6133,33 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="43.5" customHeight="1">
       <c r="A50" s="5" t="n">
         <v>42</v>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Стойка / кронштейны и хомуты-держатели для колонн</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Ø38</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -6123,17 +6169,17 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут для труб</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="43.5" customHeight="1">
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="11" t="n">
         <v>43</v>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -6143,17 +6189,17 @@
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6163,7 +6209,7 @@
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
@@ -6173,27 +6219,27 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6203,7 +6249,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
@@ -6213,29 +6259,29 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6243,7 +6289,7 @@
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: фильтр межкламповый K50,5 316</t>
         </is>
       </c>
     </row>
@@ -6253,27 +6299,27 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6283,7 +6329,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый K50,5 316</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6339,7 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -6303,17 +6349,17 @@
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -6323,22 +6369,22 @@
       </c>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16.5" customHeight="1">
       <c r="A56" s="5" t="n">
         <v>48</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -6348,12 +6394,12 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -6363,7 +6409,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6424,7 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -6388,12 +6434,12 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
@@ -6418,7 +6464,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -6428,12 +6474,12 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -6447,23 +6493,23 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="16.5" customHeight="1">
+    <row r="59" ht="30" customHeight="1">
       <c r="A59" s="11" t="n">
         <v>51</v>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 101,6 мм (≈625 ₽)</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>Ø101,6 (K119, 4″)</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
@@ -6473,7 +6519,7 @@
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
@@ -6483,7 +6529,7 @@
       </c>
       <c r="H59" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут трубный 101,6 мм</t>
         </is>
       </c>
     </row>
@@ -6493,27 +6539,27 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 38,1 мм (≈320 ₽)</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>Ø38,1 (1½″)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -6523,7 +6569,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
+          <t>Гросснер: хомут трубный 38,1 мм</t>
         </is>
       </c>
     </row>
@@ -6533,27 +6579,27 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>по Ø: ½″, K119</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>6 / 30 / 8</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>8 / 32 / 10</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -6563,37 +6609,37 @@
       </c>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
+          <t>Гросснер: хомут червячный</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16.5" customHeight="1">
       <c r="A62" s="5" t="n">
         <v>54</v>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1½″) × 400</t>
+          <t>по Ø: ½″</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -6603,7 +6649,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп 1½″ × 400</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
@@ -6613,17 +6659,17 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К50,5 (1½″) × 400</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
@@ -6643,7 +6689,7 @@
       </c>
       <c r="H63" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: царга кламп 1½″ × 400</t>
         </is>
       </c>
     </row>
@@ -6653,27 +6699,27 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
@@ -6683,7 +6729,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
+          <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
@@ -6693,29 +6739,29 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
+          <t>2,5 м</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6723,7 +6769,7 @@
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
+          <t>Гросснер: силикон PF, DN ¼″</t>
         </is>
       </c>
     </row>
@@ -6738,22 +6784,22 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>≈14 м</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -6773,12 +6819,12 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
@@ -6788,12 +6834,12 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -6803,7 +6849,7 @@
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
@@ -6813,27 +6859,27 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -6843,7 +6889,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
@@ -6853,214 +6899,254 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
           <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>К25 × 6,35</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F69" s="14" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>КемИнС</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>Ø ≈ 110 мм</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr">
+      <c r="G72" s="17" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Пневмо-Электро</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="16.5" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="16.5" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>¼″</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>Реактор R-1</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>≈3 м</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Пневмо-Электро: трубки PTFE</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Профрезина</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="43.5" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="43.5" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>500×500×3</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H75"/>
+  <autoFilter ref="A1:H76"/>
   <mergeCells count="10">
-    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A75:H75"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <hyperlinks>
@@ -7125,9 +7211,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -8,13 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="По узлам схемы" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Сводная к заказу" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Аргоновая линия" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Сводная к заказу" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводная к заказу'!$A$1:$H$76</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Сводная к заказу'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Аргоновая линия'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Аргоновая линия'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Сводная к заказу'!$A$1:$H$93</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +79,11 @@
       <b val="1"/>
       <color rgb="007F6000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00404040"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="7">
@@ -195,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,6 +249,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2884,17 +2895,17 @@
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>конец гребёнки → V-F1 (аргон A4 — граница с линией смежников)</t>
+          <t>конец гребёнки нутча → штуцер S6510 6-1/4 → кран V-F1 (линия A4, лист «Аргоновая линия»)</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -2914,7 +2925,7 @@
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4355,719 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Поз. на схеме</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Размер</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Назначение / где стоит</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>По схеме</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>К закупке</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Где купить</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Доп. ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Аргон: источник и регулировка расхода (баллон → редуктор → PR-1)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>AR-1</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Баллон аргона 40 л (Ar ≥ 99,998 %)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>40 л, W21,8</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>источник аргона; подтвердить, есть ли у заказчика</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Поставщик газа</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="57" customHeight="1">
+      <c r="A4" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Редуктор баллонный аргоновый с манометрами, низкое давление на выходе 0,2–0,3 бар (двухступенчатый или с точной регулировкой)</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>вход W21,8; выход — уточнить (G¼″)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>после вентиля баллона; уставка 200–300 мбар (раздел 13); подтвердить, есть ли</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Яндекс.Маркет: редуктор аргоновый</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70.5" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>PR-1</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Ротаметр газовый с игольчатым вентилем (стекло, поплавок), диапазон до 10 л/мин; для синтеза 0,1–0,2 л/мин — второй, малый (0,1–1 л/мин), либо один с вентилем тонкой регулировки</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>присоединение — уточнить (G¼″)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>после редуктора: синтез 0,1–0,2 л/мин, продувки 3–5, выгрузка ≈10 л/мин</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Яндекс.Маркет: ротаметр с вентилем</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Аргон: трубка полиамидная 6×4 и цанговые фитинги</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="70.5" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Трубка полиамидная (PA12) 6×4 мм, Camozzi TRN 6/4, до 28 бар</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Ø6 × 4</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>все линии аргона: редуктор → PR-1 → раздаточный коллектор → A1 (гребёнка AV-1), A2 (G-1), A3 (тара), A4 (нутч). Длины по 3D-модели: ≈0,7 + 0,2 + 1,5 + 2,8 + 2,3 + 5,6 м; уточнить по месту</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>≈14 м</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>18 м</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): трубка TRN 6/4 (под заказ 7 дней)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="57" customHeight="1">
+      <c r="A8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Штуцер прямой цанговый с наружной резьбой G¼″ × трубка 6 мм, Camozzi S6510 6-1/4</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>G¼″ × 6</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>выход редуктора (1), вход и выход PR-1 (2), конец A1 на переходнике AV-1 (1), конец A4 на гребёнке нутча (1), ввод A2 в G-1 (1); резьбу редуктора и PR-1 подтвердить</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): S6510 6-1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Тройник T-образный цанговый 6 мм, Camozzi 6540 6</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>раздаточный коллектор после PR-1: 4 отвода A1–A4</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): тройник 6540 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Заглушка цанговая 6 мм (в порт фитинга), Camozzi 6900 6</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>конец раздаточного коллектора (резерв под 5-й отвод)</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): заглушка 6900 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Аргон: краны и обратные клапаны</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="43.5" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>A1–A4, V-F1</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровой цанговый 2/2, трубка 6 мм — 6 мм, Aignep 06560 00 002</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>A1 — гребёнка (AV-1), A2 — генератор G-1, A3 — тара MeSiCl₃ / PDMS-OH, A4 — нутч; V-F1 — у гребёнки нутча</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Би энд Би: Aignep 06560 00 002 (под заказ 7–10 дней)</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>pnevmo.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="57" customHeight="1">
+      <c r="A13" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>NRV A1–A3, NRV-5</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Клапан обратный цанговый 6 мм, Camozzi PVNR 6: открытие 0,02 бар, корпус POM, уплотнения EPDM</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>после кранов A1, A2, A3 (обязательно на A1 и A2 — лист 6); NRV-5 — на линии A4 перед V-F1 (не пускает пары растворителя из нутча в аргон)</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): PVNR 6 (нет в наличии — аналог Aignep по доп. ссылке)</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>bb-engineering.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Аргон: переходы на аппараты (границы линии)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>AV-1</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>кран AV-1 на гребёнке реактора → штуцер S6510 6-1/4 (вместо переходника на G½″)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Переходник на штуцер аргона крышки G-1 → резьба G¼″ внутр.</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>по порту G-1</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>ввод аргона A2 в генератор; резьбу порта крышки G-1 замерить (чек-лист)</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>по замеру (нерж. 316)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="43.5" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Ввод трубки 6 мм в крышку-переходник тары — через свободный порт крышки (GL14 с уплотнением под трубку 6 мм)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>линия A3 в тару MeSiCl₃ / PDMS-OH; крышка — в разделе «Реактор R-1: дозирование» основного листа</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Germeon: крышка DURAN GL45, 2 порта</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Аргоновая линия по листу 6 монтажных чертежей и сборке A1: баллон AR-1 → редуктор (200–300 мбар) → ротаметр PR-1 с вентилем → раздаточный коллектор (4 тройника 6 мм) → краны A1–A4 → обратные клапаны (A1, A2, A3; на A4 — NRV-5 у нутча) → потребители: A1 — гребёнка реактора (AV-1), A2 — генератор G-1, A3 — тара MeSiCl₃ / PDMS-OH, A4 — гребёнка нутча (V-F1). Трубка — полиамид PA12 6×4 на цанговых фитингах (аргон сухой и инертный, давление ≤ 0,3 бар). Запас: фитинги и заглушки +2, краны, клапаны, тройники +1, трубка ≈+30 %. Баллон, редуктор и ротаметр — подтвердить, есть ли у заказчика.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J17"/>
+  <mergeCells count="5">
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId14"/>
+  </hyperlinks>
+  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8&amp;A — стр. &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4536,7 +5259,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Hydrohype</t>
+          <t>Germeon</t>
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
@@ -4547,50 +5270,50 @@
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="43.5" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+          <t>Ввод трубки 6 мм в крышку-переходник тары — через свободный порт крышки (GL14 с уплотнением под трубку 6 мм)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>под корпус 10″</t>
+          <t>6 мм</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
+          <t>A3: Аргон</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
+          <t>Germeon: крышка DURAN GL45, 2 порта</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Industriation</t>
+          <t>Hydrohype</t>
         </is>
       </c>
       <c r="B8" s="3" t="n"/>
@@ -4607,27 +5330,27 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Трубка PTFE 10×12, бухта</t>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>10×12</t>
+          <t>под корпус 10″</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>≈8 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>10 м</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -4637,14 +5360,14 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Industriation: PTFE 12/10</t>
+          <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Rizur</t>
+          <t>Industriation</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -4661,138 +5384,138 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
+          <t>Трубка PTFE 10×12, бухта</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>10×12</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>≈8 м</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>10 м</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Industriation: PTFE 12/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Rizur</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
           <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>⅛″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Сжатый воздух к насосам P-2, P-4</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>Rizur: ниппель переходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Titan Lock</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>ID 6 мм</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>4 м</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Ампика</t>
+          <t>Titan Lock</t>
         </is>
       </c>
       <c r="B15" s="3" t="n"/>
@@ -4803,29 +5526,33 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n"/>
     </row>
-    <row r="16" ht="43.5" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n"/>
+          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ID 6 мм</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>P-2: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; P-4: Фильтрация F-2 и фасовка (P-4)</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -4835,14 +5562,14 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+          <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Гросснер</t>
+          <t>Ампика</t>
         </is>
       </c>
       <c r="B17" s="3" t="n"/>
@@ -4853,23 +5580,19 @@
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="43.5" customHeight="1">
       <c r="A18" s="5" t="n">
         <v>10</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>по порту</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Сжатый воздух к насосам P-2, P-4</t>
+          <t>P-2: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; P-4: Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -4879,247 +5602,195 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: ёлочка НР</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="11" t="n">
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Би энд Би</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: диоптр кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="43.5" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>12</v>
-      </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Диоптр кламп 1½″ ASME-BPE, AISI 316, PN10; уплотнения стекла в каталоге — силикон: уточнить у Гросснера EPDM/PTFE (≈5 540 ₽)</t>
+          <t>Кран шаровой цанговый 2/2, трубка 6 мм — 6 мм, Aignep 06560 00 002</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1½″), L — по каталогу</t>
+          <t>6 мм</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>A1–A4, V-F1: Аргон</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: диоптр кламп 1½″</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="43.5" customHeight="1">
-      <c r="A21" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Клапан обратный кламп пружинный</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>NRV-6: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: клапан обратный кламп</t>
-        </is>
-      </c>
+          <t>Би энд Би: Aignep 06560 00 002 (под заказ 7–10 дней)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="4" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Заглушка цанговая 6 мм (в порт фитинга), Camozzi 6900 6</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Аргон</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): заглушка 6900 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="43.5" customHeight="1">
+      <c r="A23" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Клапан обратный цанговый 6 мм, Camozzi PVNR 6: открытие 0,02 бар, корпус POM, уплотнения EPDM</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>NRV A1–A3, NRV-5: Аргон</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): PVNR 6 (нет в наличии — аналог Aignep по доп. ссылке)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>NRV-3: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Клапан обратный муфтовый пружинный, AISI 316, внутр. резьба ¼″ (≈1 280 ₽)</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>¼″ ВР (DN8)</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>NRV-4: Реактор R-1</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: клапан обратный муфтовый ¼″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
+          <t>Тройник T-образный цанговый 6 мм, Camozzi 6540 6</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>6 мм</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>F-2: Фильтрация F-2 и фасовка (P-4)</t>
+          <t>Аргон</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -5129,37 +5800,37 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: корпус 10″</t>
+          <t>Би энд Би (Camozzi): тройник 6540 6</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Кран игольчатый нерж. AISI 316, внутр. резьба ¼″, PN 413 (≈2 900 ₽)</t>
+          <t>Трубка полиамидная (PA12) 6×4 мм, Camozzi TRN 6/4, до 28 бар</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>¼″ ВР</t>
+          <t>Ø6 × 4</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>FV-1: Реактор R-1</t>
+          <t>Аргон</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -5169,37 +5840,37 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран игольчатый ¼″ 316</t>
+          <t>Би энд Би (Camozzi): трубка TRN 6/4 (под заказ 7 дней)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп 1″, AISI 316L, PN10 (≈3 265 ₽)</t>
+          <t>Штуцер прямой цанговый с наружной резьбой G¼″ × трубка 6 мм, Camozzi S6510 6-1/4</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>G¼″ × 6</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>V-P2: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Аргон</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -5209,199 +5880,173 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп 1″ 316L</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="178.5" customHeight="1">
-      <c r="A27" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>V-P3: Реактор R-1; SV-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-P1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; SP-1, V-S1: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; SV-F1: Нутч F-1 (K119) и гребёнка газов нутча; VV-2: Нутч F-1 (K119) и гребёнка газов нутча; V-F2: Нутч F-1 (K119) и гребёнка газов нутча; V-F3: Фильтрация F-2 и фасовка (P-4)</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп ½″ 316L</t>
-        </is>
-      </c>
+          <t>Би энд Би (Camozzi): S6510 6-1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Гросснер</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="4" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>по порту</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Сжатый воздух к насосам P-2, P-4</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: ёлочка НР</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16.5" customHeight="1">
+      <c r="A29" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: диоптр кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="43.5" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Диоптр кламп 1½″ ASME-BPE, AISI 316, PN10; уплотнения стекла в каталоге — силикон: уточнить у Гросснера EPDM/PTFE (≈5 540 ₽)</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>К50,5 (1½″), L — по каталогу</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: диоптр кламп 1½″</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="43.5" customHeight="1">
+      <c r="A31" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>½″ ВР (DN15)</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>V-G2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Клапан обратный кламп пружинный</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>NRV-6: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: кран шаровой ½″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>PI-5: Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Отвод кламп 90°</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: отвод кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Отвод кламп 90°, AISI 316</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5409,117 +6054,117 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
+          <t>Гросснер: клапан обратный кламп</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>NRV-3: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Клапан обратный муфтовый пружинный, AISI 316, внутр. резьба ¼″ (≈1 280 ₽)</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>¼″ ВР (DN8)</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>NRV-4: Реактор R-1</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: клапан обратный муфтовый ¼″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>10″</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: патроны</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="70.5" customHeight="1">
-      <c r="A33" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 → К25</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Реактор R-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>К119 → К64</t>
-        </is>
-      </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>F-2: Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5529,39 +6174,39 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
+          <t>Гросснер: корпус 10″</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Кран игольчатый нерж. AISI 316, внутр. резьба ¼″, PN 413 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>¼″ ВР</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>FV-1: Реактор R-1</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5569,39 +6214,39 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: кран игольчатый ¼″ 316</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+          <t>Кран шаровой кламп 1″, AISI 316L, PN10 (≈3 265 ₽)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>К25 × G¼″ вн.</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>V-P2: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5609,37 +6254,37 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
+          <t>Гросснер: кран кламп 1″ 316L</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="178.5" customHeight="1">
       <c r="A37" s="11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>V-P3: Реактор R-1; SV-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-P1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; SP-1, V-S1: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; SV-F1: Нутч F-1 (K119) и гребёнка газов нутча; VV-2: Нутч F-1 (K119) и гребёнка газов нутча; V-F2: Нутч F-1 (K119) и гребёнка газов нутча; V-F3: Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -5649,37 +6294,37 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>½″ ВР (DN15)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Фильтрация F-2 и фасовка (P-4); Сжатый воздух к насосам P-2, P-4</t>
+          <t>V-G2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -5689,27 +6334,27 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Гросснер: кран шаровой ½″ 316</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>К25 × G½″ нар.</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>PI-5: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -5719,7 +6364,7 @@
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -5729,39 +6374,39 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Отвод кламп 90°</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5769,37 +6414,37 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="57" customHeight="1">
+          <t>Гросснер: отвод кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -5809,37 +6454,37 @@
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: отвод кламп 90°</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -5849,37 +6494,37 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+          <t>Гросснер: патроны</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="70.5" customHeight="1">
       <c r="A43" s="11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Реактор R-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -5889,27 +6534,27 @@
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -5919,7 +6564,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -5929,37 +6574,37 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="11" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -5969,37 +6614,37 @@
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 × G¼″ вн.</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -6009,27 +6654,27 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="11" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -6039,7 +6684,7 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -6049,37 +6694,37 @@
       </c>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="43.5" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча; Фильтрация F-2 и фасовка (P-4); Сжатый воздух к насосам P-2, P-4; AV-1: Аргон</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6089,27 +6734,27 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 × G½″ нар.</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -6119,49 +6764,49 @@
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>К25 × ¼″</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Реактор R-1</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="43.5" customHeight="1">
-      <c r="A50" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6169,37 +6814,37 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
+          <t>Гросснер: кламп – резьба наружная</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="57" customHeight="1">
       <c r="A51" s="11" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 × ½″</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6209,17 +6854,17 @@
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
+          <t>Гросснер: кламп – резьба наружная</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -6229,17 +6874,17 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6249,17 +6894,17 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -6269,17 +6914,17 @@
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6289,37 +6934,37 @@
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый K50,5 316</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6329,159 +6974,159 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>К64 (2″)</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп PTFE</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16.5" customHeight="1">
-      <c r="A56" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Кламп-соединения на всю установку</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16.5" customHeight="1">
-      <c r="A57" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>Кламп-соединения на всю установку</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16.5" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Хомут кламп обычный, AISI 304</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>К64 (2″)</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Кламп-соединения на всю установку</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6489,77 +7134,77 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="11" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 101,6 мм (≈625 ₽)</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Ø101,6 (K119, 4″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="43.5" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: хомут трубный 101,6 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 38,1 мм (≈320 ₽)</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Ø38,1 (1½″)</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -6569,37 +7214,37 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут трубный 38,1 мм</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="11" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -6609,22 +7254,22 @@
       </c>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16.5" customHeight="1">
+          <t>Гросснер: тройник кламп 1″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>по Ø: ½″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -6634,12 +7279,12 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -6649,27 +7294,27 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="11" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1½″) × 400</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
@@ -6679,7 +7324,7 @@
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
@@ -6689,39 +7334,39 @@
       </c>
       <c r="H63" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп 1½″ × 400</t>
+          <t>Гросснер: фильтр межкламповый K50,5 316</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6729,157 +7374,157 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16.5" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16.5" customHeight="1">
+      <c r="A67" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1″)</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16.5" customHeight="1">
+      <c r="A68" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>DN ¼″ (ID 6,4)</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="inlineStr">
-        <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>2,5 м</t>
-        </is>
-      </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>4 м</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>DN 1″ (ID 25,4)</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>4 м</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: силикон армированный TSO</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="11" t="n">
-        <v>59</v>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>DN ¾″ (ID 19)</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>≈14 м</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="inlineStr">
-        <is>
-          <t>18 м</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: силикон армированный TSO</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="5" t="n">
-        <v>60</v>
-      </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -6889,37 +7534,37 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="11" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 101,6 мм (≈625 ₽)</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × 25,4</t>
+          <t>Ø101,6 (K119, 4″)</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -6929,222 +7574,830 @@
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
+          <t>Гросснер: хомут трубный 101,6 мм</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 38,1 мм (≈320 ₽)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Ø38,1 (1½″)</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут трубный 38,1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>Хомут червячный нерж.</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>8–12 / 25–40 / 32–50</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>6 / 30 / 8</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>8 / 32 / 10</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут червячный</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16.5" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Хомут-держатель для труб нерж.</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>по Ø: ½″</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>1 компл.</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут-держатель</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>К25 × 6,35</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1½″) × 400</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: царга кламп 1½″ × 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>К119 (4″) × 500</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: царга кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>DN ¼″ (ID 6,4)</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K25 × 6,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>КемИнС</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="4" t="n"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Ø ≈ 110 мм</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>отрез 0,5 м²</t>
-        </is>
-      </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>КемИнС: фильтровальные ткани PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="4" t="n"/>
-    </row>
-    <row r="74" ht="16.5" customHeight="1">
-      <c r="A74" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>¼″</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Реактор R-1</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>≈3 м</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>5 м</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>Пневмо-Электро: трубки PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Профрезина</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="43.5" customHeight="1">
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>2,5 м</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: силикон PF, DN ¼″</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
       <c r="A76" s="5" t="n">
         <v>65</v>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>DN 1″ (ID 25,4)</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>4 м</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>5 м</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: силикон армированный TSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>DN ¾″ (ID 19)</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>≈14 м</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>18 м</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: силикон армированный TSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>К25 × 19,05</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Рукава, трубки, крепёж — общее</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 19,05</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 × 25,4</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>К25 × 6,35</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: штуцер K25 × 6,35</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>КемИнС</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n"/>
+      <c r="C81" s="3" t="n"/>
+      <c r="D81" s="3" t="n"/>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="4" t="n"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Ø ≈ 110 мм</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>отрез 0,5 м²</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>КемИнС: фильтровальные ткани PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n"/>
+      <c r="C83" s="3" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="4" t="n"/>
+    </row>
+    <row r="84" ht="16.5" customHeight="1">
+      <c r="A84" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>¼″</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Реактор R-1</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>≈3 м</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>5 м</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро: трубки PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Поставщик газа</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n"/>
+      <c r="C85" s="3" t="n"/>
+      <c r="D85" s="3" t="n"/>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="4" t="n"/>
+    </row>
+    <row r="86" ht="16.5" customHeight="1">
+      <c r="A86" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Баллон аргона 40 л (Ar ≥ 99,998 %)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>40 л, W21,8</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>AR-1: Аргон</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Поставщик газа</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Профрезина</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n"/>
+      <c r="C87" s="3" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="4" t="n"/>
+    </row>
+    <row r="88" ht="43.5" customHeight="1">
+      <c r="A88" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
           <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>500×500×3</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>1 лист</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>2 листа</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
         <is>
           <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Яндекс.Маркет</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="43.5" customHeight="1">
+      <c r="A90" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Редуктор баллонный аргоновый с манометрами, низкое давление на выходе 0,2–0,3 бар (двухступенчатый или с точной регулировкой)</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>вход W21,8; выход — уточнить (G¼″)</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Аргон</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>Яндекс.Маркет: редуктор аргоновый</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="57" customHeight="1">
+      <c r="A91" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>Ротаметр газовый с игольчатым вентилем (стекло, поплавок), диапазон до 10 л/мин; для синтеза 0,1–0,2 л/мин — второй, малый (0,1–1 л/мин), либо один с вентилем тонкой регулировки</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>присоединение — уточнить (G¼″)</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>PR-1: Аргон</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G91" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>Яндекс.Маркет: ротаметр с вентилем</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>по замеру (нерж. 316)</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
+      <c r="D92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="4" t="n"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Переходник на штуцер аргона крышки G-1 → резьба G¼″ внутр.</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>по порту G-1</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>A2: Аргон</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>по замеру (нерж. 316)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H76"/>
-  <mergeCells count="10">
+  <autoFilter ref="A1:H93"/>
+  <mergeCells count="16">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A83:H83"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A81:H81"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A17:H17"/>
@@ -7156,65 +8409,76 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -12,11 +12,11 @@
     <sheet name="Сводная к заказу" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$92</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Аргоновая линия'!$A$1:$J$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Аргоновая линия'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Сводная к заказу'!$A$1:$H$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Сводная к заказу'!$A$1:$H$89</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,11 +82,17 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00404040"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +122,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -203,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -250,7 +261,10 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -618,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -722,7 +736,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>штуцер P3 → V-P3 (запас на все 10 кранов ½″ — здесь)</t>
+          <t>штуцер P3 → V-P3 (запас на все 11 кранов ½″ — здесь)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1200,17 +1214,17 @@
       <c r="B15" s="12" t="n"/>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 × 6,35</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>V-G1 → обжим 12 мм (трубка 10×12 на C-1)</t>
+          <t>V-G1 → шланг PF ¼″ на C-1 (газ CH₃NH₂, этап 1)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -1230,7 +1244,7 @@
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
     </row>
@@ -1635,24 +1649,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="43.5" customHeight="1">
+    <row r="26" ht="70.5" customHeight="1">
       <c r="A26" s="5" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 × 6,35</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>входы и выходы C-1, C-2 (4) и NRV-3 с двух сторон (2) → обжим 12 мм (трубка 10×12); запас на все 7 — здесь</t>
+          <t>газ CH₃NH₂, этап 1 — шланг PF ¼″: входы и выходы C-1, C-2 (4), вход V-G2 (1), выход NRV-3 на T2 (1); хомуты червячные 8–12 мм по 2 на конец; запас +2 на все ёлочки 6,35 — в разделе генератора</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1662,7 +1676,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -1672,7 +1686,7 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: штуцер K25 × 6,35</t>
         </is>
       </c>
     </row>
@@ -1687,17 +1701,17 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>½″ ВР (DN15)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1; на трубку 10×12 — 2 обжимных фитинга 12 мм × ½″ нар.</t>
+          <t>газ после колонн, перед NRV-3: закрывать при вакуумировании реактора и продувке G-1; кламп с двух сторон: шланг от C-2 (через штуцер-ёлочку) → V-G2 → NRV-3</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -1707,7 +1721,7 @@
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -1717,7 +1731,7 @@
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран шаровой ½″ 316</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
@@ -1766,34 +1780,34 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
+    <row r="29" ht="43.5" customHeight="1">
       <c r="A29" s="11" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="12" t="n"/>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Трубка PTFE 10×12, бухта</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>10×12</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>газ CH₃NH₂: V-G1 → C-1 → C-2 → T2</t>
+          <t>газ CH₃NH₂, этап 1: V-G1 → C-1 (≈1,5 м), C-1 → C-2 (≈1,5 м), C-2 → V-G2 (≈1 м), NRV-3 → T2 (≈3 м); длины уточнить по месту</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>≈8 м</t>
+          <t>≈7 м</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>10 м</t>
+          <t>9 м</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -1803,2454 +1817,2495 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>Industriation: PTFE 12/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="43.5" customHeight="1">
+          <t>Гросснер: силикон PF, DN ¼″</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="57" customHeight="1">
       <c r="A30" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="7" t="inlineStr">
         <is>
+          <t>Этап 2: трубка PTFE 10×12 + обжимные фитинги 12 мм + переходники кламп K25 – наружная ½″ (7 шт.) — замена силиконовых шлангов газовой линии</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>10×12</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>после первых пусков: газ V-G1 → C-1 → C-2 → V-G2/NRV-3 → T2 перевести на PTFE (силикон проницаем для влаги и метиламина). Сейчас НЕ закупать</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>≈8 м</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>ЭТАП 2</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Industriation: PTFE 12/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="43.5" customHeight="1">
+      <c r="A31" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
           <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 38,1 мм (≈320 ₽)</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Ø38,1 (1½″)</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>крепление колонн C-1, C-2 к раме или стенду — по 2 на колонну (на царгу, выше и ниже середины)</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут трубный 38,1 мм</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>сразу под краном слива BV-1 — выход в горизонталь</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Гросснер: отвод кламп 90°</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="57" customHeight="1">
-      <c r="A33" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="13" t="inlineStr">
+    <row r="34" ht="57" customHeight="1">
+      <c r="A34" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>1-й после отвода под BV-1: отвод 45° вниз — проба SP-1 (через переход 50,5 → 25), суспензия не застаивается; запас на оба тройника 45° — здесь</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="43.5" customHeight="1">
-      <c r="A34" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="7" t="inlineStr">
+    <row r="35" ht="43.5" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>2-й: вбок V-S1 на бочку (через переход 50,5 → 25), прямо — выгрузка на P-2 (переходных тройников 50,5 × 25 у Гросснера нет)</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="13" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>К50,5 → К25</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>отводы тройников → SP-1 и V-S1</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="57" customHeight="1">
-      <c r="A36" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="57" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>V-P2</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Кран шаровой кламп 1″, AISI 316L, PN10 (≈3 265 ₽)</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>перед P-2: после тройника V-S1, перед рукавом на насос — отсечь насос при обслуживании, перекрыть линию из реактора при заборе растворителя из бочки</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп 1″ 316L</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>SP-1, V-S1</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>SP-1 — проба, V-S1 — бочка растворителя</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="7" t="inlineStr">
+    <row r="39" ht="16.5" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Отвод кламп 90°</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>носик пробоотбора после SP-1</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Гросснер: отвод кламп</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="43.5" customHeight="1">
-      <c r="A39" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
+    <row r="40" ht="43.5" customHeight="1">
+      <c r="A40" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>P-2</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>выгрузка суспензии на нутч</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="43.5" customHeight="1">
-      <c r="A40" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="7" t="inlineStr">
+    <row r="41" ht="43.5" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>P-2 вход/выход и P-4 вход/выход (запас — здесь)</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Rizur: ниппель RizurLok-NP</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="13" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>P-2: вход и выход → рукав 1″</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="7" t="inlineStr">
+    <row r="43" ht="43.5" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>К50,5 × 25,4</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>рукава 1″: тройник V-S1 → P-2, P-2 → нутч (4 конца)</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>рукав 1″ (силикон TSO): кран V-P2 → вход P-2 (2 конца), выход P-2 → вход нутча F-1 (2 конца); хомуты 32–50 по 2 на конец</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K50,5 × 25,4</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="43.5" customHeight="1">
-      <c r="A43" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="13" t="inlineStr">
+    <row r="44" ht="43.5" customHeight="1">
+      <c r="A44" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>слив → P-2 (1,5 м), P-2 → нутч (2,5 м); хомуты 32–50; армирование — чтобы не сплющивался на всасе</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>4 м</t>
         </is>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>5 м</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="4" t="n"/>
-    </row>
-    <row r="45" ht="43.5" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="43.5" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>вход нутча сверху: прямо — суспензия, отвод 45° — гребёнка газов (через переход 50,5 → 25)</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B46" s="12" t="n"/>
-      <c r="C46" s="13" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="B47" s="12" t="n"/>
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>К50,5 → К25</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>отвод тройника → рукав на гребёнку (1); низ нутча → V-F2 (1)</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I46" s="15" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="7" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>К64 → К50,5</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>крышка нутча и низ нутча</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>Гросснер: переход 64 × 50,5 316</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="13" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" s="12" t="n"/>
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>К119 → К64</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>крышка нутча и низ нутча (4″ → 1″ и 4″ → ½″ одной деталью у Гросснера нет)</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
         <is>
           <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="43.5" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="7" t="inlineStr">
+    <row r="50" ht="43.5" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>2 диоптра: верхний — уровень суспензии; нижний — над межкламповым фильтром, видно осадок и слой Na₂SO₄ на ткани</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Гросснер: диоптр кламп</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>F-1</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>К119 (4″) × 500</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>корпус нутча: 2 царги подряд — 7,4 л, весь осадок партии</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
         <is>
           <t>Гросснер: царга кламп</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="43.5" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="7" t="inlineStr">
+    <row r="52" ht="43.5" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>опора слоя (ткань PTFE/PP + Na₂SO₄), под нижним диоптром — отдельная деталь между двумя стыками</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="43.5" customHeight="1">
-      <c r="A52" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="13" t="inlineStr">
+    <row r="53" ht="43.5" customHeight="1">
+      <c r="A53" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>Ø ≈ 110 мм</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>фильтрующий слой нутча под Na₂SO₄ (сетка фильтра 0,5 мм сама осадок не держит); расходник — по 1 кругу на партию</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>отрез 0,5 м²</t>
         </is>
       </c>
-      <c r="H52" s="17" t="inlineStr">
+      <c r="H53" s="17" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr">
+      <c r="I53" s="15" t="inlineStr">
         <is>
           <t>КемИнС: фильтровальные ткани PP</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="7" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>гребёнка нутча: PI-5, SV-F1, VV-2 (запас — здесь)</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>PI-5</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
         <is>
           <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>на отвод тройника гребёнки</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
+      <c r="F55" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
         <is>
           <t>Гросснер: мановакуумметр 63 мм кламп</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="57" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
+    <row r="56" ht="57" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>SV-F1</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>сброс давления нутча вручную (вместо PSV-4): тройник гребёнки → кран → ёлочка → рукав ¾″ в коллектор сбросов (коллектор — у смежников)</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>VV-2</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>вакуум нутча</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="7" t="inlineStr">
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>конец гребёнки нутча → штуцер S6510 6-1/4 → кран V-F1 (линия A4, лист «Аргоновая линия»)</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>V-F2</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>выход нутча (фильтрат)</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G58" s="14" t="inlineStr">
+      <c r="G59" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>F-1</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 101,6 мм (≈625 ₽)</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>Ø101,6 (K119, 4″)</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>крепление нутча F-1 к раме / опоре — 2 шт. на царги K119</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут трубный 101,6 мм</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="16.5" customHeight="1">
-      <c r="A60" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="13" t="inlineStr">
+    <row r="61" ht="16.5" customHeight="1">
+      <c r="A61" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>по Ø: ½″</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>крепление гребёнки нутча к раме — по месту</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="G60" s="14" t="inlineStr">
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>1 компл.</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I60" s="15" t="inlineStr">
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
-      <c r="J61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="43.5" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="4" t="n"/>
+    </row>
+    <row r="63" ht="43.5" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>P-4</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
         </is>
       </c>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>фильтрат нутча → F-2</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="13" t="inlineStr">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr">
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G63" s="14" t="inlineStr">
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>F-2</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Корпус микропористого фильтра 10″ на клампах</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>10″</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>Гросснер: корпус 10″</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="13" t="inlineStr">
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>10″</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>по 2 шт. каждого рейтинга</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>Гросснер: патроны</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="7" t="inlineStr">
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>под корпус 10″</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>Hydrohype: кольца в оболочке FEP</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>V-F3</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>выход F-2 → налив</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="G68" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Сжатый воздух к насосам P-2, P-4</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="4" t="n"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="4" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>⅛″ NPT × ¼″ BSP</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>вход воздуха насоса (по 1 на насос)</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>Rizur: ниппель переходной</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="13" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="12" t="n"/>
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
-      <c r="E70" s="13" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G70" s="14" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
         <is>
           <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="7" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>G¼ × 8</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>выход регулятора и кламп ¼″ у насоса</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G71" s="8" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <t>BB-Engineering: S6510 8-1/4</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="13" t="inlineStr">
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="13" t="inlineStr">
         <is>
           <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>G¼</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
         </is>
       </c>
-      <c r="F72" s="12" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G72" s="14" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: быстросъёмы EUROPEAN</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="7" t="inlineStr">
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>по порту</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H73" s="17" t="inlineStr">
+      <c r="H74" s="17" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>Гросснер: ёлочка НР</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости; без реактора — на штуцерах P1–P4 родные клампы, без E-1, гребёнки реактора и VP-1)</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
-      <c r="J74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="16.5" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="16.5" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>все соединения ½″ нашей обвязки</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="70.5" customHeight="1">
-      <c r="A76" s="11" t="n">
-        <v>67</v>
-      </c>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="13" t="inlineStr">
+    <row r="77" ht="70.5" customHeight="1">
+      <c r="A77" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="12" t="n"/>
+      <c r="C77" s="13" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D77" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E76" s="13" t="inlineStr">
+      <c r="E77" s="13" t="inlineStr">
         <is>
           <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, кран V-P2, выгрузка P-2, переходы нутча; колонны C-1, C-2: по 4 стыка на колонну — фильтр/переход, диоптр/фильтр, диоптр/царга, царга/верхний переход (8)</t>
         </is>
       </c>
-      <c r="F76" s="12" t="inlineStr">
+      <c r="F77" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G76" s="14" t="inlineStr">
+      <c r="G77" s="14" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="7" t="inlineStr">
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>К64 (2″)</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="57" customHeight="1">
-      <c r="A78" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="13" t="inlineStr">
+    <row r="79" ht="57" customHeight="1">
+      <c r="A79" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="12" t="n"/>
+      <c r="C79" s="13" t="inlineStr">
         <is>
           <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D79" s="12" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
+      <c r="E79" s="13" t="inlineStr">
         <is>
           <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход (с PTFE — только болтовые)</t>
         </is>
       </c>
-      <c r="F78" s="12" t="inlineStr">
+      <c r="F79" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G78" s="14" t="inlineStr">
+      <c r="G79" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I78" s="15" t="inlineStr">
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="43.5" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="7" t="inlineStr">
+    <row r="80" ht="43.5" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>где эфир и углеводороды: дозирование, слив и проба, выгрузка, нутч и его гребёнка, вакуум нутча, P-4, F-2</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr">
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="11" t="n">
-        <v>71</v>
-      </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="13" t="inlineStr">
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E80" s="13" t="inlineStr">
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>BV-1 → отвод, тройники 45° и прямой, кран V-P2, переходы 50,5/25, выгрузка P-2, нутч</t>
         </is>
       </c>
-      <c r="F80" s="12" t="inlineStr">
+      <c r="F81" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G80" s="14" t="inlineStr">
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="43.5" customHeight="1">
-      <c r="A81" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="7" t="inlineStr">
+    <row r="82" ht="43.5" customHeight="1">
+      <c r="A82" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G81" s="8" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
         <is>
           <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="B82" s="12" t="n"/>
-      <c r="C82" s="13" t="inlineStr">
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="B83" s="12" t="n"/>
+      <c r="C83" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>К64 (2″)</t>
         </is>
       </c>
-      <c r="E82" s="13" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>нутч: стыки переходов</t>
         </is>
       </c>
-      <c r="F82" s="12" t="inlineStr">
+      <c r="F83" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G82" s="14" t="inlineStr">
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I82" s="15" t="inlineStr">
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="43.5" customHeight="1">
-      <c r="A83" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B83" s="6" t="n"/>
-      <c r="C83" s="7" t="inlineStr">
+    <row r="84" ht="43.5" customHeight="1">
+      <c r="A84" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="43.5" customHeight="1">
-      <c r="A84" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="B84" s="12" t="n"/>
-      <c r="C84" s="13" t="inlineStr">
+    <row r="85" ht="43.5" customHeight="1">
+      <c r="A85" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="B85" s="12" t="n"/>
+      <c r="C85" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп EPDM</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D85" s="12" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E84" s="13" t="inlineStr">
+      <c r="E85" s="13" t="inlineStr">
         <is>
           <t>без углеводородов: P-1 → G-1 (4), порт G-1 → SV-G1 → рукав (2), выход газа и V-G1 (2), колонны (4), NRV-3 (2), воздух насосов (2)</t>
         </is>
       </c>
-      <c r="F84" s="12" t="inlineStr">
+      <c r="F85" s="12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G84" s="14" t="inlineStr">
+      <c r="G85" s="14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
         <is>
           <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="43.5" customHeight="1">
-      <c r="A85" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="7" t="inlineStr">
+    <row r="86" ht="43.5" customHeight="1">
+      <c r="A86" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп EPDM</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>К50,5 (1½″)</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>колонны: диоптр → царга (2), межкламповый фильтр снизу — с двух сторон: диоптр/фильтр и фильтр/переход (4)</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G85" s="8" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I85" s="10" t="inlineStr">
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
         <is>
           <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="57" customHeight="1">
-      <c r="A86" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="B86" s="12" t="n"/>
-      <c r="C86" s="13" t="inlineStr">
+    <row r="87" ht="57" customHeight="1">
+      <c r="A87" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="B87" s="12" t="n"/>
+      <c r="C87" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D87" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1½″)</t>
         </is>
       </c>
-      <c r="E86" s="13" t="inlineStr">
+      <c r="E87" s="13" t="inlineStr">
         <is>
           <t>верх колонн C-1, C-2 (царга → переход 50,5/25): держит засыпку вместо межклампового фильтра, задерживает пыль сит 3A и NaOH — по 1 на колонну</t>
         </is>
       </c>
-      <c r="F86" s="12" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G86" s="14" t="inlineStr">
+      <c r="G87" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
         <is>
           <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="4" t="n"/>
-    </row>
-    <row r="88" ht="84" customHeight="1">
-      <c r="A88" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="4" t="n"/>
+    </row>
+    <row r="89" ht="84" customHeight="1">
+      <c r="A89" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>≈14 м</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>18 м</t>
         </is>
       </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="inlineStr">
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
         <is>
           <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="43.5" customHeight="1">
-      <c r="A89" s="11" t="n">
-        <v>79</v>
-      </c>
-      <c r="B89" s="12" t="n"/>
-      <c r="C89" s="13" t="inlineStr">
+    <row r="90" ht="43.5" customHeight="1">
+      <c r="A90" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="B90" s="12" t="n"/>
+      <c r="C90" s="13" t="inlineStr">
         <is>
           <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D90" s="12" t="inlineStr">
         <is>
           <t>К25 × 19,05</t>
         </is>
       </c>
-      <c r="E89" s="13" t="inlineStr">
+      <c r="E90" s="13" t="inlineStr">
         <is>
           <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
         </is>
       </c>
-      <c r="F89" s="12" t="inlineStr">
+      <c r="F90" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G89" s="14" t="inlineStr">
+      <c r="G90" s="14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
         <is>
           <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="43.5" customHeight="1">
-      <c r="A90" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="7" t="inlineStr">
+    <row r="91" ht="57" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>Хомут червячный нерж.</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>по 2 на конец: шланг ¼″ на ёлочках 6,35 (3 конца) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>6 / 30 / 8</t>
-        </is>
-      </c>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>8 / 32 / 10</t>
-        </is>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I90" s="10" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>по 2 на конец: шланг PF ¼″ на ёлочках 6,35 — линия P-1 (3 конца) и газ CH₃NH₂ (8 концов: 6 ёлочек + V-G1 + T2) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>22 / 30 / 8</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>24 / 32 / 10</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="70.5" customHeight="1">
-      <c r="A91" s="11" t="n">
-        <v>81</v>
-      </c>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="13" t="inlineStr">
-        <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
-        </is>
-      </c>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t>12 мм / ¼″</t>
-        </is>
-      </c>
-      <c r="E91" s="13" t="inlineStr">
-        <is>
-          <t>газ CH₃NH₂ (10×12): на переходниках кламп/½″ после V-G1, колонн и NRV-3, кран V-G2 (12 × ½″ нар. — 2), ввод в T2; дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту</t>
-        </is>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
-        <is>
-          <t>≈10</t>
-        </is>
-      </c>
-      <c r="G91" s="14" t="inlineStr">
-        <is>
-          <t>≈12</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I91" s="15" t="inlineStr">
+    <row r="92" ht="57" customHeight="1">
+      <c r="A92" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="B92" s="12" t="n"/>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Фитинги обжимные нерж. ¼″ и 8 мм: прямые ¼″ × ¼″ нар.; переход обжим 8 → 6 мм на вентиль T2; отрезок трубки нерж. Ø6 ≈50 мм под шланг</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>¼″ / 8→6 мм</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>дозирование P-3 (¼″): FV-1 и NRV-4 (¼″ × ¼″ нар. — 4), переходник на P3 — по месту; газ CH₃NH₂: ввод в T2 — переход 8 → 6 мм + трубка Ø6 под шланг PF ¼″ (ID 6,4)</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>≈6</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>≈8</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>BB-Engineering: обжимные фитинги</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J91"/>
+  <autoFilter ref="A1:J92"/>
   <mergeCells count="9">
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A88:J88"/>
     <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A62:J62"/>
     <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A87:J87"/>
+    <mergeCell ref="A69:J69"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A68:J68"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
@@ -4280,7 +4335,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId31"/>
@@ -4292,7 +4347,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId43"/>
@@ -4308,18 +4363,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId70"/>
@@ -4331,10 +4386,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5017,7 +5073,7 @@
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Аргоновая линия по листу 6 монтажных чертежей и сборке A1: баллон AR-1 → редуктор (200–300 мбар) → ротаметр PR-1 с вентилем → раздаточный коллектор (4 тройника 6 мм) → краны A1–A4 → обратные клапаны (A1, A2, A3; на A4 — NRV-5 у нутча) → потребители: A1 — гребёнка реактора (AV-1), A2 — генератор G-1, A3 — тара MeSiCl₃ / PDMS-OH, A4 — гребёнка нутча (V-F1). Трубка — полиамид PA12 6×4 на цанговых фитингах (аргон сухой и инертный, давление ≤ 0,3 бар). Запас: фитинги и заглушки +2, краны, клапаны, тройники +1, трубка ≈+30 %. Баллон, редуктор и ротаметр — подтвердить, есть ли у заказчика.</t>
         </is>
@@ -5067,7 +5123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5222,12 +5278,12 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Фитинги обжимные нерж. 12 мм / ¼″: прямые, угольники, переходы на резьбу ¼″–½″; редуктор 12 → 8 мм на вентиль T2</t>
+          <t>Фитинги обжимные нерж. ¼″ и 8 мм: прямые ¼″ × ¼″ нар.; переход обжим 8 → 6 мм на вентиль T2; отрезок трубки нерж. Ø6 ≈50 мм под шланг</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>12 мм / ¼″</t>
+          <t>¼″ / 8→6 мм</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -5237,12 +5293,12 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>≈10</t>
+          <t>≈6</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>≈12</t>
+          <t>≈8</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -5367,7 +5423,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Industriation</t>
+          <t>Rizur</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -5384,27 +5440,27 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Трубка PTFE 10×12, бухта</t>
+          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>10×12</t>
+          <t>¼″ NPT × ¼″ BSP</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>≈8 м</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>10 м</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -5414,91 +5470,91 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Industriation: PTFE 12/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Rizur</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="n">
+          <t>Rizur: ниппель RizurLok-NP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Ниппель переходной нерж. 316 ¼″ NPT нар. × ¼″ BSP нар. (RizurLok-NP или аналог)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>¼″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель RizurLok-NP</t>
-        </is>
-      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Сжатый воздух к насосам P-2, P-4</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Titan Lock</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="4" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Сжатый воздух к насосам P-2, P-4</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ID 6 мм</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>4 м</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -5506,16 +5562,16 @@
           <t>КУПИТЬ</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
-        <is>
-          <t>Rizur: ниппель переходной</t>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Titan Lock: шланги EPDM</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Titan Lock</t>
+          <t>Ампика</t>
         </is>
       </c>
       <c r="B15" s="3" t="n"/>
@@ -5526,33 +5582,29 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="43.5" customHeight="1">
       <c r="A16" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Шланг EPDM химстойкий, ID 6 мм — на будущее, замена силикона после насоса (V-P1 → G-1)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ID 6 мм</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>P-2: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; P-4: Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -5562,14 +5614,14 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Titan Lock: шланги EPDM</t>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Ампика</t>
+          <t>Би энд Би</t>
         </is>
       </c>
       <c r="B17" s="3" t="n"/>
@@ -5580,29 +5632,33 @@
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n"/>
     </row>
-    <row r="18" ht="43.5" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="n">
         <v>10</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n"/>
+          <t>Кран шаровой цанговый 2/2, трубка 6 мм — 6 мм, Aignep 06560 00 002</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>P-2: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; P-4: Фильтрация F-2 и фасовка (P-4)</t>
+          <t>A1–A4, V-F1: Аргон</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -5612,14 +5668,14 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
+          <t>Би энд Би: Aignep 06560 00 002 (под заказ 7–10 дней)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Би энд Би</t>
+          <t>Би энд Би (Camozzi)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n"/>
@@ -5636,7 +5692,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой цанговый 2/2, трубка 6 мм — 6 мм, Aignep 06560 00 002</t>
+          <t>Заглушка цанговая 6 мм (в порт фитинга), Camozzi 6900 6</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -5646,51 +5702,77 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>A1–A4, V-F1: Аргон</t>
+          <t>Аргон</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): заглушка 6900 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="43.5" customHeight="1">
+      <c r="A21" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Клапан обратный цанговый 6 мм, Camozzi PVNR 6: открытие 0,02 бар, корпус POM, уплотнения EPDM</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>6 мм</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>NRV A1–A3, NRV-5: Аргон</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>Би энд Би: Aignep 06560 00 002 (под заказ 7–10 дней)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Би энд Би (Camozzi)</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="4" t="n"/>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Би энд Би (Camozzi): PVNR 6 (нет в наличии — аналог Aignep по доп. ссылке)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Заглушка цанговая 6 мм (в порт фитинга), Camozzi 6900 6</t>
+          <t>Тройник T-образный цанговый 6 мм, Camozzi 6540 6</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -5705,12 +5787,12 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -5720,37 +5802,37 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Би энд Би (Camozzi): заглушка 6900 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="43.5" customHeight="1">
+          <t>Би энд Би (Camozzi): тройник 6540 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Клапан обратный цанговый 6 мм, Camozzi PVNR 6: открытие 0,02 бар, корпус POM, уплотнения EPDM</t>
+          <t>Трубка полиамидная (PA12) 6×4 мм, Camozzi TRN 6/4, до 28 бар</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>6 мм</t>
+          <t>Ø6 × 4</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>NRV A1–A3, NRV-5: Аргон</t>
+          <t>Аргон</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -5760,22 +5842,22 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>Би энд Би (Camozzi): PVNR 6 (нет в наличии — аналог Aignep по доп. ссылке)</t>
+          <t>Би энд Би (Camozzi): трубка TRN 6/4 (под заказ 7 дней)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Тройник T-образный цанговый 6 мм, Camozzi 6540 6</t>
+          <t>Штуцер прямой цанговый с наружной резьбой G¼″ × трубка 6 мм, Camozzi S6510 6-1/4</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>6 мм</t>
+          <t>G¼″ × 6</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -5785,12 +5867,12 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -5800,49 +5882,23 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Би энд Би (Camozzi): тройник 6540 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Трубка полиамидная (PA12) 6×4 мм, Camozzi TRN 6/4, до 28 бар</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Ø6 × 4</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Аргон</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>≈14 м</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>18 м</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>Би энд Би (Camozzi): трубка TRN 6/4 (под заказ 7 дней)</t>
-        </is>
-      </c>
+          <t>Би энд Би (Camozzi): S6510 6-1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Гросснер</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="4" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="n">
@@ -5850,71 +5906,97 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Штуцер прямой цанговый с наружной резьбой G¼″ × трубка 6 мм, Camozzi S6510 6-1/4</t>
+          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>G¼″ × 6</t>
+          <t>по порту</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Аргон</t>
+          <t>Сжатый воздух к насосам P-2, P-4</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Би энд Би (Camozzi): S6510 6-1/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Гросснер</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t>Гросснер: ёлочка НР</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1">
+      <c r="A27" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: диоптр кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="43.5" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
+          <t>Диоптр кламп 1½″ ASME-BPE, AISI 316, PN10; уплотнения стекла в каталоге — силикон: уточнить у Гросснера EPDM/PTFE (≈5 540 ₽)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>по порту</t>
+          <t>К50,5 (1½″), L — по каталогу</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Сжатый воздух к насосам P-2, P-4</t>
+          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -5924,7 +6006,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -5934,39 +6016,39 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: ёлочка НР</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1">
+          <t>Гросснер: диоптр кламп 1½″</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="43.5" customHeight="1">
       <c r="A29" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Диоптр кламп (стекло, уплотнения PTFE)</t>
+          <t>Клапан обратный кламп пружинный</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>NRV-6: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -5974,119 +6056,119 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: диоптр кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="43.5" customHeight="1">
+          <t>Гросснер: клапан обратный кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Диоптр кламп 1½″ ASME-BPE, AISI 316, PN10; уплотнения стекла в каталоге — силикон: уточнить у Гросснера EPDM/PTFE (≈5 540 ₽)</t>
+          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1½″), L — по каталогу</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>NRV-3: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Клапан обратный муфтовый пружинный, AISI 316, внутр. резьба ¼″ (≈1 280 ₽)</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>¼″ ВР (DN8)</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>NRV-4: Реактор R-1</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: диоптр кламп 1½″</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="43.5" customHeight="1">
-      <c r="A31" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Клапан обратный кламп пружинный</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>NRV-6: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: клапан обратный муфтовый ¼″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>10″</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>F-2: Фильтрация F-2 и фасовка (P-4)</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: клапан обратный кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Клапан обратный кламп пружинный, AISI 316L, уплотнение PTFE, открытие от 0,1 бар (≈7 275 ₽)</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>NRV-3: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6094,27 +6176,27 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: клапан обратный кламп ½″ PTFE</t>
+          <t>Гросснер: корпус 10″</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Клапан обратный муфтовый пружинный, AISI 316, внутр. резьба ¼″ (≈1 280 ₽)</t>
+          <t>Кран игольчатый нерж. AISI 316, внутр. резьба ¼″, PN 413 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>¼″ ВР (DN8)</t>
+          <t>¼″ ВР</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>NRV-4: Реактор R-1</t>
+          <t>FV-1: Реактор R-1</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -6134,27 +6216,27 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: клапан обратный муфтовый ¼″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1">
+          <t>Гросснер: кран игольчатый ¼″ 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
+          <t>Кран шаровой кламп 1″, AISI 316L, PN10 (≈3 265 ₽)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>F-2: Фильтрация F-2 и фасовка (P-4)</t>
+          <t>V-P2: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -6164,7 +6246,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -6174,37 +6256,37 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: корпус 10″</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
+          <t>Гросснер: кран кламп 1″ 316L</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="192" customHeight="1">
       <c r="A35" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Кран игольчатый нерж. AISI 316, внутр. резьба ¼″, PN 413 (≈2 900 ₽)</t>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>¼″ ВР</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>FV-1: Реактор R-1</t>
+          <t>V-P3: Реактор R-1; SV-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-P1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; SP-1, V-S1: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; SV-F1: Нутч F-1 (K119) и гребёнка газов нутча; VV-2: Нутч F-1 (K119) и гребёнка газов нутча; V-F2: Нутч F-1 (K119) и гребёнка газов нутча; V-F3: Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -6214,27 +6296,27 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран игольчатый ¼″ 316</t>
+          <t>Гросснер: кран кламп ½″ 316L</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп 1″, AISI 316L, PN10 (≈3 265 ₽)</t>
+          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>V-P2: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>PI-5: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -6244,49 +6326,49 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: мановакуумметр 63 мм кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Отвод кламп 90°</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: кран кламп 1″ 316L</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="178.5" customHeight="1">
-      <c r="A37" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>V-P3: Реактор R-1; SV-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-G1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; V-P1: Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; SP-1, V-S1: Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; SV-F1: Нутч F-1 (K119) и гребёнка газов нутча; VV-2: Нутч F-1 (K119) и гребёнка газов нутча; V-F2: Нутч F-1 (K119) и гребёнка газов нутча; V-F3: Фильтрация F-2 и фасовка (P-4)</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6294,27 +6376,27 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп ½″ 316L</t>
+          <t>Гросснер: отвод кламп</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой нержавеющий, AISI 316, сёдла PTFE, внутр. резьба ½″ (≈805 ₽)</t>
+          <t>Отвод кламп 90°, AISI 316</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>½″ ВР (DN15)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>V-G2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -6334,37 +6416,37 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кран шаровой ½″ 316</t>
+          <t>Гросснер: отвод кламп 90°</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Мановакуумметр 63 мм, −1…+0,6 бар, мембранный разделитель на кламп</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>PI-5: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -6374,37 +6456,37 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: мановакуумметр 63 мм кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+          <t>Гросснер: патроны</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="70.5" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°</t>
+          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 → К25</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Реактор R-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -6414,37 +6496,37 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп</t>
+          <t>Гросснер: переход 1″ × ½″ 316</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Отвод кламп 90°, AISI 316</t>
+          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К119 → К64</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -6454,37 +6536,37 @@
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: отвод кламп 90°</t>
+          <t>Гросснер: переход 119 × 64 316</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>К64 → К50,5</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -6494,37 +6576,37 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="70.5" customHeight="1">
+          <t>Гросснер: переход 64 × 50,5 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический 1″ × ½″, 3A, AISI 316</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>К50,5 → К25</t>
+          <t>К25 × G¼″ вн.</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Реактор R-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2; Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -6534,27 +6616,27 @@
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 1″ × ½″ 316</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN100 × DN50, AISI 316 (≈15 765 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>К119 → К64</t>
+          <t>К50,5 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -6574,37 +6656,37 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: переход 119 × 64 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="43.5" customHeight="1">
       <c r="A45" s="11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Переход кламп концентрический DIN DN50 × DN25, AISI 316 (≈2 900 ₽)</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>К64 → К50,5</t>
+          <t>К25 × ¼″ BSP вн.</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча; Фильтрация F-2 и фасовка (P-4); Сжатый воздух к насосам P-2, P-4; AV-1: Аргон</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6614,22 +6696,22 @@
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: переход 64 × 50,5 316</t>
+          <t>Гросснер: кламп – резьба внутренняя</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, G¼″, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>К25 × G¼″ вн.</t>
+          <t>К25 × G½″ нар.</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -6639,14 +6721,14 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -6654,32 +6736,32 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
+          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>К50,5 × ¼″ BSP вн.</t>
+          <t>К25 × ¼″</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Реактор R-1</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -6694,37 +6776,37 @@
       </c>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К50,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="43.5" customHeight="1">
+          <t>Гросснер: кламп – резьба наружная</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча; Фильтрация F-2 и фасовка (P-4); Сжатый воздух к насосам P-2, P-4; AV-1: Аргон</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -6734,37 +6816,37 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная G½″, ISO DN15, AISI 316 (≈1 455 ₽)</t>
+          <t>Прокладка кламп EPDM</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>К25 × G½″ нар.</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -6774,37 +6856,37 @@
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная ½″ 316</t>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ¼″, AISI 316</t>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>К25 × ¼″</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -6814,37 +6896,37 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="57" customHeight="1">
+          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба наружная ½″, AISI 316</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>К25 × ½″</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Кламп-соединения на всю установку</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -6854,22 +6936,22 @@
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба наружная</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -6879,12 +6961,12 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -6894,22 +6976,22 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -6919,12 +7001,12 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -6934,22 +7016,22 @@
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽ (≈800 ₽)</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>К50,5 (1½″)</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -6959,12 +7041,12 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -6974,22 +7056,22 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
+          <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
@@ -6999,12 +7081,12 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -7014,17 +7096,17 @@
       </c>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="43.5" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -7034,17 +7116,17 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -7054,39 +7136,39 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: тройник кламп 45° 1″ 316</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -7094,37 +7176,37 @@
       </c>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: тройник кламп 1″ 316</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE</t>
+          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>К25 (½″)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -7134,79 +7216,79 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
+          <t>Гросснер: тройник кламп ½″ 316</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽ (≈900 ₽)</t>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>К50,5 (1½″)</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: фильтр межкламповый K50,5 316</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="43.5" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Тройник кламп 45° равнопроходной, 3A, AISI 316 (≈3 540 ₽)</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч; Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -7214,159 +7296,159 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: тройник кламп 45° 1″ 316</t>
+          <t>Гросснер: фильтр межкламповый 4″ 316</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316 (≈2 370 ₽)</t>
+          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
+          <t>К119 (4″)</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут усиленный DN100 (119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16.5" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16.5" customHeight="1">
+      <c r="A63" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: хомут кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16.5" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Хомут кламп обычный, AISI 304</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>К64 (2″)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Кламп-соединения на всю установку</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: тройник кламп 1″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Тройник кламп прямой равнопроходной, 3A, AISI 316</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: тройник кламп ½″ 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск + сетка 0,5 мм, PN10 (≈2 040 ₽)</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1½″)</t>
-        </is>
-      </c>
-      <c r="D63" s="13" t="inlineStr">
-        <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: фильтр межкламповый K50,5 316</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Фильтр межкламповый AISI 316: перфорированный диск 3 мм + сетка 0,5 мм, PN10 (≈5 655 ₽)</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -7374,37 +7456,37 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: фильтр межкламповый 4″ 316</t>
+          <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 101,6 мм (≈625 ₽)</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>К119 (4″)</t>
+          <t>Ø101,6 (K119, 4″)</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -7414,37 +7496,37 @@
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут усиленный DN100 (119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16.5" customHeight="1">
+          <t>Гросснер: хомут трубный 101,6 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 38,1 мм (≈320 ₽)</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>Ø38,1 (1½″)</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -7454,37 +7536,37 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16.5" customHeight="1">
+          <t>Гросснер: хомут трубный 38,1 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
       <c r="A67" s="11" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут червячный нерж.</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1″)</t>
+          <t>8–12 / 25–40 / 32–50</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22 / 30 / 8</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24 / 32 / 10</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -7494,37 +7576,37 @@
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут червячный</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1">
       <c r="A68" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Хомут кламп обычный, AISI 304</t>
+          <t>Хомут-держатель для труб нерж.</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>К64 (2″)</t>
+          <t>по Ø: ½″</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Кламп-соединения на всю установку</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 компл.</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -7534,27 +7616,27 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут кламп</t>
+          <t>Гросснер: хомут-держатель</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 101,6 мм (≈625 ₽)</t>
+          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Ø101,6 (K119, 4″)</t>
+          <t>К50,5 (1½″) × 400</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
@@ -7574,37 +7656,37 @@
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут трубный 101,6 мм</t>
+          <t>Гросснер: царга кламп 1½″ × 400</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 38,1 мм (≈320 ₽)</t>
+          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Ø38,1 (1½″)</t>
+          <t>К119 (4″) × 500</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -7614,37 +7696,37 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут трубный 38,1 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1">
+          <t>Гросснер: царга кламп</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="57" customHeight="1">
       <c r="A71" s="11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>DN ¼″ (ID 6,4)</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>6 / 30 / 8</t>
+          <t>2,5 м + ≈7 м</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr">
         <is>
-          <t>8 / 32 / 10</t>
+          <t>4 м + 9 м</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -7654,37 +7736,37 @@
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16.5" customHeight="1">
+          <t>Гросснер: силикон PF, DN ¼″</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>по Ø: ½″</t>
+          <t>DN 1″ (ID 25,4)</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>4 м</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
@@ -7694,37 +7776,37 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>Царга кламп (труба 38,1 × 1,65), 3A, AISI 304 (≈2 400 ₽)</t>
+          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>К50,5 (1½″) × 400</t>
+          <t>DN ¾″ (ID 19)</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>C-1, C-2: Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>≈14 м</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18 м</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
@@ -7734,37 +7816,37 @@
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп 1½″ × 400</t>
+          <t>Гросснер: силикон армированный TSO</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Царга кламп, AISI 316L (≈6 150 ₽)</t>
+          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>К119 (4″) × 500</t>
+          <t>К25 × 19,05</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>F-1: Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>Рукава, трубки, крепёж — общее</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
@@ -7774,37 +7856,37 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: царга кламп</t>
+          <t>Гросснер: штуцер K25 × 19,05</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический PF (неармированный), Гросснер</t>
+          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>DN ¼″ (ID 6,4)</t>
+          <t>К50,5 × 25,4</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>2,5 м</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
@@ -7814,37 +7896,37 @@
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: силикон PF, DN ¼″</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1">
+          <t>Гросснер: штуцер K50,5 × 25,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="57" customHeight="1">
       <c r="A76" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>DN 1″ (ID 25,4)</t>
+          <t>К25 × 6,35</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1; Колонны осушки C-1 (сита 3A), C-2 (NaOH) и газ CH₃NH₂ → реактор T2</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>4 м</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -7854,49 +7936,23 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="11" t="n">
-        <v>66</v>
-      </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>DN ¾″ (ID 19)</t>
-        </is>
-      </c>
-      <c r="D77" s="13" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>≈14 м</t>
-        </is>
-      </c>
-      <c r="F77" s="14" t="inlineStr">
-        <is>
-          <t>18 м</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H77" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: силикон армированный TSO</t>
-        </is>
-      </c>
+          <t>Гросснер: штуцер K25 × 6,35</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>КемИнС</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="4" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="5" t="n">
@@ -7904,107 +7960,81 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>Ø ≈ 110 мм</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Рукава, трубки, крепёж — общее</t>
+          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>отрез 0,5 м²</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="11" t="n">
+          <t>КемИнС: фильтровальные ткани PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Пневмо-Электро</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="4" t="n"/>
+    </row>
+    <row r="80" ht="16.5" customHeight="1">
+      <c r="A80" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>Штуцер шланговый кламп, ёлочка 25,4 (1″), AISI 316</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 × 25,4</t>
-        </is>
-      </c>
-      <c r="D79" s="13" t="inlineStr">
-        <is>
-          <t>Слив реактора BV-1 и выгрузка суспензии P-2 → нутч</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F79" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H79" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: штуцер K50,5 × 25,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="5" t="n">
-        <v>69</v>
-      </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 6,35 (¼″), AISI 316</t>
+          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>К25 × 6,35</t>
+          <t>¼″</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
+          <t>Реактор R-1</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>≈3 м</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 м</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
@@ -8014,14 +8044,14 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 6,35</t>
+          <t>Пневмо-Электро: трубки PTFE</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>КемИнС</t>
+          <t>Поставщик газа</t>
         </is>
       </c>
       <c r="B81" s="3" t="n"/>
@@ -8032,23 +8062,23 @@
       <c r="G81" s="3" t="n"/>
       <c r="H81" s="4" t="n"/>
     </row>
-    <row r="82" ht="30" customHeight="1">
+    <row r="82" ht="16.5" customHeight="1">
       <c r="A82" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Ткань фильтровальная PP (или PTFE) — круг под K119 на межкламповый фильтр</t>
+          <t>Баллон аргона 40 л (Ar ≥ 99,998 %)</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Ø ≈ 110 мм</t>
+          <t>40 л, W21,8</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Нутч F-1 (K119) и гребёнка газов нутча</t>
+          <t>AR-1: Аргон</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -8058,7 +8088,7 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>отрез 0,5 м²</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr">
@@ -8068,14 +8098,14 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>КемИнС: фильтровальные ткани PP</t>
+          <t>Поставщик газа</t>
         </is>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Пневмо-Электро</t>
+          <t>Профрезина</t>
         </is>
       </c>
       <c r="B83" s="3" t="n"/>
@@ -8086,33 +8116,33 @@
       <c r="G83" s="3" t="n"/>
       <c r="H83" s="4" t="n"/>
     </row>
-    <row r="84" ht="16.5" customHeight="1">
+    <row r="84" ht="43.5" customHeight="1">
       <c r="A84" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Трубка PTFE ¼″ (6,35 × 4,35), бухта</t>
+          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>¼″</t>
+          <t>500×500×3</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Реактор R-1</t>
+          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>≈3 м</t>
+          <t>1 лист</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>5 м</t>
+          <t>2 листа</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
@@ -8122,14 +8152,14 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>Пневмо-Электро: трубки PTFE</t>
+          <t>Профрезина: техпластина EPDM 500×500×3</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Поставщик газа</t>
+          <t>Яндекс.Маркет</t>
         </is>
       </c>
       <c r="B85" s="3" t="n"/>
@@ -8140,266 +8170,157 @@
       <c r="G85" s="3" t="n"/>
       <c r="H85" s="4" t="n"/>
     </row>
-    <row r="86" ht="16.5" customHeight="1">
+    <row r="86" ht="43.5" customHeight="1">
       <c r="A86" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Редуктор баллонный аргоновый с манометрами, низкое давление на выходе 0,2–0,3 бар (двухступенчатый или с точной регулировкой)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>вход W21,8; выход — уточнить (G¼″)</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Аргон</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Яндекс.Маркет: редуктор аргоновый</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="57" customHeight="1">
+      <c r="A87" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Баллон аргона 40 л (Ar ≥ 99,998 %)</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>40 л, W21,8</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>AR-1: Аргон</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>Ротаметр газовый с игольчатым вентилем (стекло, поплавок), диапазон до 10 л/мин; для синтеза 0,1–0,2 л/мин — второй, малый (0,1–1 л/мин), либо один с вентилем тонкой регулировки</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>присоединение — уточнить (G¼″)</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>PR-1: Аргон</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G86" s="17" t="inlineStr">
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G87" s="17" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>Поставщик газа</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Профрезина</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="4" t="n"/>
-    </row>
-    <row r="88" ht="43.5" customHeight="1">
-      <c r="A88" s="5" t="n">
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>Яндекс.Маркет: ротаметр с вентилем</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>по замеру (нерж. 316)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="4" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка крышки бака G-1 — вырезать из техпластины EPDM 500×500×3 мм (45–80 Sh A, −45…+150 °C)</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>500×500×3</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Генератор метиламина G-1 (бак Altmaler БК-40ПВ) и подача водного метиламина P-1</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>1 лист</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>2 листа</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>Профрезина: техпластина EPDM 500×500×3</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Яндекс.Маркет</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="4" t="n"/>
-    </row>
-    <row r="90" ht="43.5" customHeight="1">
-      <c r="A90" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Редуктор баллонный аргоновый с манометрами, низкое давление на выходе 0,2–0,3 бар (двухступенчатый или с точной регулировкой)</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>вход W21,8; выход — уточнить (G¼″)</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Аргон</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Переходник на штуцер аргона крышки G-1 → резьба G¼″ внутр.</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>по порту G-1</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>A2: Аргон</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr">
+      <c r="G89" s="17" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>Яндекс.Маркет: редуктор аргоновый</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="57" customHeight="1">
-      <c r="A91" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>Ротаметр газовый с игольчатым вентилем (стекло, поплавок), диапазон до 10 л/мин; для синтеза 0,1–0,2 л/мин — второй, малый (0,1–1 л/мин), либо один с вентилем тонкой регулировки</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t>присоединение — уточнить (G¼″)</t>
-        </is>
-      </c>
-      <c r="D91" s="13" t="inlineStr">
-        <is>
-          <t>PR-1: Аргон</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F91" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G91" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H91" s="15" t="inlineStr">
-        <is>
-          <t>Яндекс.Маркет: ротаметр с вентилем</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="H89" s="10" t="inlineStr">
         <is>
           <t>по замеру (нерж. 316)</t>
         </is>
       </c>
-      <c r="B92" s="3" t="n"/>
-      <c r="C92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="4" t="n"/>
-    </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Переходник на штуцер аргона крышки G-1 → резьба G¼″ внутр.</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>по порту G-1</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>A2: Аргон</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G93" s="17" t="inlineStr">
-        <is>
-          <t>УТОЧНИТЬ</t>
-        </is>
-      </c>
-      <c r="H93" s="10" t="inlineStr">
-        <is>
-          <t>по замеру (нерж. 316)</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H93"/>
-  <mergeCells count="16">
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A21:H21"/>
+  <autoFilter ref="A1:H89"/>
+  <mergeCells count="15">
+    <mergeCell ref="A77:H77"/>
     <mergeCell ref="A83:H83"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A81:H81"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A89:H89"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A79:H79"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A88:H88"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <hyperlinks>
@@ -8409,76 +8330,73 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/tefkot/itog/tefkot-770-smeta.xlsx
+++ b/tefkot/itog/tefkot-770-smeta.xlsx
@@ -12,11 +12,11 @@
     <sheet name="Сводная к заказу" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По узлам схемы'!$A$1:$J$99</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'По узлам схемы'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Аргоновая линия'!$A$1:$J$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Аргоновая линия'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Сводная к заказу'!$A$1:$H$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Сводная к заказу'!$A$1:$H$97</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Сводная к заказу'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>крепление колонн C-1, C-2 к раме или стенду — по 2 на колонну (на царгу, выше и ниже середины)</t>
+          <t>крепление колонн C-1, C-2 к стойке-треноге — по 2 на колонну (на царгу, выше и ниже середины)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>крепление нутча F-1 к раме / опоре — 2 шт. на царги K119</t>
+          <t>крепление нутча F-1 к стойке-треноге — 2 шт. на царги K119</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -3074,34 +3074,34 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="16.5" customHeight="1">
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="11" t="n">
         <v>55</v>
       </c>
       <c r="B61" s="12" t="n"/>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>Хомут-держатель для труб нерж.</t>
+          <t>Хомут трубный на ножке (держатель), AISI 304, SMS, для трубы 12,7 мм (≈205 ₽)</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>по Ø: ½″</t>
+          <t>Ø12,7 (½″)</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>крепление гребёнки нутча к раме — по месту</t>
+          <t>крепление гребёнки газов нутча (труба ½″) к раме / стойке нутча — 2 шт.</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>1 компл.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -3111,14 +3111,14 @@
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: хомут-держатель</t>
+          <t>Гросснер: хомут трубный 12,7 мм</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Фильтрация F-2 и фасовка (P-4)</t>
+          <t>Опоры-треноги колонн C-1, C-2 и нутча F-1 (напольные, из конструкционного алюминиевого профиля, паз 10)</t>
         </is>
       </c>
       <c r="B62" s="3" t="n"/>
@@ -3131,75 +3131,75 @@
       <c r="I62" s="3" t="n"/>
       <c r="J62" s="4" t="n"/>
     </row>
-    <row r="63" ht="43.5" customHeight="1">
+    <row r="63" ht="57" customHeight="1">
       <c r="A63" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>P-4</t>
-        </is>
-      </c>
+      <c r="B63" s="6" t="n"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="n"/>
+          <t>Профиль конструкционный алюминиевый 45×45, паз 10, L = 1600 мм (АЛТЕРВИА, АД31Т1, анодированный) — вертикальная стойка</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>45×45 × 1600</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>фильтрат нутча → F-2</t>
+          <t>2 стойки: (1) колонны C-1 и C-2 — на неё 4 хомута Ø38,1; (2) нутч F-1 — 2 хомута Ø101,6 на царги и 2 хомута Ø12,7 гребёнки. Длину подтвердить по месту</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Ампика: МН-0,25-PVDF/PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
+          <t>Всеинструменты: профиль 45×45 паз 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="43.5" customHeight="1">
       <c r="A64" s="11" t="n">
         <v>57</v>
       </c>
       <c r="B64" s="12" t="n"/>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
+          <t>Профиль конструкционный алюминиевый 40×40, паз 10, L = 700 мм, упаковка 4 шт. — ноги треноги</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>К25 × ¼″ BSP вн.</t>
+          <t>40×40 × 700</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
+          <t>по 3 ноги на стойку (под 120°), 6 шт. → 2 упаковки (2 шт. в запас / подкосы)</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6 шт.</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 уп.</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+          <t>Всеинструменты: профиль 40×40 × 700, уп. 4</t>
         </is>
       </c>
     </row>
@@ -3217,34 +3217,30 @@
       <c r="A65" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>F-2</t>
-        </is>
-      </c>
+      <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Корпус микропористого фильтра 10″ на клампах</t>
+          <t>Уголок усиленный для соединения профилей, паз 10 (уп. 10 шт.)</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>паз 10</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
+          <t>крепление ног к стойке: по 3 уголка на стойку + подкосы — 6…10 шт.</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>≈8</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 уп.</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -3254,40 +3250,40 @@
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: корпус 10″</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1">
+          <t>Всеинструменты: уголок усиленный АЛТЕРВИА, уп. 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="43.5" customHeight="1">
       <c r="A66" s="11" t="n">
         <v>59</v>
       </c>
       <c r="B66" s="12" t="n"/>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
+          <t>Опора регулируемая (ножка) с резьбой в торец профиля 40×40, Ø 40–60 мм, резиновая подошва</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>10″</t>
+          <t>М8 / М10 (по профилю)</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>по 2 шт. каждого рейтинга</t>
+          <t>концы ног треноги — выставить стойки по уровню</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
           <t>КУПИТЬ</t>
@@ -3295,38 +3291,38 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: патроны</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
+          <t>Яндекс.Маркет: опора регулируемая для профиля 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="43.5" customHeight="1">
       <c r="A67" s="5" t="n">
         <v>60</v>
       </c>
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+          <t>Гайка-сухарь (молоток) паз 10 М8 + болт М8 нерж. с шайбой</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>под корпус 10″</t>
+          <t>паз 10 · М8</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
+          <t>крепление хомутов на ножке к стойке (резьбу ножки хомутов — уточнить, М8/М10) и уголков: ≈8 хомутов + 16 под уголки</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>≈30</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 компл. (40 шт.)</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
@@ -3336,59 +3332,55 @@
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Hydrohype: кольца в оболочке FEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
+          <t>Яндекс.Маркет: гайка молоток паз 10 М8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="57" customHeight="1">
       <c r="A68" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="B68" s="12" t="inlineStr">
-        <is>
-          <t>V-F3</t>
-        </is>
-      </c>
+      <c r="B68" s="12" t="n"/>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
+          <t>Альтернатива: тренога сварная нерж. (AISI 304) под заказ — труба 40×40, стойка 1600 мм, 3 ноги по 600 мм, регулируемые опоры</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>К25 (½″)</t>
+          <t>по эскизу</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>выход F-2 → налив</t>
+          <t>если профиль покажется недостаточно жёстким для нутча (≈25–35 кг с осадком на высоте ≈1,5 м); стойку нутча в любом случае прикрепить к раме реактора / стене сверху</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>УТОЧНИТЬ</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: кран кламп ½″ 316L</t>
+          <t>местная металлообработка</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Сжатый воздух к насосам P-2, P-4</t>
+          <t>Фильтрация F-2 и фасовка (P-4)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n"/>
@@ -3401,34 +3393,34 @@
       <c r="I69" s="3" t="n"/>
       <c r="J69" s="4" t="n"/>
     </row>
-    <row r="70" ht="30" customHeight="1">
+    <row r="70" ht="43.5" customHeight="1">
       <c r="A70" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B70" s="6" t="n"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>P-4</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>⅛″ NPT × ¼″ BSP</t>
-        </is>
-      </c>
+          <t>Мембранный пневмонасос Ампика МН-0,25-PVDF/PTFE: ¼″ NPT вн., воздух ⅛″ NPT, до 18 л/мин</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="n"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>вход воздуха насоса (по 1 на насос)</t>
+          <t>фильтрат нутча → F-2</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
@@ -3438,7 +3430,7 @@
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>Rizur: ниппель переходной</t>
+          <t>Ампика: МН-0,25-PVDF/PTFE</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3441,7 @@
       <c r="B71" s="12" t="n"/>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316 (≈1 455 ₽)</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -3459,17 +3451,17 @@
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
+          <t>P-4: вход и выход (на ниппели ¼″ NPT × ¼″ BSP — в разделе выгрузки)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -3487,30 +3479,34 @@
       <c r="A72" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B72" s="6" t="n"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>F-2</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+          <t>Корпус микропористого фильтра 10″ на клампах</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>G¼ × 8</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>выход регулятора и кламп ¼″ у насоса</t>
+          <t>тонкая фильтрация фильтрата (+1 корпус опционально)</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
@@ -3520,7 +3516,7 @@
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>BB-Engineering: S6510 8-1/4</t>
+          <t>Гросснер: корпус 10″</t>
         </is>
       </c>
     </row>
@@ -3531,27 +3527,27 @@
       <c r="B73" s="12" t="n"/>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
+          <t>Патроны 10″ 5 / 2 / 0,2 / 0,05 мкм (PTFE или PP/PES)</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>G¼</t>
+          <t>10″</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
+          <t>по 2 шт. каждого рейтинга</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
@@ -3561,7 +3557,7 @@
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
-          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
+          <t>Гросснер: патроны</t>
         </is>
       </c>
     </row>
@@ -3572,592 +3568,596 @@
       <c r="B74" s="6" t="n"/>
       <c r="C74" s="7" t="inlineStr">
         <is>
+          <t>Кольца уплотнительные в оболочке FEP — вместо штатных силикон/EPDM</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>под корпус 10″</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>крышка корпуса и посадка патронов (продукт — углеводород, EPDM не стоек)</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>Hydrohype: кольца в оболочке FEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>V-F3</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>Кран шаровой кламп 3A, сёдла PTFE, AISI 316L, PN10 (≈3 080 ₽)</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>выход F-2 → налив</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: кран кламп ½″ 316L</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Сжатый воздух к насосам P-2, P-4</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+      <c r="I76" s="3" t="n"/>
+      <c r="J76" s="4" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Ниппель переходной ⅛″ NPT нар. × ¼″ BSP нар., нерж. или латунь</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>⅛″ NPT × ¼″ BSP</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>вход воздуха насоса (по 1 на насос)</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Rizur: ниппель переходной</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="12" t="n"/>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>Переходник кламп – резьба внутренняя ISO DN8, ¼″ BSP, AISI 316</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>К25 × ¼″ BSP вн.</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>по 2 на насос: на ниппель и ответный — на цангу линии</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: кламп – резьба внутренняя ¼″ × К25</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Фитинг цанговый прямой G¼ × трубка 8 мм, Camozzi S6510 8-1/4</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>G¼ × 8</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>выход регулятора и кламп ¼″ у насоса</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>BB-Engineering: S6510 8-1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Быстроразъём пневматический «папа» G¼ наружная (EURO)</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>G¼</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>вход регулятора ← магистраль; тип разъёма магистрали уточнить</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>BB-Engineering: быстросъёмы EUROPEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
           <t>Выхлоп насосов: шланг в вытяжку + ёлочка под порт выхлопа</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>по порту</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>резьбу выхлопного порта МН-0,25 уточнить у Ампики</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="H81" s="17" t="inlineStr">
         <is>
           <t>УТОЧНИТЬ</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>Гросснер: ёлочка НР</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Кламп-соединения на всю установку: хомуты и прокладки (по ведомости; без реактора — на штуцерах P1–P4 родные клампы, без E-1, гребёнки реактора и VP-1)</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
-      <c r="J75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="16.5" customHeight="1">
-      <c r="A76" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="B82" s="3" t="n"/>
+      <c r="C82" s="3" t="n"/>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="3" t="n"/>
+      <c r="J82" s="4" t="n"/>
+    </row>
+    <row r="83" ht="16.5" customHeight="1">
+      <c r="A83" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>все соединения ½″ нашей обвязки</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="70.5" customHeight="1">
-      <c r="A77" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="13" t="inlineStr">
+    <row r="84" ht="70.5" customHeight="1">
+      <c r="A84" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="B84" s="12" t="n"/>
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>BV-1 → отвод, тройники под BV-1 и на входе нутча, кран V-P2, выгрузка P-2, переходы нутча; колонны C-1, C-2: по 4 стыка на колонну — фильтр/переход, диоптр/фильтр, диоптр/царга, царга/верхний переход (8)</t>
         </is>
       </c>
-      <c r="F77" s="12" t="inlineStr">
+      <c r="F84" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G77" s="14" t="inlineStr">
+      <c r="G84" s="14" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="7" t="inlineStr">
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Хомут кламп обычный, AISI 304</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>К64 (2″)</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>нутч: стыки переходов 119/64 → 64/50,5 сверху и снизу</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
         <is>
           <t>Гросснер: хомут кламп</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="57" customHeight="1">
-      <c r="A79" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="13" t="inlineStr">
+    <row r="86" ht="57" customHeight="1">
+      <c r="A86" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="B86" s="12" t="n"/>
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>Хомут кламп УСИЛЕННЫЙ (болтовой), AISI 304 (≈2 770 ₽)</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D86" s="12" t="inlineStr">
         <is>
           <t>К119 (4″)</t>
         </is>
       </c>
-      <c r="E79" s="13" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход (с PTFE — только болтовые)</t>
         </is>
       </c>
-      <c r="F79" s="12" t="inlineStr">
+      <c r="F86" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G79" s="14" t="inlineStr">
+      <c r="G86" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I79" s="15" t="inlineStr">
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
         <is>
           <t>Гросснер: хомут усиленный DN100 (119)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="43.5" customHeight="1">
-      <c r="A80" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="7" t="inlineStr">
+    <row r="87" ht="43.5" customHeight="1">
+      <c r="A87" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>К25 (½″)</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>где эфир и углеводороды: дозирование, слив и проба, выгрузка, нутч и его гребёнка, вакуум нутча, P-4, F-2</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="13" t="inlineStr">
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="B88" s="12" t="n"/>
+      <c r="C88" s="13" t="inlineStr">
         <is>
           <t>Прокладка кламп PTFE</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>К50,5 (1″)</t>
         </is>
       </c>
-      <c r="E81" s="13" t="inlineStr">
+      <c r="E88" s="13" t="inlineStr">
         <is>
           <t>BV-1 → отвод, тройники 45° и прямой, кран V-P2, переходы 50,5/25, выгрузка P-2, нутч</t>
         </is>
       </c>
-      <c r="F81" s="12" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G81" s="14" t="inlineStr">
+      <c r="G88" s="14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I81" s="15" t="inlineStr">
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
         <is>
           <t>Гросснер: прокладка кламп PTFE</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="43.5" customHeight="1">
-      <c r="A82" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>К50,5 (1″)</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>К64 (2″)</t>
-        </is>
-      </c>
-      <c r="E83" s="13" t="inlineStr">
-        <is>
-          <t>нутч: стыки переходов</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G83" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I83" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="43.5" customHeight="1">
-      <c r="A84" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп PTFE</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>К119 (4″)</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка кламп PTFE</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="43.5" customHeight="1">
-      <c r="A85" s="11" t="n">
-        <v>76</v>
-      </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>К25 (½″)</t>
-        </is>
-      </c>
-      <c r="E85" s="13" t="inlineStr">
-        <is>
-          <t>без углеводородов: P-1 → G-1 (4), порт G-1 → SV-G1 → рукав (2), выход газа и V-G1 (2), колонны (4), NRV-3 (2), воздух насосов (2)</t>
-        </is>
-      </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="43.5" customHeight="1">
-      <c r="A86" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>К50,5 (1½″)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>колонны: диоптр → царга (2), межкламповый фильтр снизу — с двух сторон: диоптр/фильтр и фильтр/переход (4)</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>Гросснер: уплотнения кламп (EPDM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="57" customHeight="1">
-      <c r="A87" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="B87" s="12" t="n"/>
-      <c r="C87" s="13" t="inlineStr">
-        <is>
-          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>К50,5 (1½″)</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="inlineStr">
-        <is>
-          <t>верх колонн C-1, C-2 (царга → переход 50,5/25): держит засыпку вместо межклампового фильтра, задерживает пыль сит 3A и NaOH — по 1 на колонну</t>
-        </is>
-      </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>КУПИТЬ</t>
-        </is>
-      </c>
-      <c r="I87" s="15" t="inlineStr">
-        <is>
-          <t>Гросснер: прокладка с сеткой EPDM K50,5 0,1 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Рукава, трубки, крепёж — общее</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n"/>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="4" t="n"/>
-    </row>
-    <row r="89" ht="84" customHeight="1">
+    <row r="89" ht="43.5" customHeight="1">
       <c r="A89" s="5" t="n">
         <v>79</v>
       </c>
       <c r="B89" s="6" t="n"/>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Шланг силиконовый фармацевтический армированный проволокой TSO, Гросснер</t>
+          <t>Прокладка кламп PTFE С СЕТКОЙ AISI 316, ячейка 0,15 мм (mesh 100), ≈900 ₽</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>DN ¾″ (ID 19)</t>
+          <t>К50,5 (1″)</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>линии K25 на ёлочках K25 × 19,05: тройник 45° нутча → гребёнка 1 м, V-F2 → P-4 1 м, P-4 → F-2 1,5 м, бочка → V-S1 2,5 м, F-2 → канистра 1,5 м, VV-2 → тройник VP-1 2,5 м, SV-G1 и SV-F1 → коллектор сбросов по 2 м; хомуты 25–40</t>
+          <t>низ нутча: стык переходов 64/50,5 → 50,5/½″ — ловит зёрна Na₂SO₄ и волокна ткани, если прорвутся, до крана V-F2 и насоса P-4</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>≈14 м</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>18 м</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
@@ -4167,38 +4167,38 @@
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: силикон армированный TSO</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="43.5" customHeight="1">
+          <t>Гросснер: прокладка с сеткой PTFE 0,15 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
       <c r="A90" s="11" t="n">
         <v>80</v>
       </c>
       <c r="B90" s="12" t="n"/>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>Штуцер шланговый кламп, ёлочка 19,05 (¾″), AISI 316</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>К25 × 19,05</t>
+          <t>К64 (2″)</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>концы рукавов ¾″: гребёнка нутча 2, P-4 вход 2, P-4 → F-2 2, бочка → V-S1 2, налив 1, VV-2 → VP-1 2, SV-G1 1, SV-F1 1</t>
+          <t>нутч: стыки переходов</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
@@ -4208,38 +4208,38 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>Гросснер: штуцер K25 × 19,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="57" customHeight="1">
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="43.5" customHeight="1">
       <c r="A91" s="5" t="n">
         <v>81</v>
       </c>
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Хомут червячный нерж.</t>
+          <t>Прокладка кламп PTFE</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>8–12 / 25–40 / 32–50</t>
+          <t>К119 (4″)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>по 2 на конец: шланг PF ¼″ на ёлочках 6,35 — линия P-1 (3 конца) и газ CH₃NH₂ (8 концов: 6 ёлочек + V-G1 + T2) / рукава ¾″ (15 концов, вкл. 2 конца у коллектора) / рукава 1″ (4)</t>
+          <t>нутч: 6 стыков — переход/верхний диоптр, диоптр/царга, царга/царга, царга/нижний диоптр, диоптр/фильтр, фильтр/переход</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>22 / 30 / 8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>24 / 32 / 10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
@@ -4249,63 +4249,326 @@
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Гросснер: хомут червячный</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="57" customHeight="1">
+          <t>Гросснер: прокладка кламп PTFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="43.5" customHeight="1">
       <c r="A92" s="11" t="n">
         <v>82</v>
       </c>
       <c r="B92" s="12" t="n"/>
       <c r="C92" s="13" t="inlineStr">
         <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>К25 (½″)</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>без углеводородов: P-1 → G-1 (4), порт G-1 → SV-G1 → рукав (2), выход газа и V-G1 (2), колонны (4), NRV-3 (2), воздух насосов (2)</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="43.5" customHeight="1">
+      <c r="A93" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>К50,5 (1½″)</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>колонны: диоптр → царга (2), межкламповый фильтр снизу — с двух сторон: диоптр/фильтр и фильтр/переход (4)</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>КУПИТЬ</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>Гросснер: уплотнения кламп (EPDM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="57" customHeight="1">
+      <c r="A94" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="B94" s="12" t="n"/>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>Прокладка кламп EPDM С СЕТКОЙ AISI 316, ячейка 0,1 мм (mesh 140), ≈800 ₽</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>К50,5 (1½″)</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>верх колонн C-1, C-2 (царга → переход 50,5/25): держит засыпку вместо межклам